--- a/docs/22_Validation_Results.xlsx
+++ b/docs/22_Validation_Results.xlsx
@@ -135,7 +135,7 @@
     <t>STARTING A NEW RUN</t>
   </si>
   <si>
-    <t>Doc 21 Phase 6 requires the suite to be re-run after any fact-table reload. Eleven of the seventeen are data-dependent — the Check Catalog tab marks which. Re-run all seventeen anyway unless you are short of time; the six structural checks cost minutes.</t>
+    <t>Doc 21 Phase 6 requires the suite to be re-run after any fact-table reload. Twelve of the seventeen are data-dependent — the Check Catalog tab marks which. Re-run all seventeen anyway unless you are short of time; the five structural checks cost minutes.</t>
   </si>
   <si>
     <t>On Check Results, select the seventeen rows of the most recent run and copy them.</t>
@@ -345,7 +345,7 @@
     <t>Referential integrity</t>
   </si>
   <si>
-    <t>The §6.4 coverage query returns zero rows</t>
+    <t>The §6.5 coverage query returns zero rows</t>
   </si>
   <si>
     <t>Date relationship integrity</t>
@@ -456,7 +456,7 @@
     <t>SSMS or Power BI</t>
   </si>
   <si>
-    <t>Group FactSectorSales by DateKey for category 44X72 and confirm one row per month from pStartPeriod to pEndPeriod. A COUNTROWS card by year is enough.</t>
+    <t>Group FactSectorSales by DateKey for category 44X72 and confirm one row per month from pStartPeriod through the latest published MARTS month. A COUNTROWS card by year is enough.</t>
   </si>
   <si>
     <t>Treating an overlapping category set as a partition, and reporting a sum that double-counts.</t>
@@ -480,7 +480,7 @@
     <t>Unmapped category or item-type codes, which appear in the reports as a blank slicer entry.</t>
   </si>
   <si>
-    <t>Run the coverage query in doc 02 §6.4. A non-zero result lists exactly which codes are missing from RefMappings.xlsx.</t>
+    <t>Run the coverage query in doc 02 §6.5. A non-zero result lists exactly which codes are missing from RefMappings.xlsx.</t>
   </si>
   <si>
     <t>Fact dates outside the DimDate range. Power BI creates a blank row silently and time intelligence goes quietly wrong.</t>

--- a/docs/22_Validation_Results.xlsx
+++ b/docs/22_Validation_Results.xlsx
@@ -6,23 +6,22 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3040" yWindow="3620" windowWidth="34800" windowHeight="18440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Example" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check Results" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check Catalog" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure Log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Example" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check Results" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check Catalog" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Summary'!$A$4:$M$60</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Run Summary'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Check Results'!$A$4:$J$600</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Check Results'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Check Catalog'!$A$4:$I$21</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Check Catalog'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Failure Log'!$A$4:$J$200</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Failure Log'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Run Summary'!$A$4:$M$60</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Run Summary'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Check Results'!$A$4:$J$600</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Check Results'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Check Catalog'!$A$4:$I$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Check Catalog'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Failure Log'!$A$4:$J$200</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Failure Log'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -251,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -438,6 +437,7 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -949,76 +949,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="49" t="inlineStr">
-        <is>
-          <t>The four tabs — what each is for and what you type on it. The tab names are clickable hyperlinks that jump straight to the sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="49" t="inlineStr">
-        <is>
-          <t>Recording a run — five steps, including the one that matters: put a number in Observed value, not a tick. "330,080 staged / 330,080 loaded" is a record; "looks fine" is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="49" t="inlineStr">
-        <is>
-          <t>What the Outcome column means — PASS, BLOCKED, PASSED WITH FAILURES, INCOMPLETE, each with what you do about it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="49" t="inlineStr">
-        <is>
-          <t>Starting a new run — the copy/paste/clear procedure, and the note that the Run Summary row must be copied so the formulas come with it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="49" t="inlineStr">
-        <is>
-          <t>When a check fails — Fail stays Fail; it goes on the Failure Log and stays open until a later run re-verifies it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="49" t="inlineStr">
-        <is>
-          <t>Rules — don't reword the checks (they're quoted from doc 02 §9); N/A needs a reason in Notes or it should stay "Not run"; Run ID must match exactly between the two tabs, a trailing space zeroes the counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="49" t="inlineStr">
-        <is>
-          <t>Formula cells — do not type over these — names the exact ranges (Run Summary F:K and L, Failure Log J) and the row limits (Check Results 5–600, Run Summary 5–60).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Verified after the rebuild: seeded 16 Pass / 1 blocking Fail → Run Summary returns 17, 16, 1, 0, 1, 94%, BLOCKED. Written to X:\retail-sector-health\docs\.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
     <tabColor rgb="FF1F3864"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -1045,6 +975,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1" s="42">
       <c r="A4" s="52" t="inlineStr">
         <is>
@@ -1052,6 +983,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="18" customHeight="1" s="42">
       <c r="B6" s="1" t="inlineStr">
         <is>
@@ -1119,6 +1051,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="30" customHeight="1" s="42">
       <c r="A13" s="5" t="n">
         <v>1</v>
@@ -1139,13 +1072,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="34" customHeight="1" s="42">
+    <row r="15" ht="43" customHeight="1" s="42">
       <c r="A15" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B15" s="53" t="inlineStr">
         <is>
-          <t>For each check, go to Check Results and complete four cells on that check's row: Result (dropdown: Pass, Fail, N/A, Not run), Observed value / evidence, Checked by and Date checked.</t>
+          <t>For each check, go to Check Results and complete four cells on that check's row: Result (dropdown: Pass, Fail, N/A, Not run), Observed value / evidence, Checked by and Date checked. For checks 7, 8, 15, 16 and 17, also update Reports covered each time a report pass adds a report.</t>
         </is>
       </c>
     </row>
@@ -1176,6 +1109,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="18" customHeight="1" s="42">
       <c r="B20" s="1" t="inlineStr">
         <is>
@@ -1200,7 +1134,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="46" customHeight="1" s="42">
+    <row r="22" ht="56.5" customHeight="1" s="42">
       <c r="B22" s="6" t="inlineStr">
         <is>
           <t>PASSED WITH FAILURES</t>
@@ -1208,11 +1142,11 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Something failed, but only Advisory checks — 3, 10 and 11, the three document 02 phrases as “document what you find” rather than a pass mark. Publishing is a judgement call, and the Failure Log entry is what makes it a documented one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1" s="42">
+          <t>All seventeen recorded and nothing Blocking failed, but an Advisory check did — 3, 10 or 11. Checks 3 and 10 record a finding rather than a pass mark in document 02 §9; check 11 is rated Advisory because a missing explanation is fixed on the report page without touching the data. Publishing is a judgement call, and the Failure Log entry is what makes it a documented one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="43" customHeight="1" s="42">
       <c r="B23" s="6" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
@@ -1220,7 +1154,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Fewer than seventeen results recorded; the cell says how many are missing. A partial run is never a pass.</t>
+          <t>Fewer than seventeen results recorded and nothing Blocking failed; the cell says how many are missing, and how many Advisory checks are failing so far. A partial run is never a pass. After the model pass it reads INCOMPLETE — 5 not recorded, which is the state that permits publishing the model.</t>
         </is>
       </c>
     </row>
@@ -1231,10 +1165,11 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="44" customHeight="1" s="42">
+    <row r="25"/>
+    <row r="26" ht="43" customHeight="1" s="42">
       <c r="B26" s="53" t="inlineStr">
         <is>
-          <t>Doc 21 Phase 6 requires the suite to be re-run after any fact-table reload. Twelve of the seventeen are data-dependent — the Check Catalog tab marks which. Re-run all seventeen anyway unless you are short of time; the five structural checks cost minutes.</t>
+          <t>Doc 21 Phase 6 requires the suite to be re-run after any fact-table reload. Twelve of the seventeen are data-dependent — the Check Catalog tab marks which — and those twelve are the required re-run (document 25 §4). The five report checks are re-run only when a report has changed since the last run; otherwise record them as N/A with “no report change since Run n” in Notes.</t>
         </is>
       </c>
     </row>
@@ -1285,6 +1220,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33" ht="34" customHeight="1" s="42">
       <c r="A33" s="5" t="n">
         <v>1</v>
@@ -1332,6 +1268,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="44" customHeight="1" s="42">
       <c r="A39" s="7" t="inlineStr">
         <is>
@@ -1399,6 +1336,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46" ht="32" customHeight="1" s="42">
       <c r="B46" s="1" t="inlineStr">
         <is>
@@ -1449,6 +1387,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52" ht="18" customHeight="1" s="42">
       <c r="B52" s="1" t="inlineStr">
         <is>
@@ -1541,14 +1480,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001B9E8F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="42" min="1" max="1"/>
@@ -1733,13 +1672,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="46" customHeight="1" s="42">
+    <row r="23" ht="43" customHeight="1" s="42">
       <c r="A23" s="5" t="n">
         <v>5</v>
       </c>
       <c r="B23" s="41" t="inlineStr">
         <is>
-          <t>Difference is more than 0: some rows did not load. Before deciding anything, find out which rows and why. The load procedure drops a staged row for three reasons — the year or month will not convert, the item code is blank, or the date falls outside DimDate. This query counts each:</t>
+          <t>Difference is more than 0: some rows did not load. Before deciding anything, find out which rows and why. The load procedure drops a staged row for five reasons — the year or month will not convert, the item code is blank, the date falls outside DimDate, or the supplier or item has no row in its dimension table. This query counts each:</t>
         </is>
       </c>
     </row>
@@ -1753,21 +1692,21 @@
     <row r="25" ht="15" customHeight="1" s="42">
       <c r="B25" s="60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SUM(CASE WHEN TRY_CONVERT(int, [YEAR]) IS NULL</t>
+          <t xml:space="preserve">    SUM(CASE WHEN TRY_CONVERT(int, src.[YEAR]) IS NULL</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="42">
       <c r="B26" s="60" t="inlineStr">
         <is>
-          <t xml:space="preserve">              OR TRY_CONVERT(int, [MONTH]) IS NULL</t>
+          <t xml:space="preserve">              OR TRY_CONVERT(int, src.[MONTH]) IS NULL</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="42">
       <c r="B27" s="60" t="inlineStr">
         <is>
-          <t xml:space="preserve">              OR TRY_CONVERT(int, [MONTH]) NOT BETWEEN 1 AND 12</t>
+          <t xml:space="preserve">              OR TRY_CONVERT(int, src.[MONTH]) NOT BETWEEN 1 AND 12</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1720,7 @@
     <row r="29" ht="15" customHeight="1" s="42">
       <c r="B29" s="60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SUM(CASE WHEN NULLIF(LTRIM(RTRIM([ITEM CODE])), '') IS NULL</t>
+          <t xml:space="preserve">    SUM(CASE WHEN NULLIF(LTRIM(RTRIM(src.[ITEM CODE])), '') IS NULL</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1734,7 @@
     <row r="31" ht="15" customHeight="1" s="42">
       <c r="B31" s="60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SUM(CASE WHEN TRY_CONVERT(int, [MONTH]) BETWEEN 1 AND 12</t>
+          <t xml:space="preserve">    SUM(CASE WHEN TRY_CONVERT(int, src.[MONTH]) BETWEEN 1 AND 12</t>
         </is>
       </c>
     </row>
@@ -1809,210 +1748,204 @@
     <row r="33" ht="15" customHeight="1" s="42">
       <c r="B33" s="60" t="inlineStr">
         <is>
-          <t xml:space="preserve">                              WHERE d.DateKey = TRY_CONVERT(int, [YEAR])  * 10000</t>
+          <t xml:space="preserve">                              WHERE d.DateKey = TRY_CONVERT(int, src.[YEAR])  * 10000</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="42">
       <c r="B34" s="60" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                              + TRY_CONVERT(int, [MONTH]) * 100 + 1)</t>
+          <t xml:space="preserve">                                              + TRY_CONVERT(int, src.[MONTH]) * 100 + 1)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="42">
       <c r="B35" s="60" t="inlineStr">
         <is>
-          <t xml:space="preserve">             THEN 1 ELSE 0 END)                                AS DateOutsideDimDate</t>
+          <t xml:space="preserve">             THEN 1 ELSE 0 END)                                AS DateOutsideDimDate,</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="42">
+      <c r="A36" s="66" t="n"/>
       <c r="B36" s="60" t="inlineStr">
         <is>
-          <t>FROM stg.WarehouseRetailSales;</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="6" customHeight="1" s="42"/>
-    <row r="38" ht="32" customHeight="1" s="42">
-      <c r="A38" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B38" s="41" t="inlineStr">
-        <is>
-          <t>Compare the three counts with the difference from step 3. A row can appear in more than one column, so the columns may add up to more than the difference; what matters is that every dropped row falls under at least one reason.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="44" customHeight="1" s="42">
-      <c r="A39" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B39" s="41" t="inlineStr">
-        <is>
-          <t>Every dropped row is explained, and each reason is legitimate — a row with no item code cannot be attributed to an item: the check passes, with the explanation recorded. Any dropped row that none of the three reasons covers: the check fails. Go to Part E.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="32" customHeight="1" s="42">
-      <c r="B40" s="61" t="inlineStr">
-        <is>
-          <t>The criterion allows a gap only if it is explained. “Close enough” is not a result: a difference of 3 on 330,080 rows is 3 records nobody can account for.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="8" customHeight="1" s="42"/>
-    <row r="42" ht="22" customHeight="1" s="42">
-      <c r="A42" s="57" t="inlineStr">
-        <is>
-          <t>PART D — RECORD IT</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1" s="42">
-      <c r="A43" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B43" s="41" t="inlineStr">
-        <is>
-          <t>Get the reference for what was checked. In PowerShell, the current commit is:</t>
+          <t xml:space="preserve">    SUM(CASE WHEN NOT EXISTS (SELECT 1 FROM dw.DimSupplier AS s</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="42">
+      <c r="A37" s="66" t="n"/>
+      <c r="B37" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                              WHERE s.SupplierName = COALESCE(</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="42">
+      <c r="A38" s="66" t="n"/>
+      <c r="B38" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                    NULLIF(LTRIM(RTRIM(src.[SUPPLIER])), ''), 'Unknown Supplier'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="42">
+      <c r="A39" s="66" t="n"/>
+      <c r="B39" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             THEN 1 ELSE 0 END)                                AS SupplierNotInDimSupplier,</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="42">
+      <c r="A40" s="66" t="n"/>
+      <c r="B40" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SUM(CASE WHEN NULLIF(LTRIM(RTRIM(src.[ITEM CODE])), '') IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="42">
+      <c r="A41" s="66" t="n"/>
+      <c r="B41" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              AND NOT EXISTS (SELECT 1 FROM dw.DimItem AS i</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="42">
+      <c r="A42" s="66" t="n"/>
+      <c r="B42" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                              WHERE i.ItemCode = LTRIM(RTRIM(src.[ITEM CODE])))</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="42">
+      <c r="A43" s="66" t="n"/>
+      <c r="B43" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             THEN 1 ELSE 0 END)                                AS ItemNotInDimItem</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="42">
       <c r="B44" s="60" t="inlineStr">
         <is>
+          <t>FROM stg.WarehouseRetailSales AS src;</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="6" customHeight="1" s="42"/>
+    <row r="46" ht="29.5" customHeight="1" s="42">
+      <c r="A46" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B46" s="53" t="inlineStr">
+        <is>
+          <t>Compare the five counts with the difference from step 3. A row can appear in more than one column, so the columns may add up to more than the difference; what matters is that every dropped row falls under at least one reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="44" customHeight="1" s="42">
+      <c r="A47" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B47" s="53" t="inlineStr">
+        <is>
+          <t>Every dropped row is explained, and each reason is legitimate — a row with no item code cannot be attributed to an item: the check passes, with the explanation recorded. Any dropped row that none of the three reasons covers: the check fails. Go to Part E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1" s="42">
+      <c r="B48" s="61" t="inlineStr">
+        <is>
+          <t>The criterion allows a gap only if it is explained. “Close enough” is not a result: a difference of 3 on 330,080 rows is 3 records nobody can account for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="8" customHeight="1" s="42"/>
+    <row r="50" ht="22" customHeight="1" s="42">
+      <c r="A50" s="57" t="inlineStr">
+        <is>
+          <t>PART D — RECORD IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1" s="42">
+      <c r="A51" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B51" s="53" t="inlineStr">
+        <is>
+          <t>Get the reference for what was checked. In PowerShell, the current commit is:</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="42">
+      <c r="B52" s="60" t="inlineStr">
+        <is>
           <t>git -C X:\retail-sector-health log -1 --format=%h</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="6" customHeight="1" s="42"/>
-    <row r="46" ht="46" customHeight="1" s="42">
-      <c r="B46" s="59" t="inlineStr">
+    <row r="53" ht="6" customHeight="1" s="42"/>
+    <row r="54" ht="46" customHeight="1" s="42">
+      <c r="B54" s="59" t="inlineStr">
         <is>
           <t>Run Summary</t>
         </is>
       </c>
-      <c r="C46" s="41" t="inlineStr">
+      <c r="C54" s="41" t="inlineStr">
         <is>
           <t>Add the run if it is not there yet: Run ID (Run 1 for the initial build), Date, Trigger (Initial build — or Post fact-table reload for a later check), Model / commit reference (the hash from step 8), Run by. Leave everything from Checks recorded rightwards alone; those are formulas.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="32" customHeight="1" s="42">
-      <c r="B47" s="59" t="inlineStr">
+    <row r="55" ht="32" customHeight="1" s="42">
+      <c r="B55" s="59" t="inlineStr">
         <is>
           <t>Check Results</t>
         </is>
       </c>
-      <c r="C47" s="41" t="inlineStr">
+      <c r="C55" s="41" t="inlineStr">
         <is>
           <t>On the row for this Run ID and check 1: Result, Observed value / evidence, Checked by, Date checked. Leave Check, Pass criterion and Severity as they are.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="46" customHeight="1" s="42">
-      <c r="B48" s="58" t="inlineStr">
+    <row r="56" ht="46" customHeight="1" s="42">
+      <c r="B56" s="58" t="inlineStr">
         <is>
           <t>Observed value</t>
         </is>
       </c>
-      <c r="C48" s="41" t="inlineStr">
+      <c r="C56" s="41" t="inlineStr">
         <is>
           <t>Record numbers, not a verdict. For a pass with no gap: “Staged 330,080 · Loaded 330,080 · difference 0”. For a pass with an explained gap: “Staged [n] · Loaded [n] · [d] dropped — [d] blank ITEM CODE (diagnostic query, Worked Example step 5)”.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="32" customHeight="1" s="42">
-      <c r="B49" s="58" t="inlineStr">
+    <row r="57" ht="32" customHeight="1" s="42">
+      <c r="B57" s="58" t="inlineStr">
         <is>
           <t>Document 26</t>
         </is>
       </c>
-      <c r="C49" s="41" t="inlineStr">
+      <c r="C57" s="41" t="inlineStr">
         <is>
           <t>Tick the matching row on the Build Checklist: G1.05 at gate G1, and G5.01 at the model pass. Same result, same date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1" s="42">
-      <c r="A50" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B50" s="41" t="inlineStr">
-        <is>
-          <t>Check the Run Summary tab. Checks recorded goes up by one, and the Outcome updates on its own.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="8" customHeight="1" s="42"/>
-    <row r="52" ht="22" customHeight="1" s="42">
-      <c r="A52" s="57" t="inlineStr">
-        <is>
-          <t>PART E — IF IT FAILS</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="32" customHeight="1" s="42">
-      <c r="A53" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B53" s="41" t="inlineStr">
-        <is>
-          <t>On Check Results, record Fail with the numbers and the count of unexplained rows. Do not change it to N/A or clear it — a failure that was fixed is a better record than one that was erased.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="32" customHeight="1" s="42">
-      <c r="B54" s="59" t="inlineStr">
-        <is>
-          <t>Failure Log</t>
-        </is>
-      </c>
-      <c r="C54" s="41" t="inlineStr">
-        <is>
-          <t>Add a row: Failure ID (F-001), Run ID, Check # 1, What was observed (the counts), Root cause (what the diagnostic showed). Status reads Open.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="32" customHeight="1" s="42">
-      <c r="A55" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B55" s="41" t="inlineStr">
-        <is>
-          <t>Fix the cause where it started. A conversion problem is fixed in the cleansing of sql/04; then re-run sql/04, sql/05 and sql/06 in order — 06 because the lifecycle columns are built from the fact table and go stale when it changes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1" s="42">
-      <c r="A56" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B56" s="41" t="inlineStr">
-        <is>
-          <t>Fill in Fix applied, Fixed by and Date fixed on the Failure Log. Status changes to “Fix applied — not re-verified”.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="32" customHeight="1" s="42">
-      <c r="A57" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B57" s="41" t="inlineStr">
-        <is>
-          <t>Re-run Part B as a new run — Run 2 on the Run Summary, Trigger Ad hoc, naming the fix in Notes. Record check 1 against Run 2, and check 12 as well, since sql/06 was re-run.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" s="42">
       <c r="A58" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B58" s="41" t="inlineStr">
-        <is>
-          <t>When check 1 passes in Run 2, enter Run 2 in Re-verified in run on the Failure Log. Status changes to “Closed — re-verified”.</t>
+        <v>9</v>
+      </c>
+      <c r="B58" s="53" t="inlineStr">
+        <is>
+          <t>Check the Run Summary tab. Checks recorded goes up by one, and the Outcome updates on its own.</t>
         </is>
       </c>
     </row>
@@ -2020,110 +1953,188 @@
     <row r="60" ht="22" customHeight="1" s="42">
       <c r="A60" s="57" t="inlineStr">
         <is>
+          <t>PART E — IF IT FAILS</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1" s="42">
+      <c r="A61" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B61" s="53" t="inlineStr">
+        <is>
+          <t>On Check Results, record Fail with the numbers and the count of unexplained rows. Do not change it to N/A or clear it — a failure that was fixed is a better record than one that was erased.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1" s="42">
+      <c r="B62" s="59" t="inlineStr">
+        <is>
+          <t>Failure Log</t>
+        </is>
+      </c>
+      <c r="C62" s="41" t="inlineStr">
+        <is>
+          <t>Add a row: Failure ID (F-001), Run ID, Check # 1, What was observed (the counts), Root cause (what the diagnostic showed). Status reads Open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1" s="42">
+      <c r="A63" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B63" s="53" t="inlineStr">
+        <is>
+          <t>Fix the cause where it started. A conversion problem is fixed in the cleansing of sql/04; then re-run sql/04, sql/05 and sql/06 in order — 06 because the lifecycle columns are built from the fact table and go stale when it changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1" s="42">
+      <c r="A64" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B64" s="53" t="inlineStr">
+        <is>
+          <t>Fill in Fix applied, Fixed by and Date fixed on the Failure Log. Status changes to “Fix applied — not re-verified”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1" s="42">
+      <c r="A65" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B65" s="53" t="inlineStr">
+        <is>
+          <t>Re-run Part B as a new run — Run 2 on the Run Summary, Trigger Ad hoc, naming the fix in Notes. Record check 1 against Run 2, and check 12 as well, since sql/06 was re-run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1" s="42">
+      <c r="A66" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B66" s="53" t="inlineStr">
+        <is>
+          <t>When check 1 passes in Run 2, enter Run 2 in Re-verified in run on the Failure Log. Status changes to “Closed — re-verified”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="8" customHeight="1" s="42"/>
+    <row r="68" ht="22" customHeight="1" s="42">
+      <c r="A68" s="57" t="inlineStr">
+        <is>
           <t>THE SAME PARTS FOR ANY OTHER CHECK</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1" s="42">
-      <c r="B61" s="58" t="inlineStr">
+    <row r="69" ht="18" customHeight="1" s="42">
+      <c r="B69" s="58" t="inlineStr">
         <is>
           <t>A — Know it</t>
         </is>
       </c>
-      <c r="C61" s="41" t="inlineStr">
+      <c r="C69" s="41" t="inlineStr">
         <is>
           <t>Its row on the Check Catalog: criterion, what it protects, where it runs, severity.</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1" s="42">
-      <c r="B62" s="58" t="inlineStr">
+    <row r="70" ht="18" customHeight="1" s="42">
+      <c r="B70" s="58" t="inlineStr">
         <is>
           <t>B — Run it</t>
         </is>
       </c>
-      <c r="C62" s="41" t="inlineStr">
+      <c r="C70" s="41" t="inlineStr">
         <is>
           <t>The query or visual on the Check Catalog row. Paste-ready SQL and DAX for most checks are in document 25 §3.</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="32" customHeight="1" s="42">
-      <c r="B63" s="58" t="inlineStr">
+    <row r="71" ht="32" customHeight="1" s="42">
+      <c r="B71" s="58" t="inlineStr">
         <is>
           <t>C — Decide</t>
         </is>
       </c>
-      <c r="C63" s="41" t="inlineStr">
+      <c r="C71" s="41" t="inlineStr">
         <is>
           <t>Against the pass criterion only. If the criterion allows an explained exception, find the explanation before deciding.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1" s="42">
-      <c r="B64" s="58" t="inlineStr">
+    <row r="72" ht="18" customHeight="1" s="42">
+      <c r="B72" s="58" t="inlineStr">
         <is>
           <t>D — Record it</t>
         </is>
       </c>
-      <c r="C64" s="41" t="inlineStr">
+      <c r="C72" s="41" t="inlineStr">
         <is>
           <t>Run Summary for the run, Check Results for the result and the numbers, document 26 for the gate row.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="18" customHeight="1" s="42">
-      <c r="B65" s="58" t="inlineStr">
+    <row r="73" ht="18" customHeight="1" s="42">
+      <c r="B73" s="58" t="inlineStr">
         <is>
           <t>E — If it fails</t>
         </is>
       </c>
-      <c r="C65" s="41" t="inlineStr">
+      <c r="C73" s="41" t="inlineStr">
         <is>
           <t>Failure Log, fix at the source, re-run as a new run, close the failure when a later run passes.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="47">
+    <mergeCell ref="B47:C47"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B46:C46"/>
     <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B66:C66"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A50:C50"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B56:C56"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B58:C58"/>
     <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B42:C42"/>
     <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B61:C61"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="A52:C52"/>
     <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A68:C68"/>
     <mergeCell ref="A13:C13"/>
-    <mergeCell ref="B44:C44"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B65:C65"/>
     <mergeCell ref="A60:C60"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B64:C64"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B51:C51"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B63:C63"/>
     <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B35:C35"/>
   </mergeCells>
   <hyperlinks>
@@ -2137,7 +2148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2279,7 +2290,7 @@
         <v/>
       </c>
       <c r="L5" s="15">
-        <f>IF($A5="","",IF($J5&gt;0,"BLOCKED",IF($H5&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F5&lt;17,"INCOMPLETE — "&amp;(17-$F5)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A5="","",IF($J5&gt;0,"BLOCKED",IF($F5&lt;17,"INCOMPLETE — "&amp;(17-$F5)&amp;" not recorded"&amp;IF($H5&gt;0," · "&amp;$H5&amp;" Advisory failing",""),IF($H5&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M5" s="16" t="n"/>
@@ -2315,7 +2326,7 @@
         <v/>
       </c>
       <c r="L6" s="23">
-        <f>IF($A6="","",IF($J6&gt;0,"BLOCKED",IF($H6&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F6&lt;17,"INCOMPLETE — "&amp;(17-$F6)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A6="","",IF($J6&gt;0,"BLOCKED",IF($F6&lt;17,"INCOMPLETE — "&amp;(17-$F6)&amp;" not recorded"&amp;IF($H6&gt;0," · "&amp;$H6&amp;" Advisory failing",""),IF($H6&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M6" s="24" t="n"/>
@@ -2351,7 +2362,7 @@
         <v/>
       </c>
       <c r="L7" s="15">
-        <f>IF($A7="","",IF($J7&gt;0,"BLOCKED",IF($H7&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F7&lt;17,"INCOMPLETE — "&amp;(17-$F7)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A7="","",IF($J7&gt;0,"BLOCKED",IF($F7&lt;17,"INCOMPLETE — "&amp;(17-$F7)&amp;" not recorded"&amp;IF($H7&gt;0," · "&amp;$H7&amp;" Advisory failing",""),IF($H7&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M7" s="16" t="n"/>
@@ -2387,7 +2398,7 @@
         <v/>
       </c>
       <c r="L8" s="23">
-        <f>IF($A8="","",IF($J8&gt;0,"BLOCKED",IF($H8&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F8&lt;17,"INCOMPLETE — "&amp;(17-$F8)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A8="","",IF($J8&gt;0,"BLOCKED",IF($F8&lt;17,"INCOMPLETE — "&amp;(17-$F8)&amp;" not recorded"&amp;IF($H8&gt;0," · "&amp;$H8&amp;" Advisory failing",""),IF($H8&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M8" s="24" t="n"/>
@@ -2423,7 +2434,7 @@
         <v/>
       </c>
       <c r="L9" s="15">
-        <f>IF($A9="","",IF($J9&gt;0,"BLOCKED",IF($H9&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F9&lt;17,"INCOMPLETE — "&amp;(17-$F9)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A9="","",IF($J9&gt;0,"BLOCKED",IF($F9&lt;17,"INCOMPLETE — "&amp;(17-$F9)&amp;" not recorded"&amp;IF($H9&gt;0," · "&amp;$H9&amp;" Advisory failing",""),IF($H9&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M9" s="16" t="n"/>
@@ -2459,7 +2470,7 @@
         <v/>
       </c>
       <c r="L10" s="23">
-        <f>IF($A10="","",IF($J10&gt;0,"BLOCKED",IF($H10&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F10&lt;17,"INCOMPLETE — "&amp;(17-$F10)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A10="","",IF($J10&gt;0,"BLOCKED",IF($F10&lt;17,"INCOMPLETE — "&amp;(17-$F10)&amp;" not recorded"&amp;IF($H10&gt;0," · "&amp;$H10&amp;" Advisory failing",""),IF($H10&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M10" s="24" t="n"/>
@@ -2495,7 +2506,7 @@
         <v/>
       </c>
       <c r="L11" s="15">
-        <f>IF($A11="","",IF($J11&gt;0,"BLOCKED",IF($H11&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F11&lt;17,"INCOMPLETE — "&amp;(17-$F11)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A11="","",IF($J11&gt;0,"BLOCKED",IF($F11&lt;17,"INCOMPLETE — "&amp;(17-$F11)&amp;" not recorded"&amp;IF($H11&gt;0," · "&amp;$H11&amp;" Advisory failing",""),IF($H11&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M11" s="16" t="n"/>
@@ -2531,7 +2542,7 @@
         <v/>
       </c>
       <c r="L12" s="23">
-        <f>IF($A12="","",IF($J12&gt;0,"BLOCKED",IF($H12&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F12&lt;17,"INCOMPLETE — "&amp;(17-$F12)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A12="","",IF($J12&gt;0,"BLOCKED",IF($F12&lt;17,"INCOMPLETE — "&amp;(17-$F12)&amp;" not recorded"&amp;IF($H12&gt;0," · "&amp;$H12&amp;" Advisory failing",""),IF($H12&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M12" s="24" t="n"/>
@@ -2567,7 +2578,7 @@
         <v/>
       </c>
       <c r="L13" s="15">
-        <f>IF($A13="","",IF($J13&gt;0,"BLOCKED",IF($H13&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F13&lt;17,"INCOMPLETE — "&amp;(17-$F13)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A13="","",IF($J13&gt;0,"BLOCKED",IF($F13&lt;17,"INCOMPLETE — "&amp;(17-$F13)&amp;" not recorded"&amp;IF($H13&gt;0," · "&amp;$H13&amp;" Advisory failing",""),IF($H13&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M13" s="16" t="n"/>
@@ -2603,7 +2614,7 @@
         <v/>
       </c>
       <c r="L14" s="23">
-        <f>IF($A14="","",IF($J14&gt;0,"BLOCKED",IF($H14&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F14&lt;17,"INCOMPLETE — "&amp;(17-$F14)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A14="","",IF($J14&gt;0,"BLOCKED",IF($F14&lt;17,"INCOMPLETE — "&amp;(17-$F14)&amp;" not recorded"&amp;IF($H14&gt;0," · "&amp;$H14&amp;" Advisory failing",""),IF($H14&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M14" s="24" t="n"/>
@@ -2639,7 +2650,7 @@
         <v/>
       </c>
       <c r="L15" s="15">
-        <f>IF($A15="","",IF($J15&gt;0,"BLOCKED",IF($H15&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F15&lt;17,"INCOMPLETE — "&amp;(17-$F15)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A15="","",IF($J15&gt;0,"BLOCKED",IF($F15&lt;17,"INCOMPLETE — "&amp;(17-$F15)&amp;" not recorded"&amp;IF($H15&gt;0," · "&amp;$H15&amp;" Advisory failing",""),IF($H15&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M15" s="16" t="n"/>
@@ -2675,7 +2686,7 @@
         <v/>
       </c>
       <c r="L16" s="23">
-        <f>IF($A16="","",IF($J16&gt;0,"BLOCKED",IF($H16&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F16&lt;17,"INCOMPLETE — "&amp;(17-$F16)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A16="","",IF($J16&gt;0,"BLOCKED",IF($F16&lt;17,"INCOMPLETE — "&amp;(17-$F16)&amp;" not recorded"&amp;IF($H16&gt;0," · "&amp;$H16&amp;" Advisory failing",""),IF($H16&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M16" s="24" t="n"/>
@@ -2711,7 +2722,7 @@
         <v/>
       </c>
       <c r="L17" s="15">
-        <f>IF($A17="","",IF($J17&gt;0,"BLOCKED",IF($H17&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F17&lt;17,"INCOMPLETE — "&amp;(17-$F17)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A17="","",IF($J17&gt;0,"BLOCKED",IF($F17&lt;17,"INCOMPLETE — "&amp;(17-$F17)&amp;" not recorded"&amp;IF($H17&gt;0," · "&amp;$H17&amp;" Advisory failing",""),IF($H17&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M17" s="16" t="n"/>
@@ -2747,7 +2758,7 @@
         <v/>
       </c>
       <c r="L18" s="23">
-        <f>IF($A18="","",IF($J18&gt;0,"BLOCKED",IF($H18&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F18&lt;17,"INCOMPLETE — "&amp;(17-$F18)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A18="","",IF($J18&gt;0,"BLOCKED",IF($F18&lt;17,"INCOMPLETE — "&amp;(17-$F18)&amp;" not recorded"&amp;IF($H18&gt;0," · "&amp;$H18&amp;" Advisory failing",""),IF($H18&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M18" s="24" t="n"/>
@@ -2783,7 +2794,7 @@
         <v/>
       </c>
       <c r="L19" s="15">
-        <f>IF($A19="","",IF($J19&gt;0,"BLOCKED",IF($H19&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F19&lt;17,"INCOMPLETE — "&amp;(17-$F19)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A19="","",IF($J19&gt;0,"BLOCKED",IF($F19&lt;17,"INCOMPLETE — "&amp;(17-$F19)&amp;" not recorded"&amp;IF($H19&gt;0," · "&amp;$H19&amp;" Advisory failing",""),IF($H19&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M19" s="16" t="n"/>
@@ -2819,7 +2830,7 @@
         <v/>
       </c>
       <c r="L20" s="23">
-        <f>IF($A20="","",IF($J20&gt;0,"BLOCKED",IF($H20&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F20&lt;17,"INCOMPLETE — "&amp;(17-$F20)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A20="","",IF($J20&gt;0,"BLOCKED",IF($F20&lt;17,"INCOMPLETE — "&amp;(17-$F20)&amp;" not recorded"&amp;IF($H20&gt;0," · "&amp;$H20&amp;" Advisory failing",""),IF($H20&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M20" s="24" t="n"/>
@@ -2855,7 +2866,7 @@
         <v/>
       </c>
       <c r="L21" s="15">
-        <f>IF($A21="","",IF($J21&gt;0,"BLOCKED",IF($H21&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F21&lt;17,"INCOMPLETE — "&amp;(17-$F21)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A21="","",IF($J21&gt;0,"BLOCKED",IF($F21&lt;17,"INCOMPLETE — "&amp;(17-$F21)&amp;" not recorded"&amp;IF($H21&gt;0," · "&amp;$H21&amp;" Advisory failing",""),IF($H21&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M21" s="16" t="n"/>
@@ -2891,7 +2902,7 @@
         <v/>
       </c>
       <c r="L22" s="23">
-        <f>IF($A22="","",IF($J22&gt;0,"BLOCKED",IF($H22&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F22&lt;17,"INCOMPLETE — "&amp;(17-$F22)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A22="","",IF($J22&gt;0,"BLOCKED",IF($F22&lt;17,"INCOMPLETE — "&amp;(17-$F22)&amp;" not recorded"&amp;IF($H22&gt;0," · "&amp;$H22&amp;" Advisory failing",""),IF($H22&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M22" s="24" t="n"/>
@@ -2927,7 +2938,7 @@
         <v/>
       </c>
       <c r="L23" s="15">
-        <f>IF($A23="","",IF($J23&gt;0,"BLOCKED",IF($H23&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F23&lt;17,"INCOMPLETE — "&amp;(17-$F23)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A23="","",IF($J23&gt;0,"BLOCKED",IF($F23&lt;17,"INCOMPLETE — "&amp;(17-$F23)&amp;" not recorded"&amp;IF($H23&gt;0," · "&amp;$H23&amp;" Advisory failing",""),IF($H23&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M23" s="16" t="n"/>
@@ -2963,7 +2974,7 @@
         <v/>
       </c>
       <c r="L24" s="23">
-        <f>IF($A24="","",IF($J24&gt;0,"BLOCKED",IF($H24&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F24&lt;17,"INCOMPLETE — "&amp;(17-$F24)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A24="","",IF($J24&gt;0,"BLOCKED",IF($F24&lt;17,"INCOMPLETE — "&amp;(17-$F24)&amp;" not recorded"&amp;IF($H24&gt;0," · "&amp;$H24&amp;" Advisory failing",""),IF($H24&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M24" s="24" t="n"/>
@@ -2999,7 +3010,7 @@
         <v/>
       </c>
       <c r="L25" s="15">
-        <f>IF($A25="","",IF($J25&gt;0,"BLOCKED",IF($H25&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F25&lt;17,"INCOMPLETE — "&amp;(17-$F25)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A25="","",IF($J25&gt;0,"BLOCKED",IF($F25&lt;17,"INCOMPLETE — "&amp;(17-$F25)&amp;" not recorded"&amp;IF($H25&gt;0," · "&amp;$H25&amp;" Advisory failing",""),IF($H25&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M25" s="16" t="n"/>
@@ -3035,7 +3046,7 @@
         <v/>
       </c>
       <c r="L26" s="23">
-        <f>IF($A26="","",IF($J26&gt;0,"BLOCKED",IF($H26&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F26&lt;17,"INCOMPLETE — "&amp;(17-$F26)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A26="","",IF($J26&gt;0,"BLOCKED",IF($F26&lt;17,"INCOMPLETE — "&amp;(17-$F26)&amp;" not recorded"&amp;IF($H26&gt;0," · "&amp;$H26&amp;" Advisory failing",""),IF($H26&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M26" s="24" t="n"/>
@@ -3071,7 +3082,7 @@
         <v/>
       </c>
       <c r="L27" s="15">
-        <f>IF($A27="","",IF($J27&gt;0,"BLOCKED",IF($H27&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F27&lt;17,"INCOMPLETE — "&amp;(17-$F27)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A27="","",IF($J27&gt;0,"BLOCKED",IF($F27&lt;17,"INCOMPLETE — "&amp;(17-$F27)&amp;" not recorded"&amp;IF($H27&gt;0," · "&amp;$H27&amp;" Advisory failing",""),IF($H27&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M27" s="16" t="n"/>
@@ -3107,7 +3118,7 @@
         <v/>
       </c>
       <c r="L28" s="23">
-        <f>IF($A28="","",IF($J28&gt;0,"BLOCKED",IF($H28&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F28&lt;17,"INCOMPLETE — "&amp;(17-$F28)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A28="","",IF($J28&gt;0,"BLOCKED",IF($F28&lt;17,"INCOMPLETE — "&amp;(17-$F28)&amp;" not recorded"&amp;IF($H28&gt;0," · "&amp;$H28&amp;" Advisory failing",""),IF($H28&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M28" s="24" t="n"/>
@@ -3143,7 +3154,7 @@
         <v/>
       </c>
       <c r="L29" s="15">
-        <f>IF($A29="","",IF($J29&gt;0,"BLOCKED",IF($H29&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F29&lt;17,"INCOMPLETE — "&amp;(17-$F29)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A29="","",IF($J29&gt;0,"BLOCKED",IF($F29&lt;17,"INCOMPLETE — "&amp;(17-$F29)&amp;" not recorded"&amp;IF($H29&gt;0," · "&amp;$H29&amp;" Advisory failing",""),IF($H29&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M29" s="16" t="n"/>
@@ -3179,7 +3190,7 @@
         <v/>
       </c>
       <c r="L30" s="23">
-        <f>IF($A30="","",IF($J30&gt;0,"BLOCKED",IF($H30&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F30&lt;17,"INCOMPLETE — "&amp;(17-$F30)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A30="","",IF($J30&gt;0,"BLOCKED",IF($F30&lt;17,"INCOMPLETE — "&amp;(17-$F30)&amp;" not recorded"&amp;IF($H30&gt;0," · "&amp;$H30&amp;" Advisory failing",""),IF($H30&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M30" s="24" t="n"/>
@@ -3215,7 +3226,7 @@
         <v/>
       </c>
       <c r="L31" s="15">
-        <f>IF($A31="","",IF($J31&gt;0,"BLOCKED",IF($H31&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F31&lt;17,"INCOMPLETE — "&amp;(17-$F31)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A31="","",IF($J31&gt;0,"BLOCKED",IF($F31&lt;17,"INCOMPLETE — "&amp;(17-$F31)&amp;" not recorded"&amp;IF($H31&gt;0," · "&amp;$H31&amp;" Advisory failing",""),IF($H31&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M31" s="16" t="n"/>
@@ -3251,7 +3262,7 @@
         <v/>
       </c>
       <c r="L32" s="23">
-        <f>IF($A32="","",IF($J32&gt;0,"BLOCKED",IF($H32&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F32&lt;17,"INCOMPLETE — "&amp;(17-$F32)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A32="","",IF($J32&gt;0,"BLOCKED",IF($F32&lt;17,"INCOMPLETE — "&amp;(17-$F32)&amp;" not recorded"&amp;IF($H32&gt;0," · "&amp;$H32&amp;" Advisory failing",""),IF($H32&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M32" s="24" t="n"/>
@@ -3287,7 +3298,7 @@
         <v/>
       </c>
       <c r="L33" s="15">
-        <f>IF($A33="","",IF($J33&gt;0,"BLOCKED",IF($H33&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F33&lt;17,"INCOMPLETE — "&amp;(17-$F33)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A33="","",IF($J33&gt;0,"BLOCKED",IF($F33&lt;17,"INCOMPLETE — "&amp;(17-$F33)&amp;" not recorded"&amp;IF($H33&gt;0," · "&amp;$H33&amp;" Advisory failing",""),IF($H33&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M33" s="16" t="n"/>
@@ -3323,7 +3334,7 @@
         <v/>
       </c>
       <c r="L34" s="23">
-        <f>IF($A34="","",IF($J34&gt;0,"BLOCKED",IF($H34&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F34&lt;17,"INCOMPLETE — "&amp;(17-$F34)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A34="","",IF($J34&gt;0,"BLOCKED",IF($F34&lt;17,"INCOMPLETE — "&amp;(17-$F34)&amp;" not recorded"&amp;IF($H34&gt;0," · "&amp;$H34&amp;" Advisory failing",""),IF($H34&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M34" s="24" t="n"/>
@@ -3359,7 +3370,7 @@
         <v/>
       </c>
       <c r="L35" s="15">
-        <f>IF($A35="","",IF($J35&gt;0,"BLOCKED",IF($H35&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F35&lt;17,"INCOMPLETE — "&amp;(17-$F35)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A35="","",IF($J35&gt;0,"BLOCKED",IF($F35&lt;17,"INCOMPLETE — "&amp;(17-$F35)&amp;" not recorded"&amp;IF($H35&gt;0," · "&amp;$H35&amp;" Advisory failing",""),IF($H35&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M35" s="16" t="n"/>
@@ -3395,7 +3406,7 @@
         <v/>
       </c>
       <c r="L36" s="23">
-        <f>IF($A36="","",IF($J36&gt;0,"BLOCKED",IF($H36&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F36&lt;17,"INCOMPLETE — "&amp;(17-$F36)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A36="","",IF($J36&gt;0,"BLOCKED",IF($F36&lt;17,"INCOMPLETE — "&amp;(17-$F36)&amp;" not recorded"&amp;IF($H36&gt;0," · "&amp;$H36&amp;" Advisory failing",""),IF($H36&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M36" s="24" t="n"/>
@@ -3431,7 +3442,7 @@
         <v/>
       </c>
       <c r="L37" s="15">
-        <f>IF($A37="","",IF($J37&gt;0,"BLOCKED",IF($H37&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F37&lt;17,"INCOMPLETE — "&amp;(17-$F37)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A37="","",IF($J37&gt;0,"BLOCKED",IF($F37&lt;17,"INCOMPLETE — "&amp;(17-$F37)&amp;" not recorded"&amp;IF($H37&gt;0," · "&amp;$H37&amp;" Advisory failing",""),IF($H37&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M37" s="16" t="n"/>
@@ -3467,7 +3478,7 @@
         <v/>
       </c>
       <c r="L38" s="23">
-        <f>IF($A38="","",IF($J38&gt;0,"BLOCKED",IF($H38&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F38&lt;17,"INCOMPLETE — "&amp;(17-$F38)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A38="","",IF($J38&gt;0,"BLOCKED",IF($F38&lt;17,"INCOMPLETE — "&amp;(17-$F38)&amp;" not recorded"&amp;IF($H38&gt;0," · "&amp;$H38&amp;" Advisory failing",""),IF($H38&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M38" s="24" t="n"/>
@@ -3503,7 +3514,7 @@
         <v/>
       </c>
       <c r="L39" s="15">
-        <f>IF($A39="","",IF($J39&gt;0,"BLOCKED",IF($H39&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F39&lt;17,"INCOMPLETE — "&amp;(17-$F39)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A39="","",IF($J39&gt;0,"BLOCKED",IF($F39&lt;17,"INCOMPLETE — "&amp;(17-$F39)&amp;" not recorded"&amp;IF($H39&gt;0," · "&amp;$H39&amp;" Advisory failing",""),IF($H39&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M39" s="16" t="n"/>
@@ -3539,7 +3550,7 @@
         <v/>
       </c>
       <c r="L40" s="23">
-        <f>IF($A40="","",IF($J40&gt;0,"BLOCKED",IF($H40&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F40&lt;17,"INCOMPLETE — "&amp;(17-$F40)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A40="","",IF($J40&gt;0,"BLOCKED",IF($F40&lt;17,"INCOMPLETE — "&amp;(17-$F40)&amp;" not recorded"&amp;IF($H40&gt;0," · "&amp;$H40&amp;" Advisory failing",""),IF($H40&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M40" s="24" t="n"/>
@@ -3575,7 +3586,7 @@
         <v/>
       </c>
       <c r="L41" s="15">
-        <f>IF($A41="","",IF($J41&gt;0,"BLOCKED",IF($H41&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F41&lt;17,"INCOMPLETE — "&amp;(17-$F41)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A41="","",IF($J41&gt;0,"BLOCKED",IF($F41&lt;17,"INCOMPLETE — "&amp;(17-$F41)&amp;" not recorded"&amp;IF($H41&gt;0," · "&amp;$H41&amp;" Advisory failing",""),IF($H41&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M41" s="16" t="n"/>
@@ -3611,7 +3622,7 @@
         <v/>
       </c>
       <c r="L42" s="23">
-        <f>IF($A42="","",IF($J42&gt;0,"BLOCKED",IF($H42&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F42&lt;17,"INCOMPLETE — "&amp;(17-$F42)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A42="","",IF($J42&gt;0,"BLOCKED",IF($F42&lt;17,"INCOMPLETE — "&amp;(17-$F42)&amp;" not recorded"&amp;IF($H42&gt;0," · "&amp;$H42&amp;" Advisory failing",""),IF($H42&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M42" s="24" t="n"/>
@@ -3647,7 +3658,7 @@
         <v/>
       </c>
       <c r="L43" s="15">
-        <f>IF($A43="","",IF($J43&gt;0,"BLOCKED",IF($H43&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F43&lt;17,"INCOMPLETE — "&amp;(17-$F43)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A43="","",IF($J43&gt;0,"BLOCKED",IF($F43&lt;17,"INCOMPLETE — "&amp;(17-$F43)&amp;" not recorded"&amp;IF($H43&gt;0," · "&amp;$H43&amp;" Advisory failing",""),IF($H43&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M43" s="16" t="n"/>
@@ -3683,7 +3694,7 @@
         <v/>
       </c>
       <c r="L44" s="23">
-        <f>IF($A44="","",IF($J44&gt;0,"BLOCKED",IF($H44&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F44&lt;17,"INCOMPLETE — "&amp;(17-$F44)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A44="","",IF($J44&gt;0,"BLOCKED",IF($F44&lt;17,"INCOMPLETE — "&amp;(17-$F44)&amp;" not recorded"&amp;IF($H44&gt;0," · "&amp;$H44&amp;" Advisory failing",""),IF($H44&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M44" s="24" t="n"/>
@@ -3719,7 +3730,7 @@
         <v/>
       </c>
       <c r="L45" s="15">
-        <f>IF($A45="","",IF($J45&gt;0,"BLOCKED",IF($H45&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F45&lt;17,"INCOMPLETE — "&amp;(17-$F45)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A45="","",IF($J45&gt;0,"BLOCKED",IF($F45&lt;17,"INCOMPLETE — "&amp;(17-$F45)&amp;" not recorded"&amp;IF($H45&gt;0," · "&amp;$H45&amp;" Advisory failing",""),IF($H45&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M45" s="16" t="n"/>
@@ -3755,7 +3766,7 @@
         <v/>
       </c>
       <c r="L46" s="23">
-        <f>IF($A46="","",IF($J46&gt;0,"BLOCKED",IF($H46&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F46&lt;17,"INCOMPLETE — "&amp;(17-$F46)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A46="","",IF($J46&gt;0,"BLOCKED",IF($F46&lt;17,"INCOMPLETE — "&amp;(17-$F46)&amp;" not recorded"&amp;IF($H46&gt;0," · "&amp;$H46&amp;" Advisory failing",""),IF($H46&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M46" s="24" t="n"/>
@@ -3791,7 +3802,7 @@
         <v/>
       </c>
       <c r="L47" s="15">
-        <f>IF($A47="","",IF($J47&gt;0,"BLOCKED",IF($H47&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F47&lt;17,"INCOMPLETE — "&amp;(17-$F47)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A47="","",IF($J47&gt;0,"BLOCKED",IF($F47&lt;17,"INCOMPLETE — "&amp;(17-$F47)&amp;" not recorded"&amp;IF($H47&gt;0," · "&amp;$H47&amp;" Advisory failing",""),IF($H47&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M47" s="16" t="n"/>
@@ -3827,7 +3838,7 @@
         <v/>
       </c>
       <c r="L48" s="23">
-        <f>IF($A48="","",IF($J48&gt;0,"BLOCKED",IF($H48&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F48&lt;17,"INCOMPLETE — "&amp;(17-$F48)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A48="","",IF($J48&gt;0,"BLOCKED",IF($F48&lt;17,"INCOMPLETE — "&amp;(17-$F48)&amp;" not recorded"&amp;IF($H48&gt;0," · "&amp;$H48&amp;" Advisory failing",""),IF($H48&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M48" s="24" t="n"/>
@@ -3863,7 +3874,7 @@
         <v/>
       </c>
       <c r="L49" s="15">
-        <f>IF($A49="","",IF($J49&gt;0,"BLOCKED",IF($H49&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F49&lt;17,"INCOMPLETE — "&amp;(17-$F49)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A49="","",IF($J49&gt;0,"BLOCKED",IF($F49&lt;17,"INCOMPLETE — "&amp;(17-$F49)&amp;" not recorded"&amp;IF($H49&gt;0," · "&amp;$H49&amp;" Advisory failing",""),IF($H49&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M49" s="16" t="n"/>
@@ -3899,7 +3910,7 @@
         <v/>
       </c>
       <c r="L50" s="23">
-        <f>IF($A50="","",IF($J50&gt;0,"BLOCKED",IF($H50&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F50&lt;17,"INCOMPLETE — "&amp;(17-$F50)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A50="","",IF($J50&gt;0,"BLOCKED",IF($F50&lt;17,"INCOMPLETE — "&amp;(17-$F50)&amp;" not recorded"&amp;IF($H50&gt;0," · "&amp;$H50&amp;" Advisory failing",""),IF($H50&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M50" s="24" t="n"/>
@@ -3935,7 +3946,7 @@
         <v/>
       </c>
       <c r="L51" s="15">
-        <f>IF($A51="","",IF($J51&gt;0,"BLOCKED",IF($H51&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F51&lt;17,"INCOMPLETE — "&amp;(17-$F51)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A51="","",IF($J51&gt;0,"BLOCKED",IF($F51&lt;17,"INCOMPLETE — "&amp;(17-$F51)&amp;" not recorded"&amp;IF($H51&gt;0," · "&amp;$H51&amp;" Advisory failing",""),IF($H51&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M51" s="16" t="n"/>
@@ -3971,7 +3982,7 @@
         <v/>
       </c>
       <c r="L52" s="23">
-        <f>IF($A52="","",IF($J52&gt;0,"BLOCKED",IF($H52&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F52&lt;17,"INCOMPLETE — "&amp;(17-$F52)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A52="","",IF($J52&gt;0,"BLOCKED",IF($F52&lt;17,"INCOMPLETE — "&amp;(17-$F52)&amp;" not recorded"&amp;IF($H52&gt;0," · "&amp;$H52&amp;" Advisory failing",""),IF($H52&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M52" s="24" t="n"/>
@@ -4007,7 +4018,7 @@
         <v/>
       </c>
       <c r="L53" s="15">
-        <f>IF($A53="","",IF($J53&gt;0,"BLOCKED",IF($H53&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F53&lt;17,"INCOMPLETE — "&amp;(17-$F53)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A53="","",IF($J53&gt;0,"BLOCKED",IF($F53&lt;17,"INCOMPLETE — "&amp;(17-$F53)&amp;" not recorded"&amp;IF($H53&gt;0," · "&amp;$H53&amp;" Advisory failing",""),IF($H53&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M53" s="16" t="n"/>
@@ -4043,7 +4054,7 @@
         <v/>
       </c>
       <c r="L54" s="23">
-        <f>IF($A54="","",IF($J54&gt;0,"BLOCKED",IF($H54&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F54&lt;17,"INCOMPLETE — "&amp;(17-$F54)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A54="","",IF($J54&gt;0,"BLOCKED",IF($F54&lt;17,"INCOMPLETE — "&amp;(17-$F54)&amp;" not recorded"&amp;IF($H54&gt;0," · "&amp;$H54&amp;" Advisory failing",""),IF($H54&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M54" s="24" t="n"/>
@@ -4079,7 +4090,7 @@
         <v/>
       </c>
       <c r="L55" s="15">
-        <f>IF($A55="","",IF($J55&gt;0,"BLOCKED",IF($H55&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F55&lt;17,"INCOMPLETE — "&amp;(17-$F55)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A55="","",IF($J55&gt;0,"BLOCKED",IF($F55&lt;17,"INCOMPLETE — "&amp;(17-$F55)&amp;" not recorded"&amp;IF($H55&gt;0," · "&amp;$H55&amp;" Advisory failing",""),IF($H55&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M55" s="16" t="n"/>
@@ -4115,7 +4126,7 @@
         <v/>
       </c>
       <c r="L56" s="23">
-        <f>IF($A56="","",IF($J56&gt;0,"BLOCKED",IF($H56&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F56&lt;17,"INCOMPLETE — "&amp;(17-$F56)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A56="","",IF($J56&gt;0,"BLOCKED",IF($F56&lt;17,"INCOMPLETE — "&amp;(17-$F56)&amp;" not recorded"&amp;IF($H56&gt;0," · "&amp;$H56&amp;" Advisory failing",""),IF($H56&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M56" s="24" t="n"/>
@@ -4151,7 +4162,7 @@
         <v/>
       </c>
       <c r="L57" s="15">
-        <f>IF($A57="","",IF($J57&gt;0,"BLOCKED",IF($H57&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F57&lt;17,"INCOMPLETE — "&amp;(17-$F57)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A57="","",IF($J57&gt;0,"BLOCKED",IF($F57&lt;17,"INCOMPLETE — "&amp;(17-$F57)&amp;" not recorded"&amp;IF($H57&gt;0," · "&amp;$H57&amp;" Advisory failing",""),IF($H57&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M57" s="16" t="n"/>
@@ -4187,7 +4198,7 @@
         <v/>
       </c>
       <c r="L58" s="23">
-        <f>IF($A58="","",IF($J58&gt;0,"BLOCKED",IF($H58&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F58&lt;17,"INCOMPLETE — "&amp;(17-$F58)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A58="","",IF($J58&gt;0,"BLOCKED",IF($F58&lt;17,"INCOMPLETE — "&amp;(17-$F58)&amp;" not recorded"&amp;IF($H58&gt;0," · "&amp;$H58&amp;" Advisory failing",""),IF($H58&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M58" s="24" t="n"/>
@@ -4223,7 +4234,7 @@
         <v/>
       </c>
       <c r="L59" s="15">
-        <f>IF($A59="","",IF($J59&gt;0,"BLOCKED",IF($H59&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F59&lt;17,"INCOMPLETE — "&amp;(17-$F59)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A59="","",IF($J59&gt;0,"BLOCKED",IF($F59&lt;17,"INCOMPLETE — "&amp;(17-$F59)&amp;" not recorded"&amp;IF($H59&gt;0," · "&amp;$H59&amp;" Advisory failing",""),IF($H59&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M59" s="16" t="n"/>
@@ -4259,7 +4270,7 @@
         <v/>
       </c>
       <c r="L60" s="23">
-        <f>IF($A60="","",IF($J60&gt;0,"BLOCKED",IF($H60&gt;0,"PASSED WITH FAILURES — see Failure Log",IF($F60&lt;17,"INCOMPLETE — "&amp;(17-$F60)&amp;" not recorded","PASS"))))</f>
+        <f>IF($A60="","",IF($J60&gt;0,"BLOCKED",IF($F60&lt;17,"INCOMPLETE — "&amp;(17-$F60)&amp;" not recorded"&amp;IF($H60&gt;0," · "&amp;$H60&amp;" Advisory failing",""),IF($H60&gt;0,"PASSED WITH FAILURES — see Failure Log","PASS"))))</f>
         <v/>
       </c>
       <c r="M60" s="24" t="n"/>
@@ -4299,13 +4310,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J600"/>
+  <dimension ref="A1:K600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" style="42" min="1" max="1"/>
@@ -4313,9 +4324,12 @@
     <col width="26" customWidth="1" style="42" min="3" max="3"/>
     <col width="46" customWidth="1" style="42" min="4" max="4"/>
     <col width="11" customWidth="1" style="42" min="5" max="6"/>
+    <col width="13" customWidth="1" style="42" min="6" max="6"/>
     <col width="42" customWidth="1" style="42" min="7" max="7"/>
     <col width="13" customWidth="1" style="42" min="8" max="9"/>
+    <col width="13" customWidth="1" style="42" min="9" max="9"/>
     <col width="34" customWidth="1" style="42" min="10" max="10"/>
+    <col width="30" customWidth="1" style="42" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" s="42">
@@ -4325,10 +4339,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" s="42">
+    <row r="2" ht="29.5" customHeight="1" s="42">
       <c r="A2" s="63" t="inlineStr">
         <is>
-          <t>Fill in Result, Observed value and Date. Result drives every figure on the Run Summary tab. For a new run, copy the seventeen rows below, paste them underneath, change the Run ID and clear the results. Check, Pass criterion and Severity are quoted from document 02 §9 and the Check Catalog tab — do not reword them.</t>
+          <t>Fill in Result, Observed value and Date. Result drives every figure on the Run Summary tab. For a new run, copy the seventeen rows below, paste them underneath, change the Run ID and clear the results. Check, Pass criterion and Severity are quoted from document 02 §9 and the Check Catalog tab — do not reword them. For checks 7, 8, 15, 16 and 17, which are recorded at each report’s own report pass, keep Reports covered up to date; Result stays Not run until every report the check applies to is covered.</t>
         </is>
       </c>
     </row>
@@ -4381,6 +4395,11 @@
       <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>Reports covered</t>
         </is>
       </c>
     </row>
@@ -4417,6 +4436,7 @@
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="27" t="n"/>
       <c r="J5" s="16" t="n"/>
+      <c r="K5" s="16" t="n"/>
     </row>
     <row r="6" ht="42" customHeight="1" s="42">
       <c r="A6" s="17" t="inlineStr">
@@ -4451,6 +4471,7 @@
       <c r="H6" s="20" t="n"/>
       <c r="I6" s="30" t="n"/>
       <c r="J6" s="24" t="n"/>
+      <c r="K6" s="24" t="n"/>
     </row>
     <row r="7" ht="42" customHeight="1" s="42">
       <c r="A7" s="9" t="inlineStr">
@@ -4485,6 +4506,7 @@
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="27" t="n"/>
       <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
     </row>
     <row r="8" ht="42" customHeight="1" s="42">
       <c r="A8" s="17" t="inlineStr">
@@ -4519,6 +4541,7 @@
       <c r="H8" s="20" t="n"/>
       <c r="I8" s="30" t="n"/>
       <c r="J8" s="24" t="n"/>
+      <c r="K8" s="24" t="n"/>
     </row>
     <row r="9" ht="42" customHeight="1" s="42">
       <c r="A9" s="9" t="inlineStr">
@@ -4553,6 +4576,7 @@
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="27" t="n"/>
       <c r="J9" s="16" t="n"/>
+      <c r="K9" s="16" t="n"/>
     </row>
     <row r="10" ht="42" customHeight="1" s="42">
       <c r="A10" s="17" t="inlineStr">
@@ -4587,6 +4611,7 @@
       <c r="H10" s="20" t="n"/>
       <c r="I10" s="30" t="n"/>
       <c r="J10" s="24" t="n"/>
+      <c r="K10" s="24" t="n"/>
     </row>
     <row r="11" ht="42" customHeight="1" s="42">
       <c r="A11" s="9" t="inlineStr">
@@ -4621,6 +4646,11 @@
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="27" t="n"/>
       <c r="J11" s="16" t="n"/>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>R1: not run · R2: not run · R3: not run</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="42" customHeight="1" s="42">
       <c r="A12" s="17" t="inlineStr">
@@ -4655,6 +4685,11 @@
       <c r="H12" s="20" t="n"/>
       <c r="I12" s="30" t="n"/>
       <c r="J12" s="24" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>R1: not run · R2: not run · R3: not run</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="42" customHeight="1" s="42">
       <c r="A13" s="9" t="inlineStr">
@@ -4689,6 +4724,7 @@
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="27" t="n"/>
       <c r="J13" s="16" t="n"/>
+      <c r="K13" s="16" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1" s="42">
       <c r="A14" s="17" t="inlineStr">
@@ -4723,6 +4759,7 @@
       <c r="H14" s="20" t="n"/>
       <c r="I14" s="30" t="n"/>
       <c r="J14" s="24" t="n"/>
+      <c r="K14" s="24" t="n"/>
     </row>
     <row r="15" ht="42" customHeight="1" s="42">
       <c r="A15" s="9" t="inlineStr">
@@ -4757,6 +4794,7 @@
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="27" t="n"/>
       <c r="J15" s="16" t="n"/>
+      <c r="K15" s="16" t="n"/>
     </row>
     <row r="16" ht="42" customHeight="1" s="42">
       <c r="A16" s="17" t="inlineStr">
@@ -4791,6 +4829,7 @@
       <c r="H16" s="20" t="n"/>
       <c r="I16" s="30" t="n"/>
       <c r="J16" s="24" t="n"/>
+      <c r="K16" s="24" t="n"/>
     </row>
     <row r="17" ht="42" customHeight="1" s="42">
       <c r="A17" s="9" t="inlineStr">
@@ -4825,6 +4864,7 @@
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="27" t="n"/>
       <c r="J17" s="16" t="n"/>
+      <c r="K17" s="16" t="n"/>
     </row>
     <row r="18" ht="42" customHeight="1" s="42">
       <c r="A18" s="17" t="inlineStr">
@@ -4859,6 +4899,7 @@
       <c r="H18" s="20" t="n"/>
       <c r="I18" s="30" t="n"/>
       <c r="J18" s="24" t="n"/>
+      <c r="K18" s="24" t="n"/>
     </row>
     <row r="19" ht="42" customHeight="1" s="42">
       <c r="A19" s="9" t="inlineStr">
@@ -4893,6 +4934,11 @@
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="27" t="n"/>
       <c r="J19" s="16" t="n"/>
+      <c r="K19" s="16" t="inlineStr">
+        <is>
+          <t>R2: not run (only R2 has slopes)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="42" customHeight="1" s="42">
       <c r="A20" s="17" t="inlineStr">
@@ -4927,6 +4973,11 @@
       <c r="H20" s="20" t="n"/>
       <c r="I20" s="30" t="n"/>
       <c r="J20" s="24" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>R3: not run (only R3 has survival visuals)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="42" customHeight="1" s="42">
       <c r="A21" s="9" t="inlineStr">
@@ -4961,6 +5012,11 @@
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="27" t="n"/>
       <c r="J21" s="16" t="n"/>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>R1: not run · R2: not run · R3: not run</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1" s="42">
       <c r="A22" s="19" t="n"/>
@@ -4973,6 +5029,7 @@
       <c r="H22" s="19" t="n"/>
       <c r="I22" s="33" t="n"/>
       <c r="J22" s="19" t="n"/>
+      <c r="K22" s="19" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1" s="42">
       <c r="A23" s="11" t="n"/>
@@ -4985,6 +5042,7 @@
       <c r="H23" s="11" t="n"/>
       <c r="I23" s="34" t="n"/>
       <c r="J23" s="11" t="n"/>
+      <c r="K23" s="11" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1" s="42">
       <c r="A24" s="19" t="n"/>
@@ -4997,6 +5055,7 @@
       <c r="H24" s="19" t="n"/>
       <c r="I24" s="33" t="n"/>
       <c r="J24" s="19" t="n"/>
+      <c r="K24" s="19" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="42">
       <c r="A25" s="11" t="n"/>
@@ -5009,6 +5068,7 @@
       <c r="H25" s="11" t="n"/>
       <c r="I25" s="34" t="n"/>
       <c r="J25" s="11" t="n"/>
+      <c r="K25" s="11" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="42">
       <c r="A26" s="19" t="n"/>
@@ -5021,6 +5081,7 @@
       <c r="H26" s="19" t="n"/>
       <c r="I26" s="33" t="n"/>
       <c r="J26" s="19" t="n"/>
+      <c r="K26" s="19" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="42">
       <c r="A27" s="11" t="n"/>
@@ -5033,6 +5094,7 @@
       <c r="H27" s="11" t="n"/>
       <c r="I27" s="34" t="n"/>
       <c r="J27" s="11" t="n"/>
+      <c r="K27" s="11" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="42">
       <c r="A28" s="19" t="n"/>
@@ -5045,6 +5107,7 @@
       <c r="H28" s="19" t="n"/>
       <c r="I28" s="33" t="n"/>
       <c r="J28" s="19" t="n"/>
+      <c r="K28" s="19" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="42">
       <c r="A29" s="11" t="n"/>
@@ -5057,6 +5120,7 @@
       <c r="H29" s="11" t="n"/>
       <c r="I29" s="34" t="n"/>
       <c r="J29" s="11" t="n"/>
+      <c r="K29" s="11" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="42">
       <c r="A30" s="19" t="n"/>
@@ -5069,6 +5133,7 @@
       <c r="H30" s="19" t="n"/>
       <c r="I30" s="33" t="n"/>
       <c r="J30" s="19" t="n"/>
+      <c r="K30" s="19" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="42">
       <c r="A31" s="11" t="n"/>
@@ -5081,6 +5146,7 @@
       <c r="H31" s="11" t="n"/>
       <c r="I31" s="34" t="n"/>
       <c r="J31" s="11" t="n"/>
+      <c r="K31" s="11" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="42">
       <c r="A32" s="19" t="n"/>
@@ -5093,6 +5159,7 @@
       <c r="H32" s="19" t="n"/>
       <c r="I32" s="33" t="n"/>
       <c r="J32" s="19" t="n"/>
+      <c r="K32" s="19" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="42">
       <c r="A33" s="11" t="n"/>
@@ -5105,6 +5172,7 @@
       <c r="H33" s="11" t="n"/>
       <c r="I33" s="34" t="n"/>
       <c r="J33" s="11" t="n"/>
+      <c r="K33" s="11" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="42">
       <c r="A34" s="19" t="n"/>
@@ -5117,6 +5185,7 @@
       <c r="H34" s="19" t="n"/>
       <c r="I34" s="33" t="n"/>
       <c r="J34" s="19" t="n"/>
+      <c r="K34" s="19" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1" s="42">
       <c r="A35" s="11" t="n"/>
@@ -5129,6 +5198,7 @@
       <c r="H35" s="11" t="n"/>
       <c r="I35" s="34" t="n"/>
       <c r="J35" s="11" t="n"/>
+      <c r="K35" s="11" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1" s="42">
       <c r="A36" s="19" t="n"/>
@@ -5141,6 +5211,7 @@
       <c r="H36" s="19" t="n"/>
       <c r="I36" s="33" t="n"/>
       <c r="J36" s="19" t="n"/>
+      <c r="K36" s="19" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="42">
       <c r="A37" s="11" t="n"/>
@@ -5153,6 +5224,7 @@
       <c r="H37" s="11" t="n"/>
       <c r="I37" s="34" t="n"/>
       <c r="J37" s="11" t="n"/>
+      <c r="K37" s="11" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="42">
       <c r="A38" s="19" t="n"/>
@@ -5165,6 +5237,7 @@
       <c r="H38" s="19" t="n"/>
       <c r="I38" s="33" t="n"/>
       <c r="J38" s="19" t="n"/>
+      <c r="K38" s="19" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1" s="42">
       <c r="A39" s="11" t="n"/>
@@ -5177,6 +5250,7 @@
       <c r="H39" s="11" t="n"/>
       <c r="I39" s="34" t="n"/>
       <c r="J39" s="11" t="n"/>
+      <c r="K39" s="11" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1" s="42">
       <c r="A40" s="19" t="n"/>
@@ -5189,6 +5263,7 @@
       <c r="H40" s="19" t="n"/>
       <c r="I40" s="33" t="n"/>
       <c r="J40" s="19" t="n"/>
+      <c r="K40" s="19" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1" s="42">
       <c r="A41" s="11" t="n"/>
@@ -5201,6 +5276,7 @@
       <c r="H41" s="11" t="n"/>
       <c r="I41" s="34" t="n"/>
       <c r="J41" s="11" t="n"/>
+      <c r="K41" s="11" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1" s="42">
       <c r="A42" s="19" t="n"/>
@@ -5213,6 +5289,7 @@
       <c r="H42" s="19" t="n"/>
       <c r="I42" s="33" t="n"/>
       <c r="J42" s="19" t="n"/>
+      <c r="K42" s="19" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1" s="42">
       <c r="A43" s="11" t="n"/>
@@ -5225,6 +5302,7 @@
       <c r="H43" s="11" t="n"/>
       <c r="I43" s="34" t="n"/>
       <c r="J43" s="11" t="n"/>
+      <c r="K43" s="11" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1" s="42">
       <c r="A44" s="19" t="n"/>
@@ -5237,6 +5315,7 @@
       <c r="H44" s="19" t="n"/>
       <c r="I44" s="33" t="n"/>
       <c r="J44" s="19" t="n"/>
+      <c r="K44" s="19" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1" s="42">
       <c r="A45" s="11" t="n"/>
@@ -5249,6 +5328,7 @@
       <c r="H45" s="11" t="n"/>
       <c r="I45" s="34" t="n"/>
       <c r="J45" s="11" t="n"/>
+      <c r="K45" s="11" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1" s="42">
       <c r="A46" s="19" t="n"/>
@@ -5261,6 +5341,7 @@
       <c r="H46" s="19" t="n"/>
       <c r="I46" s="33" t="n"/>
       <c r="J46" s="19" t="n"/>
+      <c r="K46" s="19" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="42">
       <c r="A47" s="11" t="n"/>
@@ -5273,6 +5354,7 @@
       <c r="H47" s="11" t="n"/>
       <c r="I47" s="34" t="n"/>
       <c r="J47" s="11" t="n"/>
+      <c r="K47" s="11" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1" s="42">
       <c r="A48" s="19" t="n"/>
@@ -5285,6 +5367,7 @@
       <c r="H48" s="19" t="n"/>
       <c r="I48" s="33" t="n"/>
       <c r="J48" s="19" t="n"/>
+      <c r="K48" s="19" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1" s="42">
       <c r="A49" s="11" t="n"/>
@@ -5297,6 +5380,7 @@
       <c r="H49" s="11" t="n"/>
       <c r="I49" s="34" t="n"/>
       <c r="J49" s="11" t="n"/>
+      <c r="K49" s="11" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1" s="42">
       <c r="A50" s="19" t="n"/>
@@ -5309,6 +5393,7 @@
       <c r="H50" s="19" t="n"/>
       <c r="I50" s="33" t="n"/>
       <c r="J50" s="19" t="n"/>
+      <c r="K50" s="19" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1" s="42">
       <c r="A51" s="11" t="n"/>
@@ -5321,6 +5406,7 @@
       <c r="H51" s="11" t="n"/>
       <c r="I51" s="34" t="n"/>
       <c r="J51" s="11" t="n"/>
+      <c r="K51" s="11" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1" s="42">
       <c r="A52" s="19" t="n"/>
@@ -5333,6 +5419,7 @@
       <c r="H52" s="19" t="n"/>
       <c r="I52" s="33" t="n"/>
       <c r="J52" s="19" t="n"/>
+      <c r="K52" s="19" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1" s="42">
       <c r="A53" s="11" t="n"/>
@@ -5345,6 +5432,7 @@
       <c r="H53" s="11" t="n"/>
       <c r="I53" s="34" t="n"/>
       <c r="J53" s="11" t="n"/>
+      <c r="K53" s="11" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1" s="42">
       <c r="A54" s="19" t="n"/>
@@ -5357,6 +5445,7 @@
       <c r="H54" s="19" t="n"/>
       <c r="I54" s="33" t="n"/>
       <c r="J54" s="19" t="n"/>
+      <c r="K54" s="19" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1" s="42">
       <c r="A55" s="11" t="n"/>
@@ -5369,6 +5458,7 @@
       <c r="H55" s="11" t="n"/>
       <c r="I55" s="34" t="n"/>
       <c r="J55" s="11" t="n"/>
+      <c r="K55" s="11" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1" s="42">
       <c r="A56" s="19" t="n"/>
@@ -5381,6 +5471,7 @@
       <c r="H56" s="19" t="n"/>
       <c r="I56" s="33" t="n"/>
       <c r="J56" s="19" t="n"/>
+      <c r="K56" s="19" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1" s="42">
       <c r="A57" s="11" t="n"/>
@@ -5393,6 +5484,7 @@
       <c r="H57" s="11" t="n"/>
       <c r="I57" s="34" t="n"/>
       <c r="J57" s="11" t="n"/>
+      <c r="K57" s="11" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1" s="42">
       <c r="A58" s="19" t="n"/>
@@ -5405,6 +5497,7 @@
       <c r="H58" s="19" t="n"/>
       <c r="I58" s="33" t="n"/>
       <c r="J58" s="19" t="n"/>
+      <c r="K58" s="19" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1" s="42">
       <c r="A59" s="11" t="n"/>
@@ -5417,6 +5510,7 @@
       <c r="H59" s="11" t="n"/>
       <c r="I59" s="34" t="n"/>
       <c r="J59" s="11" t="n"/>
+      <c r="K59" s="11" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1" s="42">
       <c r="A60" s="19" t="n"/>
@@ -5429,6 +5523,7 @@
       <c r="H60" s="19" t="n"/>
       <c r="I60" s="33" t="n"/>
       <c r="J60" s="19" t="n"/>
+      <c r="K60" s="19" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1" s="42">
       <c r="A61" s="11" t="n"/>
@@ -5441,6 +5536,7 @@
       <c r="H61" s="11" t="n"/>
       <c r="I61" s="34" t="n"/>
       <c r="J61" s="11" t="n"/>
+      <c r="K61" s="11" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1" s="42">
       <c r="A62" s="19" t="n"/>
@@ -5453,6 +5549,7 @@
       <c r="H62" s="19" t="n"/>
       <c r="I62" s="33" t="n"/>
       <c r="J62" s="19" t="n"/>
+      <c r="K62" s="19" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1" s="42">
       <c r="A63" s="11" t="n"/>
@@ -5465,6 +5562,7 @@
       <c r="H63" s="11" t="n"/>
       <c r="I63" s="34" t="n"/>
       <c r="J63" s="11" t="n"/>
+      <c r="K63" s="11" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1" s="42">
       <c r="A64" s="19" t="n"/>
@@ -5477,6 +5575,7 @@
       <c r="H64" s="19" t="n"/>
       <c r="I64" s="33" t="n"/>
       <c r="J64" s="19" t="n"/>
+      <c r="K64" s="19" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1" s="42">
       <c r="A65" s="11" t="n"/>
@@ -5489,6 +5588,7 @@
       <c r="H65" s="11" t="n"/>
       <c r="I65" s="34" t="n"/>
       <c r="J65" s="11" t="n"/>
+      <c r="K65" s="11" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1" s="42">
       <c r="A66" s="19" t="n"/>
@@ -5501,6 +5601,7 @@
       <c r="H66" s="19" t="n"/>
       <c r="I66" s="33" t="n"/>
       <c r="J66" s="19" t="n"/>
+      <c r="K66" s="19" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1" s="42">
       <c r="A67" s="11" t="n"/>
@@ -5513,6 +5614,7 @@
       <c r="H67" s="11" t="n"/>
       <c r="I67" s="34" t="n"/>
       <c r="J67" s="11" t="n"/>
+      <c r="K67" s="11" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1" s="42">
       <c r="A68" s="19" t="n"/>
@@ -5525,6 +5627,7 @@
       <c r="H68" s="19" t="n"/>
       <c r="I68" s="33" t="n"/>
       <c r="J68" s="19" t="n"/>
+      <c r="K68" s="19" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1" s="42">
       <c r="A69" s="11" t="n"/>
@@ -5537,6 +5640,7 @@
       <c r="H69" s="11" t="n"/>
       <c r="I69" s="34" t="n"/>
       <c r="J69" s="11" t="n"/>
+      <c r="K69" s="11" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1" s="42">
       <c r="A70" s="19" t="n"/>
@@ -5549,6 +5653,7 @@
       <c r="H70" s="19" t="n"/>
       <c r="I70" s="33" t="n"/>
       <c r="J70" s="19" t="n"/>
+      <c r="K70" s="19" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1" s="42">
       <c r="A71" s="11" t="n"/>
@@ -5561,6 +5666,7 @@
       <c r="H71" s="11" t="n"/>
       <c r="I71" s="34" t="n"/>
       <c r="J71" s="11" t="n"/>
+      <c r="K71" s="11" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1" s="42">
       <c r="A72" s="19" t="n"/>
@@ -5573,6 +5679,7 @@
       <c r="H72" s="19" t="n"/>
       <c r="I72" s="33" t="n"/>
       <c r="J72" s="19" t="n"/>
+      <c r="K72" s="19" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1" s="42">
       <c r="A73" s="11" t="n"/>
@@ -5585,6 +5692,7 @@
       <c r="H73" s="11" t="n"/>
       <c r="I73" s="34" t="n"/>
       <c r="J73" s="11" t="n"/>
+      <c r="K73" s="11" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1" s="42">
       <c r="A74" s="19" t="n"/>
@@ -5597,6 +5705,7 @@
       <c r="H74" s="19" t="n"/>
       <c r="I74" s="33" t="n"/>
       <c r="J74" s="19" t="n"/>
+      <c r="K74" s="19" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1" s="42">
       <c r="A75" s="11" t="n"/>
@@ -5609,6 +5718,7 @@
       <c r="H75" s="11" t="n"/>
       <c r="I75" s="34" t="n"/>
       <c r="J75" s="11" t="n"/>
+      <c r="K75" s="11" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1" s="42">
       <c r="A76" s="19" t="n"/>
@@ -5621,6 +5731,7 @@
       <c r="H76" s="19" t="n"/>
       <c r="I76" s="33" t="n"/>
       <c r="J76" s="19" t="n"/>
+      <c r="K76" s="19" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1" s="42">
       <c r="A77" s="11" t="n"/>
@@ -5633,6 +5744,7 @@
       <c r="H77" s="11" t="n"/>
       <c r="I77" s="34" t="n"/>
       <c r="J77" s="11" t="n"/>
+      <c r="K77" s="11" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1" s="42">
       <c r="A78" s="19" t="n"/>
@@ -5645,6 +5757,7 @@
       <c r="H78" s="19" t="n"/>
       <c r="I78" s="33" t="n"/>
       <c r="J78" s="19" t="n"/>
+      <c r="K78" s="19" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1" s="42">
       <c r="A79" s="11" t="n"/>
@@ -5657,6 +5770,7 @@
       <c r="H79" s="11" t="n"/>
       <c r="I79" s="34" t="n"/>
       <c r="J79" s="11" t="n"/>
+      <c r="K79" s="11" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1" s="42">
       <c r="A80" s="19" t="n"/>
@@ -5669,6 +5783,7 @@
       <c r="H80" s="19" t="n"/>
       <c r="I80" s="33" t="n"/>
       <c r="J80" s="19" t="n"/>
+      <c r="K80" s="19" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1" s="42">
       <c r="A81" s="11" t="n"/>
@@ -5681,6 +5796,7 @@
       <c r="H81" s="11" t="n"/>
       <c r="I81" s="34" t="n"/>
       <c r="J81" s="11" t="n"/>
+      <c r="K81" s="11" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1" s="42">
       <c r="A82" s="19" t="n"/>
@@ -5693,6 +5809,7 @@
       <c r="H82" s="19" t="n"/>
       <c r="I82" s="33" t="n"/>
       <c r="J82" s="19" t="n"/>
+      <c r="K82" s="19" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1" s="42">
       <c r="A83" s="11" t="n"/>
@@ -5705,6 +5822,7 @@
       <c r="H83" s="11" t="n"/>
       <c r="I83" s="34" t="n"/>
       <c r="J83" s="11" t="n"/>
+      <c r="K83" s="11" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1" s="42">
       <c r="A84" s="19" t="n"/>
@@ -5717,6 +5835,7 @@
       <c r="H84" s="19" t="n"/>
       <c r="I84" s="33" t="n"/>
       <c r="J84" s="19" t="n"/>
+      <c r="K84" s="19" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1" s="42">
       <c r="A85" s="11" t="n"/>
@@ -5729,6 +5848,7 @@
       <c r="H85" s="11" t="n"/>
       <c r="I85" s="34" t="n"/>
       <c r="J85" s="11" t="n"/>
+      <c r="K85" s="11" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1" s="42">
       <c r="A86" s="19" t="n"/>
@@ -5741,6 +5861,7 @@
       <c r="H86" s="19" t="n"/>
       <c r="I86" s="33" t="n"/>
       <c r="J86" s="19" t="n"/>
+      <c r="K86" s="19" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1" s="42">
       <c r="A87" s="11" t="n"/>
@@ -5753,6 +5874,7 @@
       <c r="H87" s="11" t="n"/>
       <c r="I87" s="34" t="n"/>
       <c r="J87" s="11" t="n"/>
+      <c r="K87" s="11" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1" s="42">
       <c r="A88" s="19" t="n"/>
@@ -5765,6 +5887,7 @@
       <c r="H88" s="19" t="n"/>
       <c r="I88" s="33" t="n"/>
       <c r="J88" s="19" t="n"/>
+      <c r="K88" s="19" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1" s="42">
       <c r="A89" s="11" t="n"/>
@@ -5777,6 +5900,7 @@
       <c r="H89" s="11" t="n"/>
       <c r="I89" s="34" t="n"/>
       <c r="J89" s="11" t="n"/>
+      <c r="K89" s="11" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1" s="42">
       <c r="A90" s="19" t="n"/>
@@ -5789,6 +5913,7 @@
       <c r="H90" s="19" t="n"/>
       <c r="I90" s="33" t="n"/>
       <c r="J90" s="19" t="n"/>
+      <c r="K90" s="19" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1" s="42">
       <c r="A91" s="11" t="n"/>
@@ -5801,6 +5926,7 @@
       <c r="H91" s="11" t="n"/>
       <c r="I91" s="34" t="n"/>
       <c r="J91" s="11" t="n"/>
+      <c r="K91" s="11" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1" s="42">
       <c r="A92" s="19" t="n"/>
@@ -5813,6 +5939,7 @@
       <c r="H92" s="19" t="n"/>
       <c r="I92" s="33" t="n"/>
       <c r="J92" s="19" t="n"/>
+      <c r="K92" s="19" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1" s="42">
       <c r="A93" s="11" t="n"/>
@@ -5825,6 +5952,7 @@
       <c r="H93" s="11" t="n"/>
       <c r="I93" s="34" t="n"/>
       <c r="J93" s="11" t="n"/>
+      <c r="K93" s="11" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1" s="42">
       <c r="A94" s="19" t="n"/>
@@ -5837,6 +5965,7 @@
       <c r="H94" s="19" t="n"/>
       <c r="I94" s="33" t="n"/>
       <c r="J94" s="19" t="n"/>
+      <c r="K94" s="19" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1" s="42">
       <c r="A95" s="11" t="n"/>
@@ -5849,6 +5978,7 @@
       <c r="H95" s="11" t="n"/>
       <c r="I95" s="34" t="n"/>
       <c r="J95" s="11" t="n"/>
+      <c r="K95" s="11" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1" s="42">
       <c r="A96" s="19" t="n"/>
@@ -5861,6 +5991,7 @@
       <c r="H96" s="19" t="n"/>
       <c r="I96" s="33" t="n"/>
       <c r="J96" s="19" t="n"/>
+      <c r="K96" s="19" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1" s="42">
       <c r="A97" s="11" t="n"/>
@@ -5873,6 +6004,7 @@
       <c r="H97" s="11" t="n"/>
       <c r="I97" s="34" t="n"/>
       <c r="J97" s="11" t="n"/>
+      <c r="K97" s="11" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1" s="42">
       <c r="A98" s="19" t="n"/>
@@ -5885,6 +6017,7 @@
       <c r="H98" s="19" t="n"/>
       <c r="I98" s="33" t="n"/>
       <c r="J98" s="19" t="n"/>
+      <c r="K98" s="19" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1" s="42">
       <c r="A99" s="11" t="n"/>
@@ -5897,6 +6030,7 @@
       <c r="H99" s="11" t="n"/>
       <c r="I99" s="34" t="n"/>
       <c r="J99" s="11" t="n"/>
+      <c r="K99" s="11" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1" s="42">
       <c r="A100" s="19" t="n"/>
@@ -5909,6 +6043,7 @@
       <c r="H100" s="19" t="n"/>
       <c r="I100" s="33" t="n"/>
       <c r="J100" s="19" t="n"/>
+      <c r="K100" s="19" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1" s="42">
       <c r="A101" s="11" t="n"/>
@@ -5921,6 +6056,7 @@
       <c r="H101" s="11" t="n"/>
       <c r="I101" s="34" t="n"/>
       <c r="J101" s="11" t="n"/>
+      <c r="K101" s="11" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1" s="42">
       <c r="A102" s="19" t="n"/>
@@ -5933,6 +6069,7 @@
       <c r="H102" s="19" t="n"/>
       <c r="I102" s="33" t="n"/>
       <c r="J102" s="19" t="n"/>
+      <c r="K102" s="19" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1" s="42">
       <c r="A103" s="11" t="n"/>
@@ -5945,6 +6082,7 @@
       <c r="H103" s="11" t="n"/>
       <c r="I103" s="34" t="n"/>
       <c r="J103" s="11" t="n"/>
+      <c r="K103" s="11" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1" s="42">
       <c r="A104" s="19" t="n"/>
@@ -5957,6 +6095,7 @@
       <c r="H104" s="19" t="n"/>
       <c r="I104" s="33" t="n"/>
       <c r="J104" s="19" t="n"/>
+      <c r="K104" s="19" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1" s="42">
       <c r="A105" s="11" t="n"/>
@@ -5969,6 +6108,7 @@
       <c r="H105" s="11" t="n"/>
       <c r="I105" s="34" t="n"/>
       <c r="J105" s="11" t="n"/>
+      <c r="K105" s="11" t="n"/>
     </row>
     <row r="106" ht="18" customHeight="1" s="42">
       <c r="A106" s="19" t="n"/>
@@ -5981,6 +6121,7 @@
       <c r="H106" s="19" t="n"/>
       <c r="I106" s="33" t="n"/>
       <c r="J106" s="19" t="n"/>
+      <c r="K106" s="19" t="n"/>
     </row>
     <row r="107" ht="18" customHeight="1" s="42">
       <c r="A107" s="11" t="n"/>
@@ -5993,6 +6134,7 @@
       <c r="H107" s="11" t="n"/>
       <c r="I107" s="34" t="n"/>
       <c r="J107" s="11" t="n"/>
+      <c r="K107" s="11" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1" s="42">
       <c r="A108" s="19" t="n"/>
@@ -6005,6 +6147,7 @@
       <c r="H108" s="19" t="n"/>
       <c r="I108" s="33" t="n"/>
       <c r="J108" s="19" t="n"/>
+      <c r="K108" s="19" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1" s="42">
       <c r="A109" s="11" t="n"/>
@@ -6017,6 +6160,7 @@
       <c r="H109" s="11" t="n"/>
       <c r="I109" s="34" t="n"/>
       <c r="J109" s="11" t="n"/>
+      <c r="K109" s="11" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1" s="42">
       <c r="A110" s="19" t="n"/>
@@ -6029,6 +6173,7 @@
       <c r="H110" s="19" t="n"/>
       <c r="I110" s="33" t="n"/>
       <c r="J110" s="19" t="n"/>
+      <c r="K110" s="19" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1" s="42">
       <c r="A111" s="11" t="n"/>
@@ -6041,6 +6186,7 @@
       <c r="H111" s="11" t="n"/>
       <c r="I111" s="34" t="n"/>
       <c r="J111" s="11" t="n"/>
+      <c r="K111" s="11" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1" s="42">
       <c r="A112" s="19" t="n"/>
@@ -6053,6 +6199,7 @@
       <c r="H112" s="19" t="n"/>
       <c r="I112" s="33" t="n"/>
       <c r="J112" s="19" t="n"/>
+      <c r="K112" s="19" t="n"/>
     </row>
     <row r="113" ht="18" customHeight="1" s="42">
       <c r="A113" s="11" t="n"/>
@@ -6065,6 +6212,7 @@
       <c r="H113" s="11" t="n"/>
       <c r="I113" s="34" t="n"/>
       <c r="J113" s="11" t="n"/>
+      <c r="K113" s="11" t="n"/>
     </row>
     <row r="114" ht="18" customHeight="1" s="42">
       <c r="A114" s="19" t="n"/>
@@ -6077,6 +6225,7 @@
       <c r="H114" s="19" t="n"/>
       <c r="I114" s="33" t="n"/>
       <c r="J114" s="19" t="n"/>
+      <c r="K114" s="19" t="n"/>
     </row>
     <row r="115" ht="18" customHeight="1" s="42">
       <c r="A115" s="11" t="n"/>
@@ -6089,6 +6238,7 @@
       <c r="H115" s="11" t="n"/>
       <c r="I115" s="34" t="n"/>
       <c r="J115" s="11" t="n"/>
+      <c r="K115" s="11" t="n"/>
     </row>
     <row r="116" ht="18" customHeight="1" s="42">
       <c r="A116" s="19" t="n"/>
@@ -6101,6 +6251,7 @@
       <c r="H116" s="19" t="n"/>
       <c r="I116" s="33" t="n"/>
       <c r="J116" s="19" t="n"/>
+      <c r="K116" s="19" t="n"/>
     </row>
     <row r="117" ht="18" customHeight="1" s="42">
       <c r="A117" s="11" t="n"/>
@@ -6113,6 +6264,7 @@
       <c r="H117" s="11" t="n"/>
       <c r="I117" s="34" t="n"/>
       <c r="J117" s="11" t="n"/>
+      <c r="K117" s="11" t="n"/>
     </row>
     <row r="118" ht="18" customHeight="1" s="42">
       <c r="A118" s="19" t="n"/>
@@ -6125,6 +6277,7 @@
       <c r="H118" s="19" t="n"/>
       <c r="I118" s="33" t="n"/>
       <c r="J118" s="19" t="n"/>
+      <c r="K118" s="19" t="n"/>
     </row>
     <row r="119" ht="18" customHeight="1" s="42">
       <c r="A119" s="11" t="n"/>
@@ -6137,6 +6290,7 @@
       <c r="H119" s="11" t="n"/>
       <c r="I119" s="34" t="n"/>
       <c r="J119" s="11" t="n"/>
+      <c r="K119" s="11" t="n"/>
     </row>
     <row r="120" ht="18" customHeight="1" s="42">
       <c r="A120" s="19" t="n"/>
@@ -6149,6 +6303,7 @@
       <c r="H120" s="19" t="n"/>
       <c r="I120" s="33" t="n"/>
       <c r="J120" s="19" t="n"/>
+      <c r="K120" s="19" t="n"/>
     </row>
     <row r="121" ht="18" customHeight="1" s="42">
       <c r="A121" s="11" t="n"/>
@@ -6161,6 +6316,7 @@
       <c r="H121" s="11" t="n"/>
       <c r="I121" s="34" t="n"/>
       <c r="J121" s="11" t="n"/>
+      <c r="K121" s="11" t="n"/>
     </row>
     <row r="122" ht="18" customHeight="1" s="42">
       <c r="A122" s="19" t="n"/>
@@ -6173,6 +6329,7 @@
       <c r="H122" s="19" t="n"/>
       <c r="I122" s="33" t="n"/>
       <c r="J122" s="19" t="n"/>
+      <c r="K122" s="19" t="n"/>
     </row>
     <row r="123" ht="18" customHeight="1" s="42">
       <c r="A123" s="11" t="n"/>
@@ -6185,6 +6342,7 @@
       <c r="H123" s="11" t="n"/>
       <c r="I123" s="34" t="n"/>
       <c r="J123" s="11" t="n"/>
+      <c r="K123" s="11" t="n"/>
     </row>
     <row r="124" ht="18" customHeight="1" s="42">
       <c r="A124" s="19" t="n"/>
@@ -6197,6 +6355,7 @@
       <c r="H124" s="19" t="n"/>
       <c r="I124" s="33" t="n"/>
       <c r="J124" s="19" t="n"/>
+      <c r="K124" s="19" t="n"/>
     </row>
     <row r="125" ht="18" customHeight="1" s="42">
       <c r="A125" s="11" t="n"/>
@@ -6209,6 +6368,7 @@
       <c r="H125" s="11" t="n"/>
       <c r="I125" s="34" t="n"/>
       <c r="J125" s="11" t="n"/>
+      <c r="K125" s="11" t="n"/>
     </row>
     <row r="126" ht="18" customHeight="1" s="42">
       <c r="A126" s="19" t="n"/>
@@ -6221,6 +6381,7 @@
       <c r="H126" s="19" t="n"/>
       <c r="I126" s="33" t="n"/>
       <c r="J126" s="19" t="n"/>
+      <c r="K126" s="19" t="n"/>
     </row>
     <row r="127" ht="18" customHeight="1" s="42">
       <c r="A127" s="11" t="n"/>
@@ -6233,6 +6394,7 @@
       <c r="H127" s="11" t="n"/>
       <c r="I127" s="34" t="n"/>
       <c r="J127" s="11" t="n"/>
+      <c r="K127" s="11" t="n"/>
     </row>
     <row r="128" ht="18" customHeight="1" s="42">
       <c r="A128" s="19" t="n"/>
@@ -6245,6 +6407,7 @@
       <c r="H128" s="19" t="n"/>
       <c r="I128" s="33" t="n"/>
       <c r="J128" s="19" t="n"/>
+      <c r="K128" s="19" t="n"/>
     </row>
     <row r="129" ht="18" customHeight="1" s="42">
       <c r="A129" s="11" t="n"/>
@@ -6257,6 +6420,7 @@
       <c r="H129" s="11" t="n"/>
       <c r="I129" s="34" t="n"/>
       <c r="J129" s="11" t="n"/>
+      <c r="K129" s="11" t="n"/>
     </row>
     <row r="130" ht="18" customHeight="1" s="42">
       <c r="A130" s="19" t="n"/>
@@ -6269,6 +6433,7 @@
       <c r="H130" s="19" t="n"/>
       <c r="I130" s="33" t="n"/>
       <c r="J130" s="19" t="n"/>
+      <c r="K130" s="19" t="n"/>
     </row>
     <row r="131" ht="18" customHeight="1" s="42">
       <c r="A131" s="11" t="n"/>
@@ -6281,6 +6446,7 @@
       <c r="H131" s="11" t="n"/>
       <c r="I131" s="34" t="n"/>
       <c r="J131" s="11" t="n"/>
+      <c r="K131" s="11" t="n"/>
     </row>
     <row r="132" ht="18" customHeight="1" s="42">
       <c r="A132" s="19" t="n"/>
@@ -6293,6 +6459,7 @@
       <c r="H132" s="19" t="n"/>
       <c r="I132" s="33" t="n"/>
       <c r="J132" s="19" t="n"/>
+      <c r="K132" s="19" t="n"/>
     </row>
     <row r="133" ht="18" customHeight="1" s="42">
       <c r="A133" s="11" t="n"/>
@@ -6305,6 +6472,7 @@
       <c r="H133" s="11" t="n"/>
       <c r="I133" s="34" t="n"/>
       <c r="J133" s="11" t="n"/>
+      <c r="K133" s="11" t="n"/>
     </row>
     <row r="134" ht="18" customHeight="1" s="42">
       <c r="A134" s="19" t="n"/>
@@ -6317,6 +6485,7 @@
       <c r="H134" s="19" t="n"/>
       <c r="I134" s="33" t="n"/>
       <c r="J134" s="19" t="n"/>
+      <c r="K134" s="19" t="n"/>
     </row>
     <row r="135" ht="18" customHeight="1" s="42">
       <c r="A135" s="11" t="n"/>
@@ -6329,6 +6498,7 @@
       <c r="H135" s="11" t="n"/>
       <c r="I135" s="34" t="n"/>
       <c r="J135" s="11" t="n"/>
+      <c r="K135" s="11" t="n"/>
     </row>
     <row r="136" ht="18" customHeight="1" s="42">
       <c r="A136" s="19" t="n"/>
@@ -6341,6 +6511,7 @@
       <c r="H136" s="19" t="n"/>
       <c r="I136" s="33" t="n"/>
       <c r="J136" s="19" t="n"/>
+      <c r="K136" s="19" t="n"/>
     </row>
     <row r="137" ht="18" customHeight="1" s="42">
       <c r="A137" s="11" t="n"/>
@@ -6353,6 +6524,7 @@
       <c r="H137" s="11" t="n"/>
       <c r="I137" s="34" t="n"/>
       <c r="J137" s="11" t="n"/>
+      <c r="K137" s="11" t="n"/>
     </row>
     <row r="138" ht="18" customHeight="1" s="42">
       <c r="A138" s="19" t="n"/>
@@ -6365,6 +6537,7 @@
       <c r="H138" s="19" t="n"/>
       <c r="I138" s="33" t="n"/>
       <c r="J138" s="19" t="n"/>
+      <c r="K138" s="19" t="n"/>
     </row>
     <row r="139" ht="18" customHeight="1" s="42">
       <c r="A139" s="11" t="n"/>
@@ -6377,6 +6550,7 @@
       <c r="H139" s="11" t="n"/>
       <c r="I139" s="34" t="n"/>
       <c r="J139" s="11" t="n"/>
+      <c r="K139" s="11" t="n"/>
     </row>
     <row r="140" ht="18" customHeight="1" s="42">
       <c r="A140" s="19" t="n"/>
@@ -6389,6 +6563,7 @@
       <c r="H140" s="19" t="n"/>
       <c r="I140" s="33" t="n"/>
       <c r="J140" s="19" t="n"/>
+      <c r="K140" s="19" t="n"/>
     </row>
     <row r="141" ht="18" customHeight="1" s="42">
       <c r="A141" s="11" t="n"/>
@@ -6401,6 +6576,7 @@
       <c r="H141" s="11" t="n"/>
       <c r="I141" s="34" t="n"/>
       <c r="J141" s="11" t="n"/>
+      <c r="K141" s="11" t="n"/>
     </row>
     <row r="142" ht="18" customHeight="1" s="42">
       <c r="A142" s="19" t="n"/>
@@ -6413,6 +6589,7 @@
       <c r="H142" s="19" t="n"/>
       <c r="I142" s="33" t="n"/>
       <c r="J142" s="19" t="n"/>
+      <c r="K142" s="19" t="n"/>
     </row>
     <row r="143" ht="18" customHeight="1" s="42">
       <c r="A143" s="11" t="n"/>
@@ -6425,6 +6602,7 @@
       <c r="H143" s="11" t="n"/>
       <c r="I143" s="34" t="n"/>
       <c r="J143" s="11" t="n"/>
+      <c r="K143" s="11" t="n"/>
     </row>
     <row r="144" ht="18" customHeight="1" s="42">
       <c r="A144" s="19" t="n"/>
@@ -6437,6 +6615,7 @@
       <c r="H144" s="19" t="n"/>
       <c r="I144" s="33" t="n"/>
       <c r="J144" s="19" t="n"/>
+      <c r="K144" s="19" t="n"/>
     </row>
     <row r="145" ht="18" customHeight="1" s="42">
       <c r="A145" s="11" t="n"/>
@@ -6449,6 +6628,7 @@
       <c r="H145" s="11" t="n"/>
       <c r="I145" s="34" t="n"/>
       <c r="J145" s="11" t="n"/>
+      <c r="K145" s="11" t="n"/>
     </row>
     <row r="146" ht="18" customHeight="1" s="42">
       <c r="A146" s="19" t="n"/>
@@ -6461,6 +6641,7 @@
       <c r="H146" s="19" t="n"/>
       <c r="I146" s="33" t="n"/>
       <c r="J146" s="19" t="n"/>
+      <c r="K146" s="19" t="n"/>
     </row>
     <row r="147" ht="18" customHeight="1" s="42">
       <c r="A147" s="11" t="n"/>
@@ -6473,6 +6654,7 @@
       <c r="H147" s="11" t="n"/>
       <c r="I147" s="34" t="n"/>
       <c r="J147" s="11" t="n"/>
+      <c r="K147" s="11" t="n"/>
     </row>
     <row r="148" ht="18" customHeight="1" s="42">
       <c r="A148" s="19" t="n"/>
@@ -6485,6 +6667,7 @@
       <c r="H148" s="19" t="n"/>
       <c r="I148" s="33" t="n"/>
       <c r="J148" s="19" t="n"/>
+      <c r="K148" s="19" t="n"/>
     </row>
     <row r="149" ht="18" customHeight="1" s="42">
       <c r="A149" s="11" t="n"/>
@@ -6497,6 +6680,7 @@
       <c r="H149" s="11" t="n"/>
       <c r="I149" s="34" t="n"/>
       <c r="J149" s="11" t="n"/>
+      <c r="K149" s="11" t="n"/>
     </row>
     <row r="150" ht="18" customHeight="1" s="42">
       <c r="A150" s="19" t="n"/>
@@ -6509,6 +6693,7 @@
       <c r="H150" s="19" t="n"/>
       <c r="I150" s="33" t="n"/>
       <c r="J150" s="19" t="n"/>
+      <c r="K150" s="19" t="n"/>
     </row>
     <row r="151" ht="18" customHeight="1" s="42">
       <c r="A151" s="11" t="n"/>
@@ -6521,6 +6706,7 @@
       <c r="H151" s="11" t="n"/>
       <c r="I151" s="34" t="n"/>
       <c r="J151" s="11" t="n"/>
+      <c r="K151" s="11" t="n"/>
     </row>
     <row r="152" ht="18" customHeight="1" s="42">
       <c r="A152" s="19" t="n"/>
@@ -6533,6 +6719,7 @@
       <c r="H152" s="19" t="n"/>
       <c r="I152" s="33" t="n"/>
       <c r="J152" s="19" t="n"/>
+      <c r="K152" s="19" t="n"/>
     </row>
     <row r="153" ht="18" customHeight="1" s="42">
       <c r="A153" s="11" t="n"/>
@@ -6545,6 +6732,7 @@
       <c r="H153" s="11" t="n"/>
       <c r="I153" s="34" t="n"/>
       <c r="J153" s="11" t="n"/>
+      <c r="K153" s="11" t="n"/>
     </row>
     <row r="154" ht="18" customHeight="1" s="42">
       <c r="A154" s="19" t="n"/>
@@ -6557,6 +6745,7 @@
       <c r="H154" s="19" t="n"/>
       <c r="I154" s="33" t="n"/>
       <c r="J154" s="19" t="n"/>
+      <c r="K154" s="19" t="n"/>
     </row>
     <row r="155" ht="18" customHeight="1" s="42">
       <c r="A155" s="11" t="n"/>
@@ -6569,6 +6758,7 @@
       <c r="H155" s="11" t="n"/>
       <c r="I155" s="34" t="n"/>
       <c r="J155" s="11" t="n"/>
+      <c r="K155" s="11" t="n"/>
     </row>
     <row r="156" ht="18" customHeight="1" s="42">
       <c r="A156" s="19" t="n"/>
@@ -6581,6 +6771,7 @@
       <c r="H156" s="19" t="n"/>
       <c r="I156" s="33" t="n"/>
       <c r="J156" s="19" t="n"/>
+      <c r="K156" s="19" t="n"/>
     </row>
     <row r="157" ht="18" customHeight="1" s="42">
       <c r="A157" s="11" t="n"/>
@@ -6593,6 +6784,7 @@
       <c r="H157" s="11" t="n"/>
       <c r="I157" s="34" t="n"/>
       <c r="J157" s="11" t="n"/>
+      <c r="K157" s="11" t="n"/>
     </row>
     <row r="158" ht="18" customHeight="1" s="42">
       <c r="A158" s="19" t="n"/>
@@ -6605,6 +6797,7 @@
       <c r="H158" s="19" t="n"/>
       <c r="I158" s="33" t="n"/>
       <c r="J158" s="19" t="n"/>
+      <c r="K158" s="19" t="n"/>
     </row>
     <row r="159" ht="18" customHeight="1" s="42">
       <c r="A159" s="11" t="n"/>
@@ -6617,6 +6810,7 @@
       <c r="H159" s="11" t="n"/>
       <c r="I159" s="34" t="n"/>
       <c r="J159" s="11" t="n"/>
+      <c r="K159" s="11" t="n"/>
     </row>
     <row r="160" ht="18" customHeight="1" s="42">
       <c r="A160" s="19" t="n"/>
@@ -6629,6 +6823,7 @@
       <c r="H160" s="19" t="n"/>
       <c r="I160" s="33" t="n"/>
       <c r="J160" s="19" t="n"/>
+      <c r="K160" s="19" t="n"/>
     </row>
     <row r="161" ht="18" customHeight="1" s="42">
       <c r="A161" s="11" t="n"/>
@@ -6641,6 +6836,7 @@
       <c r="H161" s="11" t="n"/>
       <c r="I161" s="34" t="n"/>
       <c r="J161" s="11" t="n"/>
+      <c r="K161" s="11" t="n"/>
     </row>
     <row r="162" ht="18" customHeight="1" s="42">
       <c r="A162" s="19" t="n"/>
@@ -6653,6 +6849,7 @@
       <c r="H162" s="19" t="n"/>
       <c r="I162" s="33" t="n"/>
       <c r="J162" s="19" t="n"/>
+      <c r="K162" s="19" t="n"/>
     </row>
     <row r="163" ht="18" customHeight="1" s="42">
       <c r="A163" s="11" t="n"/>
@@ -6665,6 +6862,7 @@
       <c r="H163" s="11" t="n"/>
       <c r="I163" s="34" t="n"/>
       <c r="J163" s="11" t="n"/>
+      <c r="K163" s="11" t="n"/>
     </row>
     <row r="164" ht="18" customHeight="1" s="42">
       <c r="A164" s="19" t="n"/>
@@ -6677,6 +6875,7 @@
       <c r="H164" s="19" t="n"/>
       <c r="I164" s="33" t="n"/>
       <c r="J164" s="19" t="n"/>
+      <c r="K164" s="19" t="n"/>
     </row>
     <row r="165" ht="18" customHeight="1" s="42">
       <c r="A165" s="11" t="n"/>
@@ -6689,6 +6888,7 @@
       <c r="H165" s="11" t="n"/>
       <c r="I165" s="34" t="n"/>
       <c r="J165" s="11" t="n"/>
+      <c r="K165" s="11" t="n"/>
     </row>
     <row r="166" ht="18" customHeight="1" s="42">
       <c r="A166" s="19" t="n"/>
@@ -6701,6 +6901,7 @@
       <c r="H166" s="19" t="n"/>
       <c r="I166" s="33" t="n"/>
       <c r="J166" s="19" t="n"/>
+      <c r="K166" s="19" t="n"/>
     </row>
     <row r="167" ht="18" customHeight="1" s="42">
       <c r="A167" s="11" t="n"/>
@@ -6713,6 +6914,7 @@
       <c r="H167" s="11" t="n"/>
       <c r="I167" s="34" t="n"/>
       <c r="J167" s="11" t="n"/>
+      <c r="K167" s="11" t="n"/>
     </row>
     <row r="168" ht="18" customHeight="1" s="42">
       <c r="A168" s="19" t="n"/>
@@ -6725,6 +6927,7 @@
       <c r="H168" s="19" t="n"/>
       <c r="I168" s="33" t="n"/>
       <c r="J168" s="19" t="n"/>
+      <c r="K168" s="19" t="n"/>
     </row>
     <row r="169" ht="18" customHeight="1" s="42">
       <c r="A169" s="11" t="n"/>
@@ -6737,6 +6940,7 @@
       <c r="H169" s="11" t="n"/>
       <c r="I169" s="34" t="n"/>
       <c r="J169" s="11" t="n"/>
+      <c r="K169" s="11" t="n"/>
     </row>
     <row r="170" ht="18" customHeight="1" s="42">
       <c r="A170" s="19" t="n"/>
@@ -6749,6 +6953,7 @@
       <c r="H170" s="19" t="n"/>
       <c r="I170" s="33" t="n"/>
       <c r="J170" s="19" t="n"/>
+      <c r="K170" s="19" t="n"/>
     </row>
     <row r="171" ht="18" customHeight="1" s="42">
       <c r="A171" s="11" t="n"/>
@@ -6761,6 +6966,7 @@
       <c r="H171" s="11" t="n"/>
       <c r="I171" s="34" t="n"/>
       <c r="J171" s="11" t="n"/>
+      <c r="K171" s="11" t="n"/>
     </row>
     <row r="172" ht="18" customHeight="1" s="42">
       <c r="A172" s="19" t="n"/>
@@ -6773,6 +6979,7 @@
       <c r="H172" s="19" t="n"/>
       <c r="I172" s="33" t="n"/>
       <c r="J172" s="19" t="n"/>
+      <c r="K172" s="19" t="n"/>
     </row>
     <row r="173" ht="18" customHeight="1" s="42">
       <c r="A173" s="11" t="n"/>
@@ -6785,6 +6992,7 @@
       <c r="H173" s="11" t="n"/>
       <c r="I173" s="34" t="n"/>
       <c r="J173" s="11" t="n"/>
+      <c r="K173" s="11" t="n"/>
     </row>
     <row r="174" ht="18" customHeight="1" s="42">
       <c r="A174" s="19" t="n"/>
@@ -6797,6 +7005,7 @@
       <c r="H174" s="19" t="n"/>
       <c r="I174" s="33" t="n"/>
       <c r="J174" s="19" t="n"/>
+      <c r="K174" s="19" t="n"/>
     </row>
     <row r="175" ht="18" customHeight="1" s="42">
       <c r="A175" s="11" t="n"/>
@@ -6809,6 +7018,7 @@
       <c r="H175" s="11" t="n"/>
       <c r="I175" s="34" t="n"/>
       <c r="J175" s="11" t="n"/>
+      <c r="K175" s="11" t="n"/>
     </row>
     <row r="176" ht="18" customHeight="1" s="42">
       <c r="A176" s="19" t="n"/>
@@ -6821,6 +7031,7 @@
       <c r="H176" s="19" t="n"/>
       <c r="I176" s="33" t="n"/>
       <c r="J176" s="19" t="n"/>
+      <c r="K176" s="19" t="n"/>
     </row>
     <row r="177" ht="18" customHeight="1" s="42">
       <c r="A177" s="11" t="n"/>
@@ -6833,6 +7044,7 @@
       <c r="H177" s="11" t="n"/>
       <c r="I177" s="34" t="n"/>
       <c r="J177" s="11" t="n"/>
+      <c r="K177" s="11" t="n"/>
     </row>
     <row r="178" ht="18" customHeight="1" s="42">
       <c r="A178" s="19" t="n"/>
@@ -6845,6 +7057,7 @@
       <c r="H178" s="19" t="n"/>
       <c r="I178" s="33" t="n"/>
       <c r="J178" s="19" t="n"/>
+      <c r="K178" s="19" t="n"/>
     </row>
     <row r="179" ht="18" customHeight="1" s="42">
       <c r="A179" s="11" t="n"/>
@@ -6857,6 +7070,7 @@
       <c r="H179" s="11" t="n"/>
       <c r="I179" s="34" t="n"/>
       <c r="J179" s="11" t="n"/>
+      <c r="K179" s="11" t="n"/>
     </row>
     <row r="180" ht="18" customHeight="1" s="42">
       <c r="A180" s="19" t="n"/>
@@ -6869,6 +7083,7 @@
       <c r="H180" s="19" t="n"/>
       <c r="I180" s="33" t="n"/>
       <c r="J180" s="19" t="n"/>
+      <c r="K180" s="19" t="n"/>
     </row>
     <row r="181" ht="18" customHeight="1" s="42">
       <c r="A181" s="11" t="n"/>
@@ -6881,6 +7096,7 @@
       <c r="H181" s="11" t="n"/>
       <c r="I181" s="34" t="n"/>
       <c r="J181" s="11" t="n"/>
+      <c r="K181" s="11" t="n"/>
     </row>
     <row r="182" ht="18" customHeight="1" s="42">
       <c r="A182" s="19" t="n"/>
@@ -6893,6 +7109,7 @@
       <c r="H182" s="19" t="n"/>
       <c r="I182" s="33" t="n"/>
       <c r="J182" s="19" t="n"/>
+      <c r="K182" s="19" t="n"/>
     </row>
     <row r="183" ht="18" customHeight="1" s="42">
       <c r="A183" s="11" t="n"/>
@@ -6905,6 +7122,7 @@
       <c r="H183" s="11" t="n"/>
       <c r="I183" s="34" t="n"/>
       <c r="J183" s="11" t="n"/>
+      <c r="K183" s="11" t="n"/>
     </row>
     <row r="184" ht="18" customHeight="1" s="42">
       <c r="A184" s="19" t="n"/>
@@ -6917,6 +7135,7 @@
       <c r="H184" s="19" t="n"/>
       <c r="I184" s="33" t="n"/>
       <c r="J184" s="19" t="n"/>
+      <c r="K184" s="19" t="n"/>
     </row>
     <row r="185" ht="18" customHeight="1" s="42">
       <c r="A185" s="11" t="n"/>
@@ -6929,6 +7148,7 @@
       <c r="H185" s="11" t="n"/>
       <c r="I185" s="34" t="n"/>
       <c r="J185" s="11" t="n"/>
+      <c r="K185" s="11" t="n"/>
     </row>
     <row r="186" ht="18" customHeight="1" s="42">
       <c r="A186" s="19" t="n"/>
@@ -6941,6 +7161,7 @@
       <c r="H186" s="19" t="n"/>
       <c r="I186" s="33" t="n"/>
       <c r="J186" s="19" t="n"/>
+      <c r="K186" s="19" t="n"/>
     </row>
     <row r="187" ht="18" customHeight="1" s="42">
       <c r="A187" s="11" t="n"/>
@@ -6953,6 +7174,7 @@
       <c r="H187" s="11" t="n"/>
       <c r="I187" s="34" t="n"/>
       <c r="J187" s="11" t="n"/>
+      <c r="K187" s="11" t="n"/>
     </row>
     <row r="188" ht="18" customHeight="1" s="42">
       <c r="A188" s="19" t="n"/>
@@ -6965,6 +7187,7 @@
       <c r="H188" s="19" t="n"/>
       <c r="I188" s="33" t="n"/>
       <c r="J188" s="19" t="n"/>
+      <c r="K188" s="19" t="n"/>
     </row>
     <row r="189" ht="18" customHeight="1" s="42">
       <c r="A189" s="11" t="n"/>
@@ -6977,6 +7200,7 @@
       <c r="H189" s="11" t="n"/>
       <c r="I189" s="34" t="n"/>
       <c r="J189" s="11" t="n"/>
+      <c r="K189" s="11" t="n"/>
     </row>
     <row r="190" ht="18" customHeight="1" s="42">
       <c r="A190" s="19" t="n"/>
@@ -6989,6 +7213,7 @@
       <c r="H190" s="19" t="n"/>
       <c r="I190" s="33" t="n"/>
       <c r="J190" s="19" t="n"/>
+      <c r="K190" s="19" t="n"/>
     </row>
     <row r="191" ht="18" customHeight="1" s="42">
       <c r="A191" s="11" t="n"/>
@@ -7001,6 +7226,7 @@
       <c r="H191" s="11" t="n"/>
       <c r="I191" s="34" t="n"/>
       <c r="J191" s="11" t="n"/>
+      <c r="K191" s="11" t="n"/>
     </row>
     <row r="192" ht="18" customHeight="1" s="42">
       <c r="A192" s="19" t="n"/>
@@ -7013,6 +7239,7 @@
       <c r="H192" s="19" t="n"/>
       <c r="I192" s="33" t="n"/>
       <c r="J192" s="19" t="n"/>
+      <c r="K192" s="19" t="n"/>
     </row>
     <row r="193" ht="18" customHeight="1" s="42">
       <c r="A193" s="11" t="n"/>
@@ -7025,6 +7252,7 @@
       <c r="H193" s="11" t="n"/>
       <c r="I193" s="34" t="n"/>
       <c r="J193" s="11" t="n"/>
+      <c r="K193" s="11" t="n"/>
     </row>
     <row r="194" ht="18" customHeight="1" s="42">
       <c r="A194" s="19" t="n"/>
@@ -7037,6 +7265,7 @@
       <c r="H194" s="19" t="n"/>
       <c r="I194" s="33" t="n"/>
       <c r="J194" s="19" t="n"/>
+      <c r="K194" s="19" t="n"/>
     </row>
     <row r="195" ht="18" customHeight="1" s="42">
       <c r="A195" s="11" t="n"/>
@@ -7049,6 +7278,7 @@
       <c r="H195" s="11" t="n"/>
       <c r="I195" s="34" t="n"/>
       <c r="J195" s="11" t="n"/>
+      <c r="K195" s="11" t="n"/>
     </row>
     <row r="196" ht="18" customHeight="1" s="42">
       <c r="A196" s="19" t="n"/>
@@ -7061,6 +7291,7 @@
       <c r="H196" s="19" t="n"/>
       <c r="I196" s="33" t="n"/>
       <c r="J196" s="19" t="n"/>
+      <c r="K196" s="19" t="n"/>
     </row>
     <row r="197" ht="18" customHeight="1" s="42">
       <c r="A197" s="11" t="n"/>
@@ -7073,6 +7304,7 @@
       <c r="H197" s="11" t="n"/>
       <c r="I197" s="34" t="n"/>
       <c r="J197" s="11" t="n"/>
+      <c r="K197" s="11" t="n"/>
     </row>
     <row r="198" ht="18" customHeight="1" s="42">
       <c r="A198" s="19" t="n"/>
@@ -7085,6 +7317,7 @@
       <c r="H198" s="19" t="n"/>
       <c r="I198" s="33" t="n"/>
       <c r="J198" s="19" t="n"/>
+      <c r="K198" s="19" t="n"/>
     </row>
     <row r="199" ht="18" customHeight="1" s="42">
       <c r="A199" s="11" t="n"/>
@@ -7097,6 +7330,7 @@
       <c r="H199" s="11" t="n"/>
       <c r="I199" s="34" t="n"/>
       <c r="J199" s="11" t="n"/>
+      <c r="K199" s="11" t="n"/>
     </row>
     <row r="200" ht="18" customHeight="1" s="42">
       <c r="A200" s="19" t="n"/>
@@ -7109,6 +7343,7 @@
       <c r="H200" s="19" t="n"/>
       <c r="I200" s="33" t="n"/>
       <c r="J200" s="19" t="n"/>
+      <c r="K200" s="19" t="n"/>
     </row>
     <row r="201" ht="18" customHeight="1" s="42">
       <c r="A201" s="11" t="n"/>
@@ -7121,6 +7356,7 @@
       <c r="H201" s="11" t="n"/>
       <c r="I201" s="34" t="n"/>
       <c r="J201" s="11" t="n"/>
+      <c r="K201" s="11" t="n"/>
     </row>
     <row r="202" ht="18" customHeight="1" s="42">
       <c r="A202" s="19" t="n"/>
@@ -7133,6 +7369,7 @@
       <c r="H202" s="19" t="n"/>
       <c r="I202" s="33" t="n"/>
       <c r="J202" s="19" t="n"/>
+      <c r="K202" s="19" t="n"/>
     </row>
     <row r="203" ht="18" customHeight="1" s="42">
       <c r="A203" s="11" t="n"/>
@@ -7145,6 +7382,7 @@
       <c r="H203" s="11" t="n"/>
       <c r="I203" s="34" t="n"/>
       <c r="J203" s="11" t="n"/>
+      <c r="K203" s="11" t="n"/>
     </row>
     <row r="204" ht="18" customHeight="1" s="42">
       <c r="A204" s="19" t="n"/>
@@ -7157,6 +7395,7 @@
       <c r="H204" s="19" t="n"/>
       <c r="I204" s="33" t="n"/>
       <c r="J204" s="19" t="n"/>
+      <c r="K204" s="19" t="n"/>
     </row>
     <row r="205" ht="18" customHeight="1" s="42">
       <c r="A205" s="11" t="n"/>
@@ -7169,6 +7408,7 @@
       <c r="H205" s="11" t="n"/>
       <c r="I205" s="34" t="n"/>
       <c r="J205" s="11" t="n"/>
+      <c r="K205" s="11" t="n"/>
     </row>
     <row r="206" ht="18" customHeight="1" s="42">
       <c r="A206" s="19" t="n"/>
@@ -7181,6 +7421,7 @@
       <c r="H206" s="19" t="n"/>
       <c r="I206" s="33" t="n"/>
       <c r="J206" s="19" t="n"/>
+      <c r="K206" s="19" t="n"/>
     </row>
     <row r="207" ht="18" customHeight="1" s="42">
       <c r="A207" s="11" t="n"/>
@@ -7193,6 +7434,7 @@
       <c r="H207" s="11" t="n"/>
       <c r="I207" s="34" t="n"/>
       <c r="J207" s="11" t="n"/>
+      <c r="K207" s="11" t="n"/>
     </row>
     <row r="208" ht="18" customHeight="1" s="42">
       <c r="A208" s="19" t="n"/>
@@ -7205,6 +7447,7 @@
       <c r="H208" s="19" t="n"/>
       <c r="I208" s="33" t="n"/>
       <c r="J208" s="19" t="n"/>
+      <c r="K208" s="19" t="n"/>
     </row>
     <row r="209" ht="18" customHeight="1" s="42">
       <c r="A209" s="11" t="n"/>
@@ -7217,6 +7460,7 @@
       <c r="H209" s="11" t="n"/>
       <c r="I209" s="34" t="n"/>
       <c r="J209" s="11" t="n"/>
+      <c r="K209" s="11" t="n"/>
     </row>
     <row r="210" ht="18" customHeight="1" s="42">
       <c r="A210" s="19" t="n"/>
@@ -7229,6 +7473,7 @@
       <c r="H210" s="19" t="n"/>
       <c r="I210" s="33" t="n"/>
       <c r="J210" s="19" t="n"/>
+      <c r="K210" s="19" t="n"/>
     </row>
     <row r="211" ht="18" customHeight="1" s="42">
       <c r="A211" s="11" t="n"/>
@@ -7241,6 +7486,7 @@
       <c r="H211" s="11" t="n"/>
       <c r="I211" s="34" t="n"/>
       <c r="J211" s="11" t="n"/>
+      <c r="K211" s="11" t="n"/>
     </row>
     <row r="212" ht="18" customHeight="1" s="42">
       <c r="A212" s="19" t="n"/>
@@ -7253,6 +7499,7 @@
       <c r="H212" s="19" t="n"/>
       <c r="I212" s="33" t="n"/>
       <c r="J212" s="19" t="n"/>
+      <c r="K212" s="19" t="n"/>
     </row>
     <row r="213" ht="18" customHeight="1" s="42">
       <c r="A213" s="11" t="n"/>
@@ -7265,6 +7512,7 @@
       <c r="H213" s="11" t="n"/>
       <c r="I213" s="34" t="n"/>
       <c r="J213" s="11" t="n"/>
+      <c r="K213" s="11" t="n"/>
     </row>
     <row r="214" ht="18" customHeight="1" s="42">
       <c r="A214" s="19" t="n"/>
@@ -7277,6 +7525,7 @@
       <c r="H214" s="19" t="n"/>
       <c r="I214" s="33" t="n"/>
       <c r="J214" s="19" t="n"/>
+      <c r="K214" s="19" t="n"/>
     </row>
     <row r="215" ht="18" customHeight="1" s="42">
       <c r="A215" s="11" t="n"/>
@@ -7289,6 +7538,7 @@
       <c r="H215" s="11" t="n"/>
       <c r="I215" s="34" t="n"/>
       <c r="J215" s="11" t="n"/>
+      <c r="K215" s="11" t="n"/>
     </row>
     <row r="216" ht="18" customHeight="1" s="42">
       <c r="A216" s="19" t="n"/>
@@ -7301,6 +7551,7 @@
       <c r="H216" s="19" t="n"/>
       <c r="I216" s="33" t="n"/>
       <c r="J216" s="19" t="n"/>
+      <c r="K216" s="19" t="n"/>
     </row>
     <row r="217" ht="18" customHeight="1" s="42">
       <c r="A217" s="11" t="n"/>
@@ -7313,6 +7564,7 @@
       <c r="H217" s="11" t="n"/>
       <c r="I217" s="34" t="n"/>
       <c r="J217" s="11" t="n"/>
+      <c r="K217" s="11" t="n"/>
     </row>
     <row r="218" ht="18" customHeight="1" s="42">
       <c r="A218" s="19" t="n"/>
@@ -7325,6 +7577,7 @@
       <c r="H218" s="19" t="n"/>
       <c r="I218" s="33" t="n"/>
       <c r="J218" s="19" t="n"/>
+      <c r="K218" s="19" t="n"/>
     </row>
     <row r="219" ht="18" customHeight="1" s="42">
       <c r="A219" s="11" t="n"/>
@@ -7337,6 +7590,7 @@
       <c r="H219" s="11" t="n"/>
       <c r="I219" s="34" t="n"/>
       <c r="J219" s="11" t="n"/>
+      <c r="K219" s="11" t="n"/>
     </row>
     <row r="220" ht="18" customHeight="1" s="42">
       <c r="A220" s="19" t="n"/>
@@ -7349,6 +7603,7 @@
       <c r="H220" s="19" t="n"/>
       <c r="I220" s="33" t="n"/>
       <c r="J220" s="19" t="n"/>
+      <c r="K220" s="19" t="n"/>
     </row>
     <row r="221" ht="18" customHeight="1" s="42">
       <c r="A221" s="11" t="n"/>
@@ -7361,6 +7616,7 @@
       <c r="H221" s="11" t="n"/>
       <c r="I221" s="34" t="n"/>
       <c r="J221" s="11" t="n"/>
+      <c r="K221" s="11" t="n"/>
     </row>
     <row r="222" ht="18" customHeight="1" s="42">
       <c r="A222" s="19" t="n"/>
@@ -7373,6 +7629,7 @@
       <c r="H222" s="19" t="n"/>
       <c r="I222" s="33" t="n"/>
       <c r="J222" s="19" t="n"/>
+      <c r="K222" s="19" t="n"/>
     </row>
     <row r="223" ht="18" customHeight="1" s="42">
       <c r="A223" s="11" t="n"/>
@@ -7385,6 +7642,7 @@
       <c r="H223" s="11" t="n"/>
       <c r="I223" s="34" t="n"/>
       <c r="J223" s="11" t="n"/>
+      <c r="K223" s="11" t="n"/>
     </row>
     <row r="224" ht="18" customHeight="1" s="42">
       <c r="A224" s="19" t="n"/>
@@ -7397,6 +7655,7 @@
       <c r="H224" s="19" t="n"/>
       <c r="I224" s="33" t="n"/>
       <c r="J224" s="19" t="n"/>
+      <c r="K224" s="19" t="n"/>
     </row>
     <row r="225" ht="18" customHeight="1" s="42">
       <c r="A225" s="11" t="n"/>
@@ -7409,6 +7668,7 @@
       <c r="H225" s="11" t="n"/>
       <c r="I225" s="34" t="n"/>
       <c r="J225" s="11" t="n"/>
+      <c r="K225" s="11" t="n"/>
     </row>
     <row r="226" ht="18" customHeight="1" s="42">
       <c r="A226" s="19" t="n"/>
@@ -7421,6 +7681,7 @@
       <c r="H226" s="19" t="n"/>
       <c r="I226" s="33" t="n"/>
       <c r="J226" s="19" t="n"/>
+      <c r="K226" s="19" t="n"/>
     </row>
     <row r="227" ht="18" customHeight="1" s="42">
       <c r="A227" s="11" t="n"/>
@@ -7433,6 +7694,7 @@
       <c r="H227" s="11" t="n"/>
       <c r="I227" s="34" t="n"/>
       <c r="J227" s="11" t="n"/>
+      <c r="K227" s="11" t="n"/>
     </row>
     <row r="228" ht="18" customHeight="1" s="42">
       <c r="A228" s="19" t="n"/>
@@ -7445,6 +7707,7 @@
       <c r="H228" s="19" t="n"/>
       <c r="I228" s="33" t="n"/>
       <c r="J228" s="19" t="n"/>
+      <c r="K228" s="19" t="n"/>
     </row>
     <row r="229" ht="18" customHeight="1" s="42">
       <c r="A229" s="11" t="n"/>
@@ -7457,6 +7720,7 @@
       <c r="H229" s="11" t="n"/>
       <c r="I229" s="34" t="n"/>
       <c r="J229" s="11" t="n"/>
+      <c r="K229" s="11" t="n"/>
     </row>
     <row r="230" ht="18" customHeight="1" s="42">
       <c r="A230" s="19" t="n"/>
@@ -7469,6 +7733,7 @@
       <c r="H230" s="19" t="n"/>
       <c r="I230" s="33" t="n"/>
       <c r="J230" s="19" t="n"/>
+      <c r="K230" s="19" t="n"/>
     </row>
     <row r="231" ht="18" customHeight="1" s="42">
       <c r="A231" s="11" t="n"/>
@@ -7481,6 +7746,7 @@
       <c r="H231" s="11" t="n"/>
       <c r="I231" s="34" t="n"/>
       <c r="J231" s="11" t="n"/>
+      <c r="K231" s="11" t="n"/>
     </row>
     <row r="232" ht="18" customHeight="1" s="42">
       <c r="A232" s="19" t="n"/>
@@ -7493,6 +7759,7 @@
       <c r="H232" s="19" t="n"/>
       <c r="I232" s="33" t="n"/>
       <c r="J232" s="19" t="n"/>
+      <c r="K232" s="19" t="n"/>
     </row>
     <row r="233" ht="18" customHeight="1" s="42">
       <c r="A233" s="11" t="n"/>
@@ -7505,6 +7772,7 @@
       <c r="H233" s="11" t="n"/>
       <c r="I233" s="34" t="n"/>
       <c r="J233" s="11" t="n"/>
+      <c r="K233" s="11" t="n"/>
     </row>
     <row r="234" ht="18" customHeight="1" s="42">
       <c r="A234" s="19" t="n"/>
@@ -7517,6 +7785,7 @@
       <c r="H234" s="19" t="n"/>
       <c r="I234" s="33" t="n"/>
       <c r="J234" s="19" t="n"/>
+      <c r="K234" s="19" t="n"/>
     </row>
     <row r="235" ht="18" customHeight="1" s="42">
       <c r="A235" s="11" t="n"/>
@@ -7529,6 +7798,7 @@
       <c r="H235" s="11" t="n"/>
       <c r="I235" s="34" t="n"/>
       <c r="J235" s="11" t="n"/>
+      <c r="K235" s="11" t="n"/>
     </row>
     <row r="236" ht="18" customHeight="1" s="42">
       <c r="A236" s="19" t="n"/>
@@ -7541,6 +7811,7 @@
       <c r="H236" s="19" t="n"/>
       <c r="I236" s="33" t="n"/>
       <c r="J236" s="19" t="n"/>
+      <c r="K236" s="19" t="n"/>
     </row>
     <row r="237" ht="18" customHeight="1" s="42">
       <c r="A237" s="11" t="n"/>
@@ -7553,6 +7824,7 @@
       <c r="H237" s="11" t="n"/>
       <c r="I237" s="34" t="n"/>
       <c r="J237" s="11" t="n"/>
+      <c r="K237" s="11" t="n"/>
     </row>
     <row r="238" ht="18" customHeight="1" s="42">
       <c r="A238" s="19" t="n"/>
@@ -7565,6 +7837,7 @@
       <c r="H238" s="19" t="n"/>
       <c r="I238" s="33" t="n"/>
       <c r="J238" s="19" t="n"/>
+      <c r="K238" s="19" t="n"/>
     </row>
     <row r="239" ht="18" customHeight="1" s="42">
       <c r="A239" s="11" t="n"/>
@@ -7577,6 +7850,7 @@
       <c r="H239" s="11" t="n"/>
       <c r="I239" s="34" t="n"/>
       <c r="J239" s="11" t="n"/>
+      <c r="K239" s="11" t="n"/>
     </row>
     <row r="240" ht="18" customHeight="1" s="42">
       <c r="A240" s="19" t="n"/>
@@ -7589,6 +7863,7 @@
       <c r="H240" s="19" t="n"/>
       <c r="I240" s="33" t="n"/>
       <c r="J240" s="19" t="n"/>
+      <c r="K240" s="19" t="n"/>
     </row>
     <row r="241" ht="18" customHeight="1" s="42">
       <c r="A241" s="11" t="n"/>
@@ -7601,6 +7876,7 @@
       <c r="H241" s="11" t="n"/>
       <c r="I241" s="34" t="n"/>
       <c r="J241" s="11" t="n"/>
+      <c r="K241" s="11" t="n"/>
     </row>
     <row r="242" ht="18" customHeight="1" s="42">
       <c r="A242" s="19" t="n"/>
@@ -7613,6 +7889,7 @@
       <c r="H242" s="19" t="n"/>
       <c r="I242" s="33" t="n"/>
       <c r="J242" s="19" t="n"/>
+      <c r="K242" s="19" t="n"/>
     </row>
     <row r="243" ht="18" customHeight="1" s="42">
       <c r="A243" s="11" t="n"/>
@@ -7625,6 +7902,7 @@
       <c r="H243" s="11" t="n"/>
       <c r="I243" s="34" t="n"/>
       <c r="J243" s="11" t="n"/>
+      <c r="K243" s="11" t="n"/>
     </row>
     <row r="244" ht="18" customHeight="1" s="42">
       <c r="A244" s="19" t="n"/>
@@ -7637,6 +7915,7 @@
       <c r="H244" s="19" t="n"/>
       <c r="I244" s="33" t="n"/>
       <c r="J244" s="19" t="n"/>
+      <c r="K244" s="19" t="n"/>
     </row>
     <row r="245" ht="18" customHeight="1" s="42">
       <c r="A245" s="11" t="n"/>
@@ -7649,6 +7928,7 @@
       <c r="H245" s="11" t="n"/>
       <c r="I245" s="34" t="n"/>
       <c r="J245" s="11" t="n"/>
+      <c r="K245" s="11" t="n"/>
     </row>
     <row r="246" ht="18" customHeight="1" s="42">
       <c r="A246" s="19" t="n"/>
@@ -7661,6 +7941,7 @@
       <c r="H246" s="19" t="n"/>
       <c r="I246" s="33" t="n"/>
       <c r="J246" s="19" t="n"/>
+      <c r="K246" s="19" t="n"/>
     </row>
     <row r="247" ht="18" customHeight="1" s="42">
       <c r="A247" s="11" t="n"/>
@@ -7673,6 +7954,7 @@
       <c r="H247" s="11" t="n"/>
       <c r="I247" s="34" t="n"/>
       <c r="J247" s="11" t="n"/>
+      <c r="K247" s="11" t="n"/>
     </row>
     <row r="248" ht="18" customHeight="1" s="42">
       <c r="A248" s="19" t="n"/>
@@ -7685,6 +7967,7 @@
       <c r="H248" s="19" t="n"/>
       <c r="I248" s="33" t="n"/>
       <c r="J248" s="19" t="n"/>
+      <c r="K248" s="19" t="n"/>
     </row>
     <row r="249" ht="18" customHeight="1" s="42">
       <c r="A249" s="11" t="n"/>
@@ -7697,6 +7980,7 @@
       <c r="H249" s="11" t="n"/>
       <c r="I249" s="34" t="n"/>
       <c r="J249" s="11" t="n"/>
+      <c r="K249" s="11" t="n"/>
     </row>
     <row r="250" ht="18" customHeight="1" s="42">
       <c r="A250" s="19" t="n"/>
@@ -7709,6 +7993,7 @@
       <c r="H250" s="19" t="n"/>
       <c r="I250" s="33" t="n"/>
       <c r="J250" s="19" t="n"/>
+      <c r="K250" s="19" t="n"/>
     </row>
     <row r="251" ht="18" customHeight="1" s="42">
       <c r="A251" s="11" t="n"/>
@@ -7721,6 +8006,7 @@
       <c r="H251" s="11" t="n"/>
       <c r="I251" s="34" t="n"/>
       <c r="J251" s="11" t="n"/>
+      <c r="K251" s="11" t="n"/>
     </row>
     <row r="252" ht="18" customHeight="1" s="42">
       <c r="A252" s="19" t="n"/>
@@ -7733,6 +8019,7 @@
       <c r="H252" s="19" t="n"/>
       <c r="I252" s="33" t="n"/>
       <c r="J252" s="19" t="n"/>
+      <c r="K252" s="19" t="n"/>
     </row>
     <row r="253" ht="18" customHeight="1" s="42">
       <c r="A253" s="11" t="n"/>
@@ -7745,6 +8032,7 @@
       <c r="H253" s="11" t="n"/>
       <c r="I253" s="34" t="n"/>
       <c r="J253" s="11" t="n"/>
+      <c r="K253" s="11" t="n"/>
     </row>
     <row r="254" ht="18" customHeight="1" s="42">
       <c r="A254" s="19" t="n"/>
@@ -7757,6 +8045,7 @@
       <c r="H254" s="19" t="n"/>
       <c r="I254" s="33" t="n"/>
       <c r="J254" s="19" t="n"/>
+      <c r="K254" s="19" t="n"/>
     </row>
     <row r="255" ht="18" customHeight="1" s="42">
       <c r="A255" s="11" t="n"/>
@@ -7769,6 +8058,7 @@
       <c r="H255" s="11" t="n"/>
       <c r="I255" s="34" t="n"/>
       <c r="J255" s="11" t="n"/>
+      <c r="K255" s="11" t="n"/>
     </row>
     <row r="256" ht="18" customHeight="1" s="42">
       <c r="A256" s="19" t="n"/>
@@ -7781,6 +8071,7 @@
       <c r="H256" s="19" t="n"/>
       <c r="I256" s="33" t="n"/>
       <c r="J256" s="19" t="n"/>
+      <c r="K256" s="19" t="n"/>
     </row>
     <row r="257" ht="18" customHeight="1" s="42">
       <c r="A257" s="11" t="n"/>
@@ -7793,6 +8084,7 @@
       <c r="H257" s="11" t="n"/>
       <c r="I257" s="34" t="n"/>
       <c r="J257" s="11" t="n"/>
+      <c r="K257" s="11" t="n"/>
     </row>
     <row r="258" ht="18" customHeight="1" s="42">
       <c r="A258" s="19" t="n"/>
@@ -7805,6 +8097,7 @@
       <c r="H258" s="19" t="n"/>
       <c r="I258" s="33" t="n"/>
       <c r="J258" s="19" t="n"/>
+      <c r="K258" s="19" t="n"/>
     </row>
     <row r="259" ht="18" customHeight="1" s="42">
       <c r="A259" s="11" t="n"/>
@@ -7817,6 +8110,7 @@
       <c r="H259" s="11" t="n"/>
       <c r="I259" s="34" t="n"/>
       <c r="J259" s="11" t="n"/>
+      <c r="K259" s="11" t="n"/>
     </row>
     <row r="260" ht="18" customHeight="1" s="42">
       <c r="A260" s="19" t="n"/>
@@ -7829,6 +8123,7 @@
       <c r="H260" s="19" t="n"/>
       <c r="I260" s="33" t="n"/>
       <c r="J260" s="19" t="n"/>
+      <c r="K260" s="19" t="n"/>
     </row>
     <row r="261" ht="18" customHeight="1" s="42">
       <c r="A261" s="11" t="n"/>
@@ -7841,6 +8136,7 @@
       <c r="H261" s="11" t="n"/>
       <c r="I261" s="34" t="n"/>
       <c r="J261" s="11" t="n"/>
+      <c r="K261" s="11" t="n"/>
     </row>
     <row r="262" ht="18" customHeight="1" s="42">
       <c r="A262" s="19" t="n"/>
@@ -7853,6 +8149,7 @@
       <c r="H262" s="19" t="n"/>
       <c r="I262" s="33" t="n"/>
       <c r="J262" s="19" t="n"/>
+      <c r="K262" s="19" t="n"/>
     </row>
     <row r="263" ht="18" customHeight="1" s="42">
       <c r="A263" s="11" t="n"/>
@@ -7865,6 +8162,7 @@
       <c r="H263" s="11" t="n"/>
       <c r="I263" s="34" t="n"/>
       <c r="J263" s="11" t="n"/>
+      <c r="K263" s="11" t="n"/>
     </row>
     <row r="264" ht="18" customHeight="1" s="42">
       <c r="A264" s="19" t="n"/>
@@ -7877,6 +8175,7 @@
       <c r="H264" s="19" t="n"/>
       <c r="I264" s="33" t="n"/>
       <c r="J264" s="19" t="n"/>
+      <c r="K264" s="19" t="n"/>
     </row>
     <row r="265" ht="18" customHeight="1" s="42">
       <c r="A265" s="11" t="n"/>
@@ -7889,6 +8188,7 @@
       <c r="H265" s="11" t="n"/>
       <c r="I265" s="34" t="n"/>
       <c r="J265" s="11" t="n"/>
+      <c r="K265" s="11" t="n"/>
     </row>
     <row r="266" ht="18" customHeight="1" s="42">
       <c r="A266" s="19" t="n"/>
@@ -7901,6 +8201,7 @@
       <c r="H266" s="19" t="n"/>
       <c r="I266" s="33" t="n"/>
       <c r="J266" s="19" t="n"/>
+      <c r="K266" s="19" t="n"/>
     </row>
     <row r="267" ht="18" customHeight="1" s="42">
       <c r="A267" s="11" t="n"/>
@@ -7913,6 +8214,7 @@
       <c r="H267" s="11" t="n"/>
       <c r="I267" s="34" t="n"/>
       <c r="J267" s="11" t="n"/>
+      <c r="K267" s="11" t="n"/>
     </row>
     <row r="268" ht="18" customHeight="1" s="42">
       <c r="A268" s="19" t="n"/>
@@ -7925,6 +8227,7 @@
       <c r="H268" s="19" t="n"/>
       <c r="I268" s="33" t="n"/>
       <c r="J268" s="19" t="n"/>
+      <c r="K268" s="19" t="n"/>
     </row>
     <row r="269" ht="18" customHeight="1" s="42">
       <c r="A269" s="11" t="n"/>
@@ -7937,6 +8240,7 @@
       <c r="H269" s="11" t="n"/>
       <c r="I269" s="34" t="n"/>
       <c r="J269" s="11" t="n"/>
+      <c r="K269" s="11" t="n"/>
     </row>
     <row r="270" ht="18" customHeight="1" s="42">
       <c r="A270" s="19" t="n"/>
@@ -7949,6 +8253,7 @@
       <c r="H270" s="19" t="n"/>
       <c r="I270" s="33" t="n"/>
       <c r="J270" s="19" t="n"/>
+      <c r="K270" s="19" t="n"/>
     </row>
     <row r="271" ht="18" customHeight="1" s="42">
       <c r="A271" s="11" t="n"/>
@@ -7961,6 +8266,7 @@
       <c r="H271" s="11" t="n"/>
       <c r="I271" s="34" t="n"/>
       <c r="J271" s="11" t="n"/>
+      <c r="K271" s="11" t="n"/>
     </row>
     <row r="272" ht="18" customHeight="1" s="42">
       <c r="A272" s="19" t="n"/>
@@ -7973,6 +8279,7 @@
       <c r="H272" s="19" t="n"/>
       <c r="I272" s="33" t="n"/>
       <c r="J272" s="19" t="n"/>
+      <c r="K272" s="19" t="n"/>
     </row>
     <row r="273" ht="18" customHeight="1" s="42">
       <c r="A273" s="11" t="n"/>
@@ -7985,6 +8292,7 @@
       <c r="H273" s="11" t="n"/>
       <c r="I273" s="34" t="n"/>
       <c r="J273" s="11" t="n"/>
+      <c r="K273" s="11" t="n"/>
     </row>
     <row r="274" ht="18" customHeight="1" s="42">
       <c r="A274" s="19" t="n"/>
@@ -7997,6 +8305,7 @@
       <c r="H274" s="19" t="n"/>
       <c r="I274" s="33" t="n"/>
       <c r="J274" s="19" t="n"/>
+      <c r="K274" s="19" t="n"/>
     </row>
     <row r="275" ht="18" customHeight="1" s="42">
       <c r="A275" s="11" t="n"/>
@@ -8009,6 +8318,7 @@
       <c r="H275" s="11" t="n"/>
       <c r="I275" s="34" t="n"/>
       <c r="J275" s="11" t="n"/>
+      <c r="K275" s="11" t="n"/>
     </row>
     <row r="276" ht="18" customHeight="1" s="42">
       <c r="A276" s="19" t="n"/>
@@ -8021,6 +8331,7 @@
       <c r="H276" s="19" t="n"/>
       <c r="I276" s="33" t="n"/>
       <c r="J276" s="19" t="n"/>
+      <c r="K276" s="19" t="n"/>
     </row>
     <row r="277" ht="18" customHeight="1" s="42">
       <c r="A277" s="11" t="n"/>
@@ -8033,6 +8344,7 @@
       <c r="H277" s="11" t="n"/>
       <c r="I277" s="34" t="n"/>
       <c r="J277" s="11" t="n"/>
+      <c r="K277" s="11" t="n"/>
     </row>
     <row r="278" ht="18" customHeight="1" s="42">
       <c r="A278" s="19" t="n"/>
@@ -8045,6 +8357,7 @@
       <c r="H278" s="19" t="n"/>
       <c r="I278" s="33" t="n"/>
       <c r="J278" s="19" t="n"/>
+      <c r="K278" s="19" t="n"/>
     </row>
     <row r="279" ht="18" customHeight="1" s="42">
       <c r="A279" s="11" t="n"/>
@@ -8057,6 +8370,7 @@
       <c r="H279" s="11" t="n"/>
       <c r="I279" s="34" t="n"/>
       <c r="J279" s="11" t="n"/>
+      <c r="K279" s="11" t="n"/>
     </row>
     <row r="280" ht="18" customHeight="1" s="42">
       <c r="A280" s="19" t="n"/>
@@ -8069,6 +8383,7 @@
       <c r="H280" s="19" t="n"/>
       <c r="I280" s="33" t="n"/>
       <c r="J280" s="19" t="n"/>
+      <c r="K280" s="19" t="n"/>
     </row>
     <row r="281" ht="18" customHeight="1" s="42">
       <c r="A281" s="11" t="n"/>
@@ -8081,6 +8396,7 @@
       <c r="H281" s="11" t="n"/>
       <c r="I281" s="34" t="n"/>
       <c r="J281" s="11" t="n"/>
+      <c r="K281" s="11" t="n"/>
     </row>
     <row r="282" ht="18" customHeight="1" s="42">
       <c r="A282" s="19" t="n"/>
@@ -8093,6 +8409,7 @@
       <c r="H282" s="19" t="n"/>
       <c r="I282" s="33" t="n"/>
       <c r="J282" s="19" t="n"/>
+      <c r="K282" s="19" t="n"/>
     </row>
     <row r="283" ht="18" customHeight="1" s="42">
       <c r="A283" s="11" t="n"/>
@@ -8105,6 +8422,7 @@
       <c r="H283" s="11" t="n"/>
       <c r="I283" s="34" t="n"/>
       <c r="J283" s="11" t="n"/>
+      <c r="K283" s="11" t="n"/>
     </row>
     <row r="284" ht="18" customHeight="1" s="42">
       <c r="A284" s="19" t="n"/>
@@ -8117,6 +8435,7 @@
       <c r="H284" s="19" t="n"/>
       <c r="I284" s="33" t="n"/>
       <c r="J284" s="19" t="n"/>
+      <c r="K284" s="19" t="n"/>
     </row>
     <row r="285" ht="18" customHeight="1" s="42">
       <c r="A285" s="11" t="n"/>
@@ -8129,6 +8448,7 @@
       <c r="H285" s="11" t="n"/>
       <c r="I285" s="34" t="n"/>
       <c r="J285" s="11" t="n"/>
+      <c r="K285" s="11" t="n"/>
     </row>
     <row r="286" ht="18" customHeight="1" s="42">
       <c r="A286" s="19" t="n"/>
@@ -8141,6 +8461,7 @@
       <c r="H286" s="19" t="n"/>
       <c r="I286" s="33" t="n"/>
       <c r="J286" s="19" t="n"/>
+      <c r="K286" s="19" t="n"/>
     </row>
     <row r="287" ht="18" customHeight="1" s="42">
       <c r="A287" s="11" t="n"/>
@@ -8153,6 +8474,7 @@
       <c r="H287" s="11" t="n"/>
       <c r="I287" s="34" t="n"/>
       <c r="J287" s="11" t="n"/>
+      <c r="K287" s="11" t="n"/>
     </row>
     <row r="288" ht="18" customHeight="1" s="42">
       <c r="A288" s="19" t="n"/>
@@ -8165,6 +8487,7 @@
       <c r="H288" s="19" t="n"/>
       <c r="I288" s="33" t="n"/>
       <c r="J288" s="19" t="n"/>
+      <c r="K288" s="19" t="n"/>
     </row>
     <row r="289" ht="18" customHeight="1" s="42">
       <c r="A289" s="11" t="n"/>
@@ -8177,6 +8500,7 @@
       <c r="H289" s="11" t="n"/>
       <c r="I289" s="34" t="n"/>
       <c r="J289" s="11" t="n"/>
+      <c r="K289" s="11" t="n"/>
     </row>
     <row r="290" ht="18" customHeight="1" s="42">
       <c r="A290" s="19" t="n"/>
@@ -8189,6 +8513,7 @@
       <c r="H290" s="19" t="n"/>
       <c r="I290" s="33" t="n"/>
       <c r="J290" s="19" t="n"/>
+      <c r="K290" s="19" t="n"/>
     </row>
     <row r="291" ht="18" customHeight="1" s="42">
       <c r="A291" s="11" t="n"/>
@@ -8201,6 +8526,7 @@
       <c r="H291" s="11" t="n"/>
       <c r="I291" s="34" t="n"/>
       <c r="J291" s="11" t="n"/>
+      <c r="K291" s="11" t="n"/>
     </row>
     <row r="292" ht="18" customHeight="1" s="42">
       <c r="A292" s="19" t="n"/>
@@ -8213,6 +8539,7 @@
       <c r="H292" s="19" t="n"/>
       <c r="I292" s="33" t="n"/>
       <c r="J292" s="19" t="n"/>
+      <c r="K292" s="19" t="n"/>
     </row>
     <row r="293" ht="18" customHeight="1" s="42">
       <c r="A293" s="11" t="n"/>
@@ -8225,6 +8552,7 @@
       <c r="H293" s="11" t="n"/>
       <c r="I293" s="34" t="n"/>
       <c r="J293" s="11" t="n"/>
+      <c r="K293" s="11" t="n"/>
     </row>
     <row r="294" ht="18" customHeight="1" s="42">
       <c r="A294" s="19" t="n"/>
@@ -8237,6 +8565,7 @@
       <c r="H294" s="19" t="n"/>
       <c r="I294" s="33" t="n"/>
       <c r="J294" s="19" t="n"/>
+      <c r="K294" s="19" t="n"/>
     </row>
     <row r="295" ht="18" customHeight="1" s="42">
       <c r="A295" s="11" t="n"/>
@@ -8249,6 +8578,7 @@
       <c r="H295" s="11" t="n"/>
       <c r="I295" s="34" t="n"/>
       <c r="J295" s="11" t="n"/>
+      <c r="K295" s="11" t="n"/>
     </row>
     <row r="296" ht="18" customHeight="1" s="42">
       <c r="A296" s="19" t="n"/>
@@ -8261,6 +8591,7 @@
       <c r="H296" s="19" t="n"/>
       <c r="I296" s="33" t="n"/>
       <c r="J296" s="19" t="n"/>
+      <c r="K296" s="19" t="n"/>
     </row>
     <row r="297" ht="18" customHeight="1" s="42">
       <c r="A297" s="11" t="n"/>
@@ -8273,6 +8604,7 @@
       <c r="H297" s="11" t="n"/>
       <c r="I297" s="34" t="n"/>
       <c r="J297" s="11" t="n"/>
+      <c r="K297" s="11" t="n"/>
     </row>
     <row r="298" ht="18" customHeight="1" s="42">
       <c r="A298" s="19" t="n"/>
@@ -8285,6 +8617,7 @@
       <c r="H298" s="19" t="n"/>
       <c r="I298" s="33" t="n"/>
       <c r="J298" s="19" t="n"/>
+      <c r="K298" s="19" t="n"/>
     </row>
     <row r="299" ht="18" customHeight="1" s="42">
       <c r="A299" s="11" t="n"/>
@@ -8297,6 +8630,7 @@
       <c r="H299" s="11" t="n"/>
       <c r="I299" s="34" t="n"/>
       <c r="J299" s="11" t="n"/>
+      <c r="K299" s="11" t="n"/>
     </row>
     <row r="300" ht="18" customHeight="1" s="42">
       <c r="A300" s="19" t="n"/>
@@ -8309,6 +8643,7 @@
       <c r="H300" s="19" t="n"/>
       <c r="I300" s="33" t="n"/>
       <c r="J300" s="19" t="n"/>
+      <c r="K300" s="19" t="n"/>
     </row>
     <row r="301" ht="18" customHeight="1" s="42">
       <c r="A301" s="11" t="n"/>
@@ -8321,6 +8656,7 @@
       <c r="H301" s="11" t="n"/>
       <c r="I301" s="34" t="n"/>
       <c r="J301" s="11" t="n"/>
+      <c r="K301" s="11" t="n"/>
     </row>
     <row r="302" ht="18" customHeight="1" s="42">
       <c r="A302" s="19" t="n"/>
@@ -8333,6 +8669,7 @@
       <c r="H302" s="19" t="n"/>
       <c r="I302" s="33" t="n"/>
       <c r="J302" s="19" t="n"/>
+      <c r="K302" s="19" t="n"/>
     </row>
     <row r="303" ht="18" customHeight="1" s="42">
       <c r="A303" s="11" t="n"/>
@@ -8345,6 +8682,7 @@
       <c r="H303" s="11" t="n"/>
       <c r="I303" s="34" t="n"/>
       <c r="J303" s="11" t="n"/>
+      <c r="K303" s="11" t="n"/>
     </row>
     <row r="304" ht="18" customHeight="1" s="42">
       <c r="A304" s="19" t="n"/>
@@ -8357,6 +8695,7 @@
       <c r="H304" s="19" t="n"/>
       <c r="I304" s="33" t="n"/>
       <c r="J304" s="19" t="n"/>
+      <c r="K304" s="19" t="n"/>
     </row>
     <row r="305" ht="18" customHeight="1" s="42">
       <c r="A305" s="11" t="n"/>
@@ -8369,6 +8708,7 @@
       <c r="H305" s="11" t="n"/>
       <c r="I305" s="34" t="n"/>
       <c r="J305" s="11" t="n"/>
+      <c r="K305" s="11" t="n"/>
     </row>
     <row r="306" ht="18" customHeight="1" s="42">
       <c r="A306" s="19" t="n"/>
@@ -8381,6 +8721,7 @@
       <c r="H306" s="19" t="n"/>
       <c r="I306" s="33" t="n"/>
       <c r="J306" s="19" t="n"/>
+      <c r="K306" s="19" t="n"/>
     </row>
     <row r="307" ht="18" customHeight="1" s="42">
       <c r="A307" s="11" t="n"/>
@@ -8393,6 +8734,7 @@
       <c r="H307" s="11" t="n"/>
       <c r="I307" s="34" t="n"/>
       <c r="J307" s="11" t="n"/>
+      <c r="K307" s="11" t="n"/>
     </row>
     <row r="308" ht="18" customHeight="1" s="42">
       <c r="A308" s="19" t="n"/>
@@ -8405,6 +8747,7 @@
       <c r="H308" s="19" t="n"/>
       <c r="I308" s="33" t="n"/>
       <c r="J308" s="19" t="n"/>
+      <c r="K308" s="19" t="n"/>
     </row>
     <row r="309" ht="18" customHeight="1" s="42">
       <c r="A309" s="11" t="n"/>
@@ -8417,6 +8760,7 @@
       <c r="H309" s="11" t="n"/>
       <c r="I309" s="34" t="n"/>
       <c r="J309" s="11" t="n"/>
+      <c r="K309" s="11" t="n"/>
     </row>
     <row r="310" ht="18" customHeight="1" s="42">
       <c r="A310" s="19" t="n"/>
@@ -8429,6 +8773,7 @@
       <c r="H310" s="19" t="n"/>
       <c r="I310" s="33" t="n"/>
       <c r="J310" s="19" t="n"/>
+      <c r="K310" s="19" t="n"/>
     </row>
     <row r="311" ht="18" customHeight="1" s="42">
       <c r="A311" s="11" t="n"/>
@@ -8441,6 +8786,7 @@
       <c r="H311" s="11" t="n"/>
       <c r="I311" s="34" t="n"/>
       <c r="J311" s="11" t="n"/>
+      <c r="K311" s="11" t="n"/>
     </row>
     <row r="312" ht="18" customHeight="1" s="42">
       <c r="A312" s="19" t="n"/>
@@ -8453,6 +8799,7 @@
       <c r="H312" s="19" t="n"/>
       <c r="I312" s="33" t="n"/>
       <c r="J312" s="19" t="n"/>
+      <c r="K312" s="19" t="n"/>
     </row>
     <row r="313" ht="18" customHeight="1" s="42">
       <c r="A313" s="11" t="n"/>
@@ -8465,6 +8812,7 @@
       <c r="H313" s="11" t="n"/>
       <c r="I313" s="34" t="n"/>
       <c r="J313" s="11" t="n"/>
+      <c r="K313" s="11" t="n"/>
     </row>
     <row r="314" ht="18" customHeight="1" s="42">
       <c r="A314" s="19" t="n"/>
@@ -8477,6 +8825,7 @@
       <c r="H314" s="19" t="n"/>
       <c r="I314" s="33" t="n"/>
       <c r="J314" s="19" t="n"/>
+      <c r="K314" s="19" t="n"/>
     </row>
     <row r="315" ht="18" customHeight="1" s="42">
       <c r="A315" s="11" t="n"/>
@@ -8489,6 +8838,7 @@
       <c r="H315" s="11" t="n"/>
       <c r="I315" s="34" t="n"/>
       <c r="J315" s="11" t="n"/>
+      <c r="K315" s="11" t="n"/>
     </row>
     <row r="316" ht="18" customHeight="1" s="42">
       <c r="A316" s="19" t="n"/>
@@ -8501,6 +8851,7 @@
       <c r="H316" s="19" t="n"/>
       <c r="I316" s="33" t="n"/>
       <c r="J316" s="19" t="n"/>
+      <c r="K316" s="19" t="n"/>
     </row>
     <row r="317" ht="18" customHeight="1" s="42">
       <c r="A317" s="11" t="n"/>
@@ -8513,6 +8864,7 @@
       <c r="H317" s="11" t="n"/>
       <c r="I317" s="34" t="n"/>
       <c r="J317" s="11" t="n"/>
+      <c r="K317" s="11" t="n"/>
     </row>
     <row r="318" ht="18" customHeight="1" s="42">
       <c r="A318" s="19" t="n"/>
@@ -8525,6 +8877,7 @@
       <c r="H318" s="19" t="n"/>
       <c r="I318" s="33" t="n"/>
       <c r="J318" s="19" t="n"/>
+      <c r="K318" s="19" t="n"/>
     </row>
     <row r="319" ht="18" customHeight="1" s="42">
       <c r="A319" s="11" t="n"/>
@@ -8537,6 +8890,7 @@
       <c r="H319" s="11" t="n"/>
       <c r="I319" s="34" t="n"/>
       <c r="J319" s="11" t="n"/>
+      <c r="K319" s="11" t="n"/>
     </row>
     <row r="320" ht="18" customHeight="1" s="42">
       <c r="A320" s="19" t="n"/>
@@ -8549,6 +8903,7 @@
       <c r="H320" s="19" t="n"/>
       <c r="I320" s="33" t="n"/>
       <c r="J320" s="19" t="n"/>
+      <c r="K320" s="19" t="n"/>
     </row>
     <row r="321" ht="18" customHeight="1" s="42">
       <c r="A321" s="11" t="n"/>
@@ -8561,6 +8916,7 @@
       <c r="H321" s="11" t="n"/>
       <c r="I321" s="34" t="n"/>
       <c r="J321" s="11" t="n"/>
+      <c r="K321" s="11" t="n"/>
     </row>
     <row r="322" ht="18" customHeight="1" s="42">
       <c r="A322" s="19" t="n"/>
@@ -8573,6 +8929,7 @@
       <c r="H322" s="19" t="n"/>
       <c r="I322" s="33" t="n"/>
       <c r="J322" s="19" t="n"/>
+      <c r="K322" s="19" t="n"/>
     </row>
     <row r="323" ht="18" customHeight="1" s="42">
       <c r="A323" s="11" t="n"/>
@@ -8585,6 +8942,7 @@
       <c r="H323" s="11" t="n"/>
       <c r="I323" s="34" t="n"/>
       <c r="J323" s="11" t="n"/>
+      <c r="K323" s="11" t="n"/>
     </row>
     <row r="324" ht="18" customHeight="1" s="42">
       <c r="A324" s="19" t="n"/>
@@ -8597,6 +8955,7 @@
       <c r="H324" s="19" t="n"/>
       <c r="I324" s="33" t="n"/>
       <c r="J324" s="19" t="n"/>
+      <c r="K324" s="19" t="n"/>
     </row>
     <row r="325" ht="18" customHeight="1" s="42">
       <c r="A325" s="11" t="n"/>
@@ -8609,6 +8968,7 @@
       <c r="H325" s="11" t="n"/>
       <c r="I325" s="34" t="n"/>
       <c r="J325" s="11" t="n"/>
+      <c r="K325" s="11" t="n"/>
     </row>
     <row r="326" ht="18" customHeight="1" s="42">
       <c r="A326" s="19" t="n"/>
@@ -8621,6 +8981,7 @@
       <c r="H326" s="19" t="n"/>
       <c r="I326" s="33" t="n"/>
       <c r="J326" s="19" t="n"/>
+      <c r="K326" s="19" t="n"/>
     </row>
     <row r="327" ht="18" customHeight="1" s="42">
       <c r="A327" s="11" t="n"/>
@@ -8633,6 +8994,7 @@
       <c r="H327" s="11" t="n"/>
       <c r="I327" s="34" t="n"/>
       <c r="J327" s="11" t="n"/>
+      <c r="K327" s="11" t="n"/>
     </row>
     <row r="328" ht="18" customHeight="1" s="42">
       <c r="A328" s="19" t="n"/>
@@ -8645,6 +9007,7 @@
       <c r="H328" s="19" t="n"/>
       <c r="I328" s="33" t="n"/>
       <c r="J328" s="19" t="n"/>
+      <c r="K328" s="19" t="n"/>
     </row>
     <row r="329" ht="18" customHeight="1" s="42">
       <c r="A329" s="11" t="n"/>
@@ -8657,6 +9020,7 @@
       <c r="H329" s="11" t="n"/>
       <c r="I329" s="34" t="n"/>
       <c r="J329" s="11" t="n"/>
+      <c r="K329" s="11" t="n"/>
     </row>
     <row r="330" ht="18" customHeight="1" s="42">
       <c r="A330" s="19" t="n"/>
@@ -8669,6 +9033,7 @@
       <c r="H330" s="19" t="n"/>
       <c r="I330" s="33" t="n"/>
       <c r="J330" s="19" t="n"/>
+      <c r="K330" s="19" t="n"/>
     </row>
     <row r="331" ht="18" customHeight="1" s="42">
       <c r="A331" s="11" t="n"/>
@@ -8681,6 +9046,7 @@
       <c r="H331" s="11" t="n"/>
       <c r="I331" s="34" t="n"/>
       <c r="J331" s="11" t="n"/>
+      <c r="K331" s="11" t="n"/>
     </row>
     <row r="332" ht="18" customHeight="1" s="42">
       <c r="A332" s="19" t="n"/>
@@ -8693,6 +9059,7 @@
       <c r="H332" s="19" t="n"/>
       <c r="I332" s="33" t="n"/>
       <c r="J332" s="19" t="n"/>
+      <c r="K332" s="19" t="n"/>
     </row>
     <row r="333" ht="18" customHeight="1" s="42">
       <c r="A333" s="11" t="n"/>
@@ -8705,6 +9072,7 @@
       <c r="H333" s="11" t="n"/>
       <c r="I333" s="34" t="n"/>
       <c r="J333" s="11" t="n"/>
+      <c r="K333" s="11" t="n"/>
     </row>
     <row r="334" ht="18" customHeight="1" s="42">
       <c r="A334" s="19" t="n"/>
@@ -8717,6 +9085,7 @@
       <c r="H334" s="19" t="n"/>
       <c r="I334" s="33" t="n"/>
       <c r="J334" s="19" t="n"/>
+      <c r="K334" s="19" t="n"/>
     </row>
     <row r="335" ht="18" customHeight="1" s="42">
       <c r="A335" s="11" t="n"/>
@@ -8729,6 +9098,7 @@
       <c r="H335" s="11" t="n"/>
       <c r="I335" s="34" t="n"/>
       <c r="J335" s="11" t="n"/>
+      <c r="K335" s="11" t="n"/>
     </row>
     <row r="336" ht="18" customHeight="1" s="42">
       <c r="A336" s="19" t="n"/>
@@ -8741,6 +9111,7 @@
       <c r="H336" s="19" t="n"/>
       <c r="I336" s="33" t="n"/>
       <c r="J336" s="19" t="n"/>
+      <c r="K336" s="19" t="n"/>
     </row>
     <row r="337" ht="18" customHeight="1" s="42">
       <c r="A337" s="11" t="n"/>
@@ -8753,6 +9124,7 @@
       <c r="H337" s="11" t="n"/>
       <c r="I337" s="34" t="n"/>
       <c r="J337" s="11" t="n"/>
+      <c r="K337" s="11" t="n"/>
     </row>
     <row r="338" ht="18" customHeight="1" s="42">
       <c r="A338" s="19" t="n"/>
@@ -8765,6 +9137,7 @@
       <c r="H338" s="19" t="n"/>
       <c r="I338" s="33" t="n"/>
       <c r="J338" s="19" t="n"/>
+      <c r="K338" s="19" t="n"/>
     </row>
     <row r="339" ht="18" customHeight="1" s="42">
       <c r="A339" s="11" t="n"/>
@@ -8777,6 +9150,7 @@
       <c r="H339" s="11" t="n"/>
       <c r="I339" s="34" t="n"/>
       <c r="J339" s="11" t="n"/>
+      <c r="K339" s="11" t="n"/>
     </row>
     <row r="340" ht="18" customHeight="1" s="42">
       <c r="A340" s="19" t="n"/>
@@ -8789,6 +9163,7 @@
       <c r="H340" s="19" t="n"/>
       <c r="I340" s="33" t="n"/>
       <c r="J340" s="19" t="n"/>
+      <c r="K340" s="19" t="n"/>
     </row>
     <row r="341" ht="18" customHeight="1" s="42">
       <c r="A341" s="11" t="n"/>
@@ -8801,6 +9176,7 @@
       <c r="H341" s="11" t="n"/>
       <c r="I341" s="34" t="n"/>
       <c r="J341" s="11" t="n"/>
+      <c r="K341" s="11" t="n"/>
     </row>
     <row r="342" ht="18" customHeight="1" s="42">
       <c r="A342" s="19" t="n"/>
@@ -8813,6 +9189,7 @@
       <c r="H342" s="19" t="n"/>
       <c r="I342" s="33" t="n"/>
       <c r="J342" s="19" t="n"/>
+      <c r="K342" s="19" t="n"/>
     </row>
     <row r="343" ht="18" customHeight="1" s="42">
       <c r="A343" s="11" t="n"/>
@@ -8825,6 +9202,7 @@
       <c r="H343" s="11" t="n"/>
       <c r="I343" s="34" t="n"/>
       <c r="J343" s="11" t="n"/>
+      <c r="K343" s="11" t="n"/>
     </row>
     <row r="344" ht="18" customHeight="1" s="42">
       <c r="A344" s="19" t="n"/>
@@ -8837,6 +9215,7 @@
       <c r="H344" s="19" t="n"/>
       <c r="I344" s="33" t="n"/>
       <c r="J344" s="19" t="n"/>
+      <c r="K344" s="19" t="n"/>
     </row>
     <row r="345" ht="18" customHeight="1" s="42">
       <c r="A345" s="11" t="n"/>
@@ -8849,6 +9228,7 @@
       <c r="H345" s="11" t="n"/>
       <c r="I345" s="34" t="n"/>
       <c r="J345" s="11" t="n"/>
+      <c r="K345" s="11" t="n"/>
     </row>
     <row r="346" ht="18" customHeight="1" s="42">
       <c r="A346" s="19" t="n"/>
@@ -8861,6 +9241,7 @@
       <c r="H346" s="19" t="n"/>
       <c r="I346" s="33" t="n"/>
       <c r="J346" s="19" t="n"/>
+      <c r="K346" s="19" t="n"/>
     </row>
     <row r="347" ht="18" customHeight="1" s="42">
       <c r="A347" s="11" t="n"/>
@@ -8873,6 +9254,7 @@
       <c r="H347" s="11" t="n"/>
       <c r="I347" s="34" t="n"/>
       <c r="J347" s="11" t="n"/>
+      <c r="K347" s="11" t="n"/>
     </row>
     <row r="348" ht="18" customHeight="1" s="42">
       <c r="A348" s="19" t="n"/>
@@ -8885,6 +9267,7 @@
       <c r="H348" s="19" t="n"/>
       <c r="I348" s="33" t="n"/>
       <c r="J348" s="19" t="n"/>
+      <c r="K348" s="19" t="n"/>
     </row>
     <row r="349" ht="18" customHeight="1" s="42">
       <c r="A349" s="11" t="n"/>
@@ -8897,6 +9280,7 @@
       <c r="H349" s="11" t="n"/>
       <c r="I349" s="34" t="n"/>
       <c r="J349" s="11" t="n"/>
+      <c r="K349" s="11" t="n"/>
     </row>
     <row r="350" ht="18" customHeight="1" s="42">
       <c r="A350" s="19" t="n"/>
@@ -8909,6 +9293,7 @@
       <c r="H350" s="19" t="n"/>
       <c r="I350" s="33" t="n"/>
       <c r="J350" s="19" t="n"/>
+      <c r="K350" s="19" t="n"/>
     </row>
     <row r="351" ht="18" customHeight="1" s="42">
       <c r="A351" s="11" t="n"/>
@@ -8921,6 +9306,7 @@
       <c r="H351" s="11" t="n"/>
       <c r="I351" s="34" t="n"/>
       <c r="J351" s="11" t="n"/>
+      <c r="K351" s="11" t="n"/>
     </row>
     <row r="352" ht="18" customHeight="1" s="42">
       <c r="A352" s="19" t="n"/>
@@ -8933,6 +9319,7 @@
       <c r="H352" s="19" t="n"/>
       <c r="I352" s="33" t="n"/>
       <c r="J352" s="19" t="n"/>
+      <c r="K352" s="19" t="n"/>
     </row>
     <row r="353" ht="18" customHeight="1" s="42">
       <c r="A353" s="11" t="n"/>
@@ -8945,6 +9332,7 @@
       <c r="H353" s="11" t="n"/>
       <c r="I353" s="34" t="n"/>
       <c r="J353" s="11" t="n"/>
+      <c r="K353" s="11" t="n"/>
     </row>
     <row r="354" ht="18" customHeight="1" s="42">
       <c r="A354" s="19" t="n"/>
@@ -8957,6 +9345,7 @@
       <c r="H354" s="19" t="n"/>
       <c r="I354" s="33" t="n"/>
       <c r="J354" s="19" t="n"/>
+      <c r="K354" s="19" t="n"/>
     </row>
     <row r="355" ht="18" customHeight="1" s="42">
       <c r="A355" s="11" t="n"/>
@@ -8969,6 +9358,7 @@
       <c r="H355" s="11" t="n"/>
       <c r="I355" s="34" t="n"/>
       <c r="J355" s="11" t="n"/>
+      <c r="K355" s="11" t="n"/>
     </row>
     <row r="356" ht="18" customHeight="1" s="42">
       <c r="A356" s="19" t="n"/>
@@ -8981,6 +9371,7 @@
       <c r="H356" s="19" t="n"/>
       <c r="I356" s="33" t="n"/>
       <c r="J356" s="19" t="n"/>
+      <c r="K356" s="19" t="n"/>
     </row>
     <row r="357" ht="18" customHeight="1" s="42">
       <c r="A357" s="11" t="n"/>
@@ -8993,6 +9384,7 @@
       <c r="H357" s="11" t="n"/>
       <c r="I357" s="34" t="n"/>
       <c r="J357" s="11" t="n"/>
+      <c r="K357" s="11" t="n"/>
     </row>
     <row r="358" ht="18" customHeight="1" s="42">
       <c r="A358" s="19" t="n"/>
@@ -9005,6 +9397,7 @@
       <c r="H358" s="19" t="n"/>
       <c r="I358" s="33" t="n"/>
       <c r="J358" s="19" t="n"/>
+      <c r="K358" s="19" t="n"/>
     </row>
     <row r="359" ht="18" customHeight="1" s="42">
       <c r="A359" s="11" t="n"/>
@@ -9017,6 +9410,7 @@
       <c r="H359" s="11" t="n"/>
       <c r="I359" s="34" t="n"/>
       <c r="J359" s="11" t="n"/>
+      <c r="K359" s="11" t="n"/>
     </row>
     <row r="360" ht="18" customHeight="1" s="42">
       <c r="A360" s="19" t="n"/>
@@ -9029,6 +9423,7 @@
       <c r="H360" s="19" t="n"/>
       <c r="I360" s="33" t="n"/>
       <c r="J360" s="19" t="n"/>
+      <c r="K360" s="19" t="n"/>
     </row>
     <row r="361" ht="18" customHeight="1" s="42">
       <c r="A361" s="11" t="n"/>
@@ -9041,6 +9436,7 @@
       <c r="H361" s="11" t="n"/>
       <c r="I361" s="34" t="n"/>
       <c r="J361" s="11" t="n"/>
+      <c r="K361" s="11" t="n"/>
     </row>
     <row r="362" ht="18" customHeight="1" s="42">
       <c r="A362" s="19" t="n"/>
@@ -9053,6 +9449,7 @@
       <c r="H362" s="19" t="n"/>
       <c r="I362" s="33" t="n"/>
       <c r="J362" s="19" t="n"/>
+      <c r="K362" s="19" t="n"/>
     </row>
     <row r="363" ht="18" customHeight="1" s="42">
       <c r="A363" s="11" t="n"/>
@@ -9065,6 +9462,7 @@
       <c r="H363" s="11" t="n"/>
       <c r="I363" s="34" t="n"/>
       <c r="J363" s="11" t="n"/>
+      <c r="K363" s="11" t="n"/>
     </row>
     <row r="364" ht="18" customHeight="1" s="42">
       <c r="A364" s="19" t="n"/>
@@ -9077,6 +9475,7 @@
       <c r="H364" s="19" t="n"/>
       <c r="I364" s="33" t="n"/>
       <c r="J364" s="19" t="n"/>
+      <c r="K364" s="19" t="n"/>
     </row>
     <row r="365" ht="18" customHeight="1" s="42">
       <c r="A365" s="11" t="n"/>
@@ -9089,6 +9488,7 @@
       <c r="H365" s="11" t="n"/>
       <c r="I365" s="34" t="n"/>
       <c r="J365" s="11" t="n"/>
+      <c r="K365" s="11" t="n"/>
     </row>
     <row r="366" ht="18" customHeight="1" s="42">
       <c r="A366" s="19" t="n"/>
@@ -9101,6 +9501,7 @@
       <c r="H366" s="19" t="n"/>
       <c r="I366" s="33" t="n"/>
       <c r="J366" s="19" t="n"/>
+      <c r="K366" s="19" t="n"/>
     </row>
     <row r="367" ht="18" customHeight="1" s="42">
       <c r="A367" s="11" t="n"/>
@@ -9113,6 +9514,7 @@
       <c r="H367" s="11" t="n"/>
       <c r="I367" s="34" t="n"/>
       <c r="J367" s="11" t="n"/>
+      <c r="K367" s="11" t="n"/>
     </row>
     <row r="368" ht="18" customHeight="1" s="42">
       <c r="A368" s="19" t="n"/>
@@ -9125,6 +9527,7 @@
       <c r="H368" s="19" t="n"/>
       <c r="I368" s="33" t="n"/>
       <c r="J368" s="19" t="n"/>
+      <c r="K368" s="19" t="n"/>
     </row>
     <row r="369" ht="18" customHeight="1" s="42">
       <c r="A369" s="11" t="n"/>
@@ -9137,6 +9540,7 @@
       <c r="H369" s="11" t="n"/>
       <c r="I369" s="34" t="n"/>
       <c r="J369" s="11" t="n"/>
+      <c r="K369" s="11" t="n"/>
     </row>
     <row r="370" ht="18" customHeight="1" s="42">
       <c r="A370" s="19" t="n"/>
@@ -9149,6 +9553,7 @@
       <c r="H370" s="19" t="n"/>
       <c r="I370" s="33" t="n"/>
       <c r="J370" s="19" t="n"/>
+      <c r="K370" s="19" t="n"/>
     </row>
     <row r="371" ht="18" customHeight="1" s="42">
       <c r="A371" s="11" t="n"/>
@@ -9161,6 +9566,7 @@
       <c r="H371" s="11" t="n"/>
       <c r="I371" s="34" t="n"/>
       <c r="J371" s="11" t="n"/>
+      <c r="K371" s="11" t="n"/>
     </row>
     <row r="372" ht="18" customHeight="1" s="42">
       <c r="A372" s="19" t="n"/>
@@ -9173,6 +9579,7 @@
       <c r="H372" s="19" t="n"/>
       <c r="I372" s="33" t="n"/>
       <c r="J372" s="19" t="n"/>
+      <c r="K372" s="19" t="n"/>
     </row>
     <row r="373" ht="18" customHeight="1" s="42">
       <c r="A373" s="11" t="n"/>
@@ -9185,6 +9592,7 @@
       <c r="H373" s="11" t="n"/>
       <c r="I373" s="34" t="n"/>
       <c r="J373" s="11" t="n"/>
+      <c r="K373" s="11" t="n"/>
     </row>
     <row r="374" ht="18" customHeight="1" s="42">
       <c r="A374" s="19" t="n"/>
@@ -9197,6 +9605,7 @@
       <c r="H374" s="19" t="n"/>
       <c r="I374" s="33" t="n"/>
       <c r="J374" s="19" t="n"/>
+      <c r="K374" s="19" t="n"/>
     </row>
     <row r="375" ht="18" customHeight="1" s="42">
       <c r="A375" s="11" t="n"/>
@@ -9209,6 +9618,7 @@
       <c r="H375" s="11" t="n"/>
       <c r="I375" s="34" t="n"/>
       <c r="J375" s="11" t="n"/>
+      <c r="K375" s="11" t="n"/>
     </row>
     <row r="376" ht="18" customHeight="1" s="42">
       <c r="A376" s="19" t="n"/>
@@ -9221,6 +9631,7 @@
       <c r="H376" s="19" t="n"/>
       <c r="I376" s="33" t="n"/>
       <c r="J376" s="19" t="n"/>
+      <c r="K376" s="19" t="n"/>
     </row>
     <row r="377" ht="18" customHeight="1" s="42">
       <c r="A377" s="11" t="n"/>
@@ -9233,6 +9644,7 @@
       <c r="H377" s="11" t="n"/>
       <c r="I377" s="34" t="n"/>
       <c r="J377" s="11" t="n"/>
+      <c r="K377" s="11" t="n"/>
     </row>
     <row r="378" ht="18" customHeight="1" s="42">
       <c r="A378" s="19" t="n"/>
@@ -9245,6 +9657,7 @@
       <c r="H378" s="19" t="n"/>
       <c r="I378" s="33" t="n"/>
       <c r="J378" s="19" t="n"/>
+      <c r="K378" s="19" t="n"/>
     </row>
     <row r="379" ht="18" customHeight="1" s="42">
       <c r="A379" s="11" t="n"/>
@@ -9257,6 +9670,7 @@
       <c r="H379" s="11" t="n"/>
       <c r="I379" s="34" t="n"/>
       <c r="J379" s="11" t="n"/>
+      <c r="K379" s="11" t="n"/>
     </row>
     <row r="380" ht="18" customHeight="1" s="42">
       <c r="A380" s="19" t="n"/>
@@ -9269,6 +9683,7 @@
       <c r="H380" s="19" t="n"/>
       <c r="I380" s="33" t="n"/>
       <c r="J380" s="19" t="n"/>
+      <c r="K380" s="19" t="n"/>
     </row>
     <row r="381" ht="18" customHeight="1" s="42">
       <c r="A381" s="11" t="n"/>
@@ -9281,6 +9696,7 @@
       <c r="H381" s="11" t="n"/>
       <c r="I381" s="34" t="n"/>
       <c r="J381" s="11" t="n"/>
+      <c r="K381" s="11" t="n"/>
     </row>
     <row r="382" ht="18" customHeight="1" s="42">
       <c r="A382" s="19" t="n"/>
@@ -9293,6 +9709,7 @@
       <c r="H382" s="19" t="n"/>
       <c r="I382" s="33" t="n"/>
       <c r="J382" s="19" t="n"/>
+      <c r="K382" s="19" t="n"/>
     </row>
     <row r="383" ht="18" customHeight="1" s="42">
       <c r="A383" s="11" t="n"/>
@@ -9305,6 +9722,7 @@
       <c r="H383" s="11" t="n"/>
       <c r="I383" s="34" t="n"/>
       <c r="J383" s="11" t="n"/>
+      <c r="K383" s="11" t="n"/>
     </row>
     <row r="384" ht="18" customHeight="1" s="42">
       <c r="A384" s="19" t="n"/>
@@ -9317,6 +9735,7 @@
       <c r="H384" s="19" t="n"/>
       <c r="I384" s="33" t="n"/>
       <c r="J384" s="19" t="n"/>
+      <c r="K384" s="19" t="n"/>
     </row>
     <row r="385" ht="18" customHeight="1" s="42">
       <c r="A385" s="11" t="n"/>
@@ -9329,6 +9748,7 @@
       <c r="H385" s="11" t="n"/>
       <c r="I385" s="34" t="n"/>
       <c r="J385" s="11" t="n"/>
+      <c r="K385" s="11" t="n"/>
     </row>
     <row r="386" ht="18" customHeight="1" s="42">
       <c r="A386" s="19" t="n"/>
@@ -9341,6 +9761,7 @@
       <c r="H386" s="19" t="n"/>
       <c r="I386" s="33" t="n"/>
       <c r="J386" s="19" t="n"/>
+      <c r="K386" s="19" t="n"/>
     </row>
     <row r="387" ht="18" customHeight="1" s="42">
       <c r="A387" s="11" t="n"/>
@@ -9353,6 +9774,7 @@
       <c r="H387" s="11" t="n"/>
       <c r="I387" s="34" t="n"/>
       <c r="J387" s="11" t="n"/>
+      <c r="K387" s="11" t="n"/>
     </row>
     <row r="388" ht="18" customHeight="1" s="42">
       <c r="A388" s="19" t="n"/>
@@ -9365,6 +9787,7 @@
       <c r="H388" s="19" t="n"/>
       <c r="I388" s="33" t="n"/>
       <c r="J388" s="19" t="n"/>
+      <c r="K388" s="19" t="n"/>
     </row>
     <row r="389" ht="18" customHeight="1" s="42">
       <c r="A389" s="11" t="n"/>
@@ -9377,6 +9800,7 @@
       <c r="H389" s="11" t="n"/>
       <c r="I389" s="34" t="n"/>
       <c r="J389" s="11" t="n"/>
+      <c r="K389" s="11" t="n"/>
     </row>
     <row r="390" ht="18" customHeight="1" s="42">
       <c r="A390" s="19" t="n"/>
@@ -9389,6 +9813,7 @@
       <c r="H390" s="19" t="n"/>
       <c r="I390" s="33" t="n"/>
       <c r="J390" s="19" t="n"/>
+      <c r="K390" s="19" t="n"/>
     </row>
     <row r="391" ht="18" customHeight="1" s="42">
       <c r="A391" s="11" t="n"/>
@@ -9401,6 +9826,7 @@
       <c r="H391" s="11" t="n"/>
       <c r="I391" s="34" t="n"/>
       <c r="J391" s="11" t="n"/>
+      <c r="K391" s="11" t="n"/>
     </row>
     <row r="392" ht="18" customHeight="1" s="42">
       <c r="A392" s="19" t="n"/>
@@ -9413,6 +9839,7 @@
       <c r="H392" s="19" t="n"/>
       <c r="I392" s="33" t="n"/>
       <c r="J392" s="19" t="n"/>
+      <c r="K392" s="19" t="n"/>
     </row>
     <row r="393" ht="18" customHeight="1" s="42">
       <c r="A393" s="11" t="n"/>
@@ -9425,6 +9852,7 @@
       <c r="H393" s="11" t="n"/>
       <c r="I393" s="34" t="n"/>
       <c r="J393" s="11" t="n"/>
+      <c r="K393" s="11" t="n"/>
     </row>
     <row r="394" ht="18" customHeight="1" s="42">
       <c r="A394" s="19" t="n"/>
@@ -9437,6 +9865,7 @@
       <c r="H394" s="19" t="n"/>
       <c r="I394" s="33" t="n"/>
       <c r="J394" s="19" t="n"/>
+      <c r="K394" s="19" t="n"/>
     </row>
     <row r="395" ht="18" customHeight="1" s="42">
       <c r="A395" s="11" t="n"/>
@@ -9449,6 +9878,7 @@
       <c r="H395" s="11" t="n"/>
       <c r="I395" s="34" t="n"/>
       <c r="J395" s="11" t="n"/>
+      <c r="K395" s="11" t="n"/>
     </row>
     <row r="396" ht="18" customHeight="1" s="42">
       <c r="A396" s="19" t="n"/>
@@ -9461,6 +9891,7 @@
       <c r="H396" s="19" t="n"/>
       <c r="I396" s="33" t="n"/>
       <c r="J396" s="19" t="n"/>
+      <c r="K396" s="19" t="n"/>
     </row>
     <row r="397" ht="18" customHeight="1" s="42">
       <c r="A397" s="11" t="n"/>
@@ -9473,6 +9904,7 @@
       <c r="H397" s="11" t="n"/>
       <c r="I397" s="34" t="n"/>
       <c r="J397" s="11" t="n"/>
+      <c r="K397" s="11" t="n"/>
     </row>
     <row r="398" ht="18" customHeight="1" s="42">
       <c r="A398" s="19" t="n"/>
@@ -9485,6 +9917,7 @@
       <c r="H398" s="19" t="n"/>
       <c r="I398" s="33" t="n"/>
       <c r="J398" s="19" t="n"/>
+      <c r="K398" s="19" t="n"/>
     </row>
     <row r="399" ht="18" customHeight="1" s="42">
       <c r="A399" s="11" t="n"/>
@@ -9497,6 +9930,7 @@
       <c r="H399" s="11" t="n"/>
       <c r="I399" s="34" t="n"/>
       <c r="J399" s="11" t="n"/>
+      <c r="K399" s="11" t="n"/>
     </row>
     <row r="400" ht="18" customHeight="1" s="42">
       <c r="A400" s="19" t="n"/>
@@ -9509,6 +9943,7 @@
       <c r="H400" s="19" t="n"/>
       <c r="I400" s="33" t="n"/>
       <c r="J400" s="19" t="n"/>
+      <c r="K400" s="19" t="n"/>
     </row>
     <row r="401" ht="18" customHeight="1" s="42">
       <c r="A401" s="11" t="n"/>
@@ -9521,6 +9956,7 @@
       <c r="H401" s="11" t="n"/>
       <c r="I401" s="34" t="n"/>
       <c r="J401" s="11" t="n"/>
+      <c r="K401" s="11" t="n"/>
     </row>
     <row r="402" ht="18" customHeight="1" s="42">
       <c r="A402" s="19" t="n"/>
@@ -9533,6 +9969,7 @@
       <c r="H402" s="19" t="n"/>
       <c r="I402" s="33" t="n"/>
       <c r="J402" s="19" t="n"/>
+      <c r="K402" s="19" t="n"/>
     </row>
     <row r="403" ht="18" customHeight="1" s="42">
       <c r="A403" s="11" t="n"/>
@@ -9545,6 +9982,7 @@
       <c r="H403" s="11" t="n"/>
       <c r="I403" s="34" t="n"/>
       <c r="J403" s="11" t="n"/>
+      <c r="K403" s="11" t="n"/>
     </row>
     <row r="404" ht="18" customHeight="1" s="42">
       <c r="A404" s="19" t="n"/>
@@ -9557,6 +9995,7 @@
       <c r="H404" s="19" t="n"/>
       <c r="I404" s="33" t="n"/>
       <c r="J404" s="19" t="n"/>
+      <c r="K404" s="19" t="n"/>
     </row>
     <row r="405" ht="18" customHeight="1" s="42">
       <c r="A405" s="11" t="n"/>
@@ -9569,6 +10008,7 @@
       <c r="H405" s="11" t="n"/>
       <c r="I405" s="34" t="n"/>
       <c r="J405" s="11" t="n"/>
+      <c r="K405" s="11" t="n"/>
     </row>
     <row r="406" ht="18" customHeight="1" s="42">
       <c r="A406" s="19" t="n"/>
@@ -9581,6 +10021,7 @@
       <c r="H406" s="19" t="n"/>
       <c r="I406" s="33" t="n"/>
       <c r="J406" s="19" t="n"/>
+      <c r="K406" s="19" t="n"/>
     </row>
     <row r="407" ht="18" customHeight="1" s="42">
       <c r="A407" s="11" t="n"/>
@@ -9593,6 +10034,7 @@
       <c r="H407" s="11" t="n"/>
       <c r="I407" s="34" t="n"/>
       <c r="J407" s="11" t="n"/>
+      <c r="K407" s="11" t="n"/>
     </row>
     <row r="408" ht="18" customHeight="1" s="42">
       <c r="A408" s="19" t="n"/>
@@ -9605,6 +10047,7 @@
       <c r="H408" s="19" t="n"/>
       <c r="I408" s="33" t="n"/>
       <c r="J408" s="19" t="n"/>
+      <c r="K408" s="19" t="n"/>
     </row>
     <row r="409" ht="18" customHeight="1" s="42">
       <c r="A409" s="11" t="n"/>
@@ -9617,6 +10060,7 @@
       <c r="H409" s="11" t="n"/>
       <c r="I409" s="34" t="n"/>
       <c r="J409" s="11" t="n"/>
+      <c r="K409" s="11" t="n"/>
     </row>
     <row r="410" ht="18" customHeight="1" s="42">
       <c r="A410" s="19" t="n"/>
@@ -9629,6 +10073,7 @@
       <c r="H410" s="19" t="n"/>
       <c r="I410" s="33" t="n"/>
       <c r="J410" s="19" t="n"/>
+      <c r="K410" s="19" t="n"/>
     </row>
     <row r="411" ht="18" customHeight="1" s="42">
       <c r="A411" s="11" t="n"/>
@@ -9641,6 +10086,7 @@
       <c r="H411" s="11" t="n"/>
       <c r="I411" s="34" t="n"/>
       <c r="J411" s="11" t="n"/>
+      <c r="K411" s="11" t="n"/>
     </row>
     <row r="412" ht="18" customHeight="1" s="42">
       <c r="A412" s="19" t="n"/>
@@ -9653,6 +10099,7 @@
       <c r="H412" s="19" t="n"/>
       <c r="I412" s="33" t="n"/>
       <c r="J412" s="19" t="n"/>
+      <c r="K412" s="19" t="n"/>
     </row>
     <row r="413" ht="18" customHeight="1" s="42">
       <c r="A413" s="11" t="n"/>
@@ -9665,6 +10112,7 @@
       <c r="H413" s="11" t="n"/>
       <c r="I413" s="34" t="n"/>
       <c r="J413" s="11" t="n"/>
+      <c r="K413" s="11" t="n"/>
     </row>
     <row r="414" ht="18" customHeight="1" s="42">
       <c r="A414" s="19" t="n"/>
@@ -9677,6 +10125,7 @@
       <c r="H414" s="19" t="n"/>
       <c r="I414" s="33" t="n"/>
       <c r="J414" s="19" t="n"/>
+      <c r="K414" s="19" t="n"/>
     </row>
     <row r="415" ht="18" customHeight="1" s="42">
       <c r="A415" s="11" t="n"/>
@@ -9689,6 +10138,7 @@
       <c r="H415" s="11" t="n"/>
       <c r="I415" s="34" t="n"/>
       <c r="J415" s="11" t="n"/>
+      <c r="K415" s="11" t="n"/>
     </row>
     <row r="416" ht="18" customHeight="1" s="42">
       <c r="A416" s="19" t="n"/>
@@ -9701,6 +10151,7 @@
       <c r="H416" s="19" t="n"/>
       <c r="I416" s="33" t="n"/>
       <c r="J416" s="19" t="n"/>
+      <c r="K416" s="19" t="n"/>
     </row>
     <row r="417" ht="18" customHeight="1" s="42">
       <c r="A417" s="11" t="n"/>
@@ -9713,6 +10164,7 @@
       <c r="H417" s="11" t="n"/>
       <c r="I417" s="34" t="n"/>
       <c r="J417" s="11" t="n"/>
+      <c r="K417" s="11" t="n"/>
     </row>
     <row r="418" ht="18" customHeight="1" s="42">
       <c r="A418" s="19" t="n"/>
@@ -9725,6 +10177,7 @@
       <c r="H418" s="19" t="n"/>
       <c r="I418" s="33" t="n"/>
       <c r="J418" s="19" t="n"/>
+      <c r="K418" s="19" t="n"/>
     </row>
     <row r="419" ht="18" customHeight="1" s="42">
       <c r="A419" s="11" t="n"/>
@@ -9737,6 +10190,7 @@
       <c r="H419" s="11" t="n"/>
       <c r="I419" s="34" t="n"/>
       <c r="J419" s="11" t="n"/>
+      <c r="K419" s="11" t="n"/>
     </row>
     <row r="420" ht="18" customHeight="1" s="42">
       <c r="A420" s="19" t="n"/>
@@ -9749,6 +10203,7 @@
       <c r="H420" s="19" t="n"/>
       <c r="I420" s="33" t="n"/>
       <c r="J420" s="19" t="n"/>
+      <c r="K420" s="19" t="n"/>
     </row>
     <row r="421" ht="18" customHeight="1" s="42">
       <c r="A421" s="11" t="n"/>
@@ -9761,6 +10216,7 @@
       <c r="H421" s="11" t="n"/>
       <c r="I421" s="34" t="n"/>
       <c r="J421" s="11" t="n"/>
+      <c r="K421" s="11" t="n"/>
     </row>
     <row r="422" ht="18" customHeight="1" s="42">
       <c r="A422" s="19" t="n"/>
@@ -9773,6 +10229,7 @@
       <c r="H422" s="19" t="n"/>
       <c r="I422" s="33" t="n"/>
       <c r="J422" s="19" t="n"/>
+      <c r="K422" s="19" t="n"/>
     </row>
     <row r="423" ht="18" customHeight="1" s="42">
       <c r="A423" s="11" t="n"/>
@@ -9785,6 +10242,7 @@
       <c r="H423" s="11" t="n"/>
       <c r="I423" s="34" t="n"/>
       <c r="J423" s="11" t="n"/>
+      <c r="K423" s="11" t="n"/>
     </row>
     <row r="424" ht="18" customHeight="1" s="42">
       <c r="A424" s="19" t="n"/>
@@ -9797,6 +10255,7 @@
       <c r="H424" s="19" t="n"/>
       <c r="I424" s="33" t="n"/>
       <c r="J424" s="19" t="n"/>
+      <c r="K424" s="19" t="n"/>
     </row>
     <row r="425" ht="18" customHeight="1" s="42">
       <c r="A425" s="11" t="n"/>
@@ -9809,6 +10268,7 @@
       <c r="H425" s="11" t="n"/>
       <c r="I425" s="34" t="n"/>
       <c r="J425" s="11" t="n"/>
+      <c r="K425" s="11" t="n"/>
     </row>
     <row r="426" ht="18" customHeight="1" s="42">
       <c r="A426" s="19" t="n"/>
@@ -9821,6 +10281,7 @@
       <c r="H426" s="19" t="n"/>
       <c r="I426" s="33" t="n"/>
       <c r="J426" s="19" t="n"/>
+      <c r="K426" s="19" t="n"/>
     </row>
     <row r="427" ht="18" customHeight="1" s="42">
       <c r="A427" s="11" t="n"/>
@@ -9833,6 +10294,7 @@
       <c r="H427" s="11" t="n"/>
       <c r="I427" s="34" t="n"/>
       <c r="J427" s="11" t="n"/>
+      <c r="K427" s="11" t="n"/>
     </row>
     <row r="428" ht="18" customHeight="1" s="42">
       <c r="A428" s="19" t="n"/>
@@ -9845,6 +10307,7 @@
       <c r="H428" s="19" t="n"/>
       <c r="I428" s="33" t="n"/>
       <c r="J428" s="19" t="n"/>
+      <c r="K428" s="19" t="n"/>
     </row>
     <row r="429" ht="18" customHeight="1" s="42">
       <c r="A429" s="11" t="n"/>
@@ -9857,6 +10320,7 @@
       <c r="H429" s="11" t="n"/>
       <c r="I429" s="34" t="n"/>
       <c r="J429" s="11" t="n"/>
+      <c r="K429" s="11" t="n"/>
     </row>
     <row r="430" ht="18" customHeight="1" s="42">
       <c r="A430" s="19" t="n"/>
@@ -9869,6 +10333,7 @@
       <c r="H430" s="19" t="n"/>
       <c r="I430" s="33" t="n"/>
       <c r="J430" s="19" t="n"/>
+      <c r="K430" s="19" t="n"/>
     </row>
     <row r="431" ht="18" customHeight="1" s="42">
       <c r="A431" s="11" t="n"/>
@@ -9881,6 +10346,7 @@
       <c r="H431" s="11" t="n"/>
       <c r="I431" s="34" t="n"/>
       <c r="J431" s="11" t="n"/>
+      <c r="K431" s="11" t="n"/>
     </row>
     <row r="432" ht="18" customHeight="1" s="42">
       <c r="A432" s="19" t="n"/>
@@ -9893,6 +10359,7 @@
       <c r="H432" s="19" t="n"/>
       <c r="I432" s="33" t="n"/>
       <c r="J432" s="19" t="n"/>
+      <c r="K432" s="19" t="n"/>
     </row>
     <row r="433" ht="18" customHeight="1" s="42">
       <c r="A433" s="11" t="n"/>
@@ -9905,6 +10372,7 @@
       <c r="H433" s="11" t="n"/>
       <c r="I433" s="34" t="n"/>
       <c r="J433" s="11" t="n"/>
+      <c r="K433" s="11" t="n"/>
     </row>
     <row r="434" ht="18" customHeight="1" s="42">
       <c r="A434" s="19" t="n"/>
@@ -9917,6 +10385,7 @@
       <c r="H434" s="19" t="n"/>
       <c r="I434" s="33" t="n"/>
       <c r="J434" s="19" t="n"/>
+      <c r="K434" s="19" t="n"/>
     </row>
     <row r="435" ht="18" customHeight="1" s="42">
       <c r="A435" s="11" t="n"/>
@@ -9929,6 +10398,7 @@
       <c r="H435" s="11" t="n"/>
       <c r="I435" s="34" t="n"/>
       <c r="J435" s="11" t="n"/>
+      <c r="K435" s="11" t="n"/>
     </row>
     <row r="436" ht="18" customHeight="1" s="42">
       <c r="A436" s="19" t="n"/>
@@ -9941,6 +10411,7 @@
       <c r="H436" s="19" t="n"/>
       <c r="I436" s="33" t="n"/>
       <c r="J436" s="19" t="n"/>
+      <c r="K436" s="19" t="n"/>
     </row>
     <row r="437" ht="18" customHeight="1" s="42">
       <c r="A437" s="11" t="n"/>
@@ -9953,6 +10424,7 @@
       <c r="H437" s="11" t="n"/>
       <c r="I437" s="34" t="n"/>
       <c r="J437" s="11" t="n"/>
+      <c r="K437" s="11" t="n"/>
     </row>
     <row r="438" ht="18" customHeight="1" s="42">
       <c r="A438" s="19" t="n"/>
@@ -9965,6 +10437,7 @@
       <c r="H438" s="19" t="n"/>
       <c r="I438" s="33" t="n"/>
       <c r="J438" s="19" t="n"/>
+      <c r="K438" s="19" t="n"/>
     </row>
     <row r="439" ht="18" customHeight="1" s="42">
       <c r="A439" s="11" t="n"/>
@@ -9977,6 +10450,7 @@
       <c r="H439" s="11" t="n"/>
       <c r="I439" s="34" t="n"/>
       <c r="J439" s="11" t="n"/>
+      <c r="K439" s="11" t="n"/>
     </row>
     <row r="440" ht="18" customHeight="1" s="42">
       <c r="A440" s="19" t="n"/>
@@ -9989,6 +10463,7 @@
       <c r="H440" s="19" t="n"/>
       <c r="I440" s="33" t="n"/>
       <c r="J440" s="19" t="n"/>
+      <c r="K440" s="19" t="n"/>
     </row>
     <row r="441" ht="18" customHeight="1" s="42">
       <c r="A441" s="11" t="n"/>
@@ -10001,6 +10476,7 @@
       <c r="H441" s="11" t="n"/>
       <c r="I441" s="34" t="n"/>
       <c r="J441" s="11" t="n"/>
+      <c r="K441" s="11" t="n"/>
     </row>
     <row r="442" ht="18" customHeight="1" s="42">
       <c r="A442" s="19" t="n"/>
@@ -10013,6 +10489,7 @@
       <c r="H442" s="19" t="n"/>
       <c r="I442" s="33" t="n"/>
       <c r="J442" s="19" t="n"/>
+      <c r="K442" s="19" t="n"/>
     </row>
     <row r="443" ht="18" customHeight="1" s="42">
       <c r="A443" s="11" t="n"/>
@@ -10025,6 +10502,7 @@
       <c r="H443" s="11" t="n"/>
       <c r="I443" s="34" t="n"/>
       <c r="J443" s="11" t="n"/>
+      <c r="K443" s="11" t="n"/>
     </row>
     <row r="444" ht="18" customHeight="1" s="42">
       <c r="A444" s="19" t="n"/>
@@ -10037,6 +10515,7 @@
       <c r="H444" s="19" t="n"/>
       <c r="I444" s="33" t="n"/>
       <c r="J444" s="19" t="n"/>
+      <c r="K444" s="19" t="n"/>
     </row>
     <row r="445" ht="18" customHeight="1" s="42">
       <c r="A445" s="11" t="n"/>
@@ -10049,6 +10528,7 @@
       <c r="H445" s="11" t="n"/>
       <c r="I445" s="34" t="n"/>
       <c r="J445" s="11" t="n"/>
+      <c r="K445" s="11" t="n"/>
     </row>
     <row r="446" ht="18" customHeight="1" s="42">
       <c r="A446" s="19" t="n"/>
@@ -10061,6 +10541,7 @@
       <c r="H446" s="19" t="n"/>
       <c r="I446" s="33" t="n"/>
       <c r="J446" s="19" t="n"/>
+      <c r="K446" s="19" t="n"/>
     </row>
     <row r="447" ht="18" customHeight="1" s="42">
       <c r="A447" s="11" t="n"/>
@@ -10073,6 +10554,7 @@
       <c r="H447" s="11" t="n"/>
       <c r="I447" s="34" t="n"/>
       <c r="J447" s="11" t="n"/>
+      <c r="K447" s="11" t="n"/>
     </row>
     <row r="448" ht="18" customHeight="1" s="42">
       <c r="A448" s="19" t="n"/>
@@ -10085,6 +10567,7 @@
       <c r="H448" s="19" t="n"/>
       <c r="I448" s="33" t="n"/>
       <c r="J448" s="19" t="n"/>
+      <c r="K448" s="19" t="n"/>
     </row>
     <row r="449" ht="18" customHeight="1" s="42">
       <c r="A449" s="11" t="n"/>
@@ -10097,6 +10580,7 @@
       <c r="H449" s="11" t="n"/>
       <c r="I449" s="34" t="n"/>
       <c r="J449" s="11" t="n"/>
+      <c r="K449" s="11" t="n"/>
     </row>
     <row r="450" ht="18" customHeight="1" s="42">
       <c r="A450" s="19" t="n"/>
@@ -10109,6 +10593,7 @@
       <c r="H450" s="19" t="n"/>
       <c r="I450" s="33" t="n"/>
       <c r="J450" s="19" t="n"/>
+      <c r="K450" s="19" t="n"/>
     </row>
     <row r="451" ht="18" customHeight="1" s="42">
       <c r="A451" s="11" t="n"/>
@@ -10121,6 +10606,7 @@
       <c r="H451" s="11" t="n"/>
       <c r="I451" s="34" t="n"/>
       <c r="J451" s="11" t="n"/>
+      <c r="K451" s="11" t="n"/>
     </row>
     <row r="452" ht="18" customHeight="1" s="42">
       <c r="A452" s="19" t="n"/>
@@ -10133,6 +10619,7 @@
       <c r="H452" s="19" t="n"/>
       <c r="I452" s="33" t="n"/>
       <c r="J452" s="19" t="n"/>
+      <c r="K452" s="19" t="n"/>
     </row>
     <row r="453" ht="18" customHeight="1" s="42">
       <c r="A453" s="11" t="n"/>
@@ -10145,6 +10632,7 @@
       <c r="H453" s="11" t="n"/>
       <c r="I453" s="34" t="n"/>
       <c r="J453" s="11" t="n"/>
+      <c r="K453" s="11" t="n"/>
     </row>
     <row r="454" ht="18" customHeight="1" s="42">
       <c r="A454" s="19" t="n"/>
@@ -10157,6 +10645,7 @@
       <c r="H454" s="19" t="n"/>
       <c r="I454" s="33" t="n"/>
       <c r="J454" s="19" t="n"/>
+      <c r="K454" s="19" t="n"/>
     </row>
     <row r="455" ht="18" customHeight="1" s="42">
       <c r="A455" s="11" t="n"/>
@@ -10169,6 +10658,7 @@
       <c r="H455" s="11" t="n"/>
       <c r="I455" s="34" t="n"/>
       <c r="J455" s="11" t="n"/>
+      <c r="K455" s="11" t="n"/>
     </row>
     <row r="456" ht="18" customHeight="1" s="42">
       <c r="A456" s="19" t="n"/>
@@ -10181,6 +10671,7 @@
       <c r="H456" s="19" t="n"/>
       <c r="I456" s="33" t="n"/>
       <c r="J456" s="19" t="n"/>
+      <c r="K456" s="19" t="n"/>
     </row>
     <row r="457" ht="18" customHeight="1" s="42">
       <c r="A457" s="11" t="n"/>
@@ -10193,6 +10684,7 @@
       <c r="H457" s="11" t="n"/>
       <c r="I457" s="34" t="n"/>
       <c r="J457" s="11" t="n"/>
+      <c r="K457" s="11" t="n"/>
     </row>
     <row r="458" ht="18" customHeight="1" s="42">
       <c r="A458" s="19" t="n"/>
@@ -10205,6 +10697,7 @@
       <c r="H458" s="19" t="n"/>
       <c r="I458" s="33" t="n"/>
       <c r="J458" s="19" t="n"/>
+      <c r="K458" s="19" t="n"/>
     </row>
     <row r="459" ht="18" customHeight="1" s="42">
       <c r="A459" s="11" t="n"/>
@@ -10217,6 +10710,7 @@
       <c r="H459" s="11" t="n"/>
       <c r="I459" s="34" t="n"/>
       <c r="J459" s="11" t="n"/>
+      <c r="K459" s="11" t="n"/>
     </row>
     <row r="460" ht="18" customHeight="1" s="42">
       <c r="A460" s="19" t="n"/>
@@ -10229,6 +10723,7 @@
       <c r="H460" s="19" t="n"/>
       <c r="I460" s="33" t="n"/>
       <c r="J460" s="19" t="n"/>
+      <c r="K460" s="19" t="n"/>
     </row>
     <row r="461" ht="18" customHeight="1" s="42">
       <c r="A461" s="11" t="n"/>
@@ -10241,6 +10736,7 @@
       <c r="H461" s="11" t="n"/>
       <c r="I461" s="34" t="n"/>
       <c r="J461" s="11" t="n"/>
+      <c r="K461" s="11" t="n"/>
     </row>
     <row r="462" ht="18" customHeight="1" s="42">
       <c r="A462" s="19" t="n"/>
@@ -10253,6 +10749,7 @@
       <c r="H462" s="19" t="n"/>
       <c r="I462" s="33" t="n"/>
       <c r="J462" s="19" t="n"/>
+      <c r="K462" s="19" t="n"/>
     </row>
     <row r="463" ht="18" customHeight="1" s="42">
       <c r="A463" s="11" t="n"/>
@@ -10265,6 +10762,7 @@
       <c r="H463" s="11" t="n"/>
       <c r="I463" s="34" t="n"/>
       <c r="J463" s="11" t="n"/>
+      <c r="K463" s="11" t="n"/>
     </row>
     <row r="464" ht="18" customHeight="1" s="42">
       <c r="A464" s="19" t="n"/>
@@ -10277,6 +10775,7 @@
       <c r="H464" s="19" t="n"/>
       <c r="I464" s="33" t="n"/>
       <c r="J464" s="19" t="n"/>
+      <c r="K464" s="19" t="n"/>
     </row>
     <row r="465" ht="18" customHeight="1" s="42">
       <c r="A465" s="11" t="n"/>
@@ -10289,6 +10788,7 @@
       <c r="H465" s="11" t="n"/>
       <c r="I465" s="34" t="n"/>
       <c r="J465" s="11" t="n"/>
+      <c r="K465" s="11" t="n"/>
     </row>
     <row r="466" ht="18" customHeight="1" s="42">
       <c r="A466" s="19" t="n"/>
@@ -10301,6 +10801,7 @@
       <c r="H466" s="19" t="n"/>
       <c r="I466" s="33" t="n"/>
       <c r="J466" s="19" t="n"/>
+      <c r="K466" s="19" t="n"/>
     </row>
     <row r="467" ht="18" customHeight="1" s="42">
       <c r="A467" s="11" t="n"/>
@@ -10313,6 +10814,7 @@
       <c r="H467" s="11" t="n"/>
       <c r="I467" s="34" t="n"/>
       <c r="J467" s="11" t="n"/>
+      <c r="K467" s="11" t="n"/>
     </row>
     <row r="468" ht="18" customHeight="1" s="42">
       <c r="A468" s="19" t="n"/>
@@ -10325,6 +10827,7 @@
       <c r="H468" s="19" t="n"/>
       <c r="I468" s="33" t="n"/>
       <c r="J468" s="19" t="n"/>
+      <c r="K468" s="19" t="n"/>
     </row>
     <row r="469" ht="18" customHeight="1" s="42">
       <c r="A469" s="11" t="n"/>
@@ -10337,6 +10840,7 @@
       <c r="H469" s="11" t="n"/>
       <c r="I469" s="34" t="n"/>
       <c r="J469" s="11" t="n"/>
+      <c r="K469" s="11" t="n"/>
     </row>
     <row r="470" ht="18" customHeight="1" s="42">
       <c r="A470" s="19" t="n"/>
@@ -10349,6 +10853,7 @@
       <c r="H470" s="19" t="n"/>
       <c r="I470" s="33" t="n"/>
       <c r="J470" s="19" t="n"/>
+      <c r="K470" s="19" t="n"/>
     </row>
     <row r="471" ht="18" customHeight="1" s="42">
       <c r="A471" s="11" t="n"/>
@@ -10361,6 +10866,7 @@
       <c r="H471" s="11" t="n"/>
       <c r="I471" s="34" t="n"/>
       <c r="J471" s="11" t="n"/>
+      <c r="K471" s="11" t="n"/>
     </row>
     <row r="472" ht="18" customHeight="1" s="42">
       <c r="A472" s="19" t="n"/>
@@ -10373,6 +10879,7 @@
       <c r="H472" s="19" t="n"/>
       <c r="I472" s="33" t="n"/>
       <c r="J472" s="19" t="n"/>
+      <c r="K472" s="19" t="n"/>
     </row>
     <row r="473" ht="18" customHeight="1" s="42">
       <c r="A473" s="11" t="n"/>
@@ -10385,6 +10892,7 @@
       <c r="H473" s="11" t="n"/>
       <c r="I473" s="34" t="n"/>
       <c r="J473" s="11" t="n"/>
+      <c r="K473" s="11" t="n"/>
     </row>
     <row r="474" ht="18" customHeight="1" s="42">
       <c r="A474" s="19" t="n"/>
@@ -10397,6 +10905,7 @@
       <c r="H474" s="19" t="n"/>
       <c r="I474" s="33" t="n"/>
       <c r="J474" s="19" t="n"/>
+      <c r="K474" s="19" t="n"/>
     </row>
     <row r="475" ht="18" customHeight="1" s="42">
       <c r="A475" s="11" t="n"/>
@@ -10409,6 +10918,7 @@
       <c r="H475" s="11" t="n"/>
       <c r="I475" s="34" t="n"/>
       <c r="J475" s="11" t="n"/>
+      <c r="K475" s="11" t="n"/>
     </row>
     <row r="476" ht="18" customHeight="1" s="42">
       <c r="A476" s="19" t="n"/>
@@ -10421,6 +10931,7 @@
       <c r="H476" s="19" t="n"/>
       <c r="I476" s="33" t="n"/>
       <c r="J476" s="19" t="n"/>
+      <c r="K476" s="19" t="n"/>
     </row>
     <row r="477" ht="18" customHeight="1" s="42">
       <c r="A477" s="11" t="n"/>
@@ -10433,6 +10944,7 @@
       <c r="H477" s="11" t="n"/>
       <c r="I477" s="34" t="n"/>
       <c r="J477" s="11" t="n"/>
+      <c r="K477" s="11" t="n"/>
     </row>
     <row r="478" ht="18" customHeight="1" s="42">
       <c r="A478" s="19" t="n"/>
@@ -10445,6 +10957,7 @@
       <c r="H478" s="19" t="n"/>
       <c r="I478" s="33" t="n"/>
       <c r="J478" s="19" t="n"/>
+      <c r="K478" s="19" t="n"/>
     </row>
     <row r="479" ht="18" customHeight="1" s="42">
       <c r="A479" s="11" t="n"/>
@@ -10457,6 +10970,7 @@
       <c r="H479" s="11" t="n"/>
       <c r="I479" s="34" t="n"/>
       <c r="J479" s="11" t="n"/>
+      <c r="K479" s="11" t="n"/>
     </row>
     <row r="480" ht="18" customHeight="1" s="42">
       <c r="A480" s="19" t="n"/>
@@ -10469,6 +10983,7 @@
       <c r="H480" s="19" t="n"/>
       <c r="I480" s="33" t="n"/>
       <c r="J480" s="19" t="n"/>
+      <c r="K480" s="19" t="n"/>
     </row>
     <row r="481" ht="18" customHeight="1" s="42">
       <c r="A481" s="11" t="n"/>
@@ -10481,6 +10996,7 @@
       <c r="H481" s="11" t="n"/>
       <c r="I481" s="34" t="n"/>
       <c r="J481" s="11" t="n"/>
+      <c r="K481" s="11" t="n"/>
     </row>
     <row r="482" ht="18" customHeight="1" s="42">
       <c r="A482" s="19" t="n"/>
@@ -10493,6 +11009,7 @@
       <c r="H482" s="19" t="n"/>
       <c r="I482" s="33" t="n"/>
       <c r="J482" s="19" t="n"/>
+      <c r="K482" s="19" t="n"/>
     </row>
     <row r="483" ht="18" customHeight="1" s="42">
       <c r="A483" s="11" t="n"/>
@@ -10505,6 +11022,7 @@
       <c r="H483" s="11" t="n"/>
       <c r="I483" s="34" t="n"/>
       <c r="J483" s="11" t="n"/>
+      <c r="K483" s="11" t="n"/>
     </row>
     <row r="484" ht="18" customHeight="1" s="42">
       <c r="A484" s="19" t="n"/>
@@ -10517,6 +11035,7 @@
       <c r="H484" s="19" t="n"/>
       <c r="I484" s="33" t="n"/>
       <c r="J484" s="19" t="n"/>
+      <c r="K484" s="19" t="n"/>
     </row>
     <row r="485" ht="18" customHeight="1" s="42">
       <c r="A485" s="11" t="n"/>
@@ -10529,6 +11048,7 @@
       <c r="H485" s="11" t="n"/>
       <c r="I485" s="34" t="n"/>
       <c r="J485" s="11" t="n"/>
+      <c r="K485" s="11" t="n"/>
     </row>
     <row r="486" ht="18" customHeight="1" s="42">
       <c r="A486" s="19" t="n"/>
@@ -10541,6 +11061,7 @@
       <c r="H486" s="19" t="n"/>
       <c r="I486" s="33" t="n"/>
       <c r="J486" s="19" t="n"/>
+      <c r="K486" s="19" t="n"/>
     </row>
     <row r="487" ht="18" customHeight="1" s="42">
       <c r="A487" s="11" t="n"/>
@@ -10553,6 +11074,7 @@
       <c r="H487" s="11" t="n"/>
       <c r="I487" s="34" t="n"/>
       <c r="J487" s="11" t="n"/>
+      <c r="K487" s="11" t="n"/>
     </row>
     <row r="488" ht="18" customHeight="1" s="42">
       <c r="A488" s="19" t="n"/>
@@ -10565,6 +11087,7 @@
       <c r="H488" s="19" t="n"/>
       <c r="I488" s="33" t="n"/>
       <c r="J488" s="19" t="n"/>
+      <c r="K488" s="19" t="n"/>
     </row>
     <row r="489" ht="18" customHeight="1" s="42">
       <c r="A489" s="11" t="n"/>
@@ -10577,6 +11100,7 @@
       <c r="H489" s="11" t="n"/>
       <c r="I489" s="34" t="n"/>
       <c r="J489" s="11" t="n"/>
+      <c r="K489" s="11" t="n"/>
     </row>
     <row r="490" ht="18" customHeight="1" s="42">
       <c r="A490" s="19" t="n"/>
@@ -10589,6 +11113,7 @@
       <c r="H490" s="19" t="n"/>
       <c r="I490" s="33" t="n"/>
       <c r="J490" s="19" t="n"/>
+      <c r="K490" s="19" t="n"/>
     </row>
     <row r="491" ht="18" customHeight="1" s="42">
       <c r="A491" s="11" t="n"/>
@@ -10601,6 +11126,7 @@
       <c r="H491" s="11" t="n"/>
       <c r="I491" s="34" t="n"/>
       <c r="J491" s="11" t="n"/>
+      <c r="K491" s="11" t="n"/>
     </row>
     <row r="492" ht="18" customHeight="1" s="42">
       <c r="A492" s="19" t="n"/>
@@ -10613,6 +11139,7 @@
       <c r="H492" s="19" t="n"/>
       <c r="I492" s="33" t="n"/>
       <c r="J492" s="19" t="n"/>
+      <c r="K492" s="19" t="n"/>
     </row>
     <row r="493" ht="18" customHeight="1" s="42">
       <c r="A493" s="11" t="n"/>
@@ -10625,6 +11152,7 @@
       <c r="H493" s="11" t="n"/>
       <c r="I493" s="34" t="n"/>
       <c r="J493" s="11" t="n"/>
+      <c r="K493" s="11" t="n"/>
     </row>
     <row r="494" ht="18" customHeight="1" s="42">
       <c r="A494" s="19" t="n"/>
@@ -10637,6 +11165,7 @@
       <c r="H494" s="19" t="n"/>
       <c r="I494" s="33" t="n"/>
       <c r="J494" s="19" t="n"/>
+      <c r="K494" s="19" t="n"/>
     </row>
     <row r="495" ht="18" customHeight="1" s="42">
       <c r="A495" s="11" t="n"/>
@@ -10649,6 +11178,7 @@
       <c r="H495" s="11" t="n"/>
       <c r="I495" s="34" t="n"/>
       <c r="J495" s="11" t="n"/>
+      <c r="K495" s="11" t="n"/>
     </row>
     <row r="496" ht="18" customHeight="1" s="42">
       <c r="A496" s="19" t="n"/>
@@ -10661,6 +11191,7 @@
       <c r="H496" s="19" t="n"/>
       <c r="I496" s="33" t="n"/>
       <c r="J496" s="19" t="n"/>
+      <c r="K496" s="19" t="n"/>
     </row>
     <row r="497" ht="18" customHeight="1" s="42">
       <c r="A497" s="11" t="n"/>
@@ -10673,6 +11204,7 @@
       <c r="H497" s="11" t="n"/>
       <c r="I497" s="34" t="n"/>
       <c r="J497" s="11" t="n"/>
+      <c r="K497" s="11" t="n"/>
     </row>
     <row r="498" ht="18" customHeight="1" s="42">
       <c r="A498" s="19" t="n"/>
@@ -10685,6 +11217,7 @@
       <c r="H498" s="19" t="n"/>
       <c r="I498" s="33" t="n"/>
       <c r="J498" s="19" t="n"/>
+      <c r="K498" s="19" t="n"/>
     </row>
     <row r="499" ht="18" customHeight="1" s="42">
       <c r="A499" s="11" t="n"/>
@@ -10697,6 +11230,7 @@
       <c r="H499" s="11" t="n"/>
       <c r="I499" s="34" t="n"/>
       <c r="J499" s="11" t="n"/>
+      <c r="K499" s="11" t="n"/>
     </row>
     <row r="500" ht="18" customHeight="1" s="42">
       <c r="A500" s="19" t="n"/>
@@ -10709,6 +11243,7 @@
       <c r="H500" s="19" t="n"/>
       <c r="I500" s="33" t="n"/>
       <c r="J500" s="19" t="n"/>
+      <c r="K500" s="19" t="n"/>
     </row>
     <row r="501" ht="18" customHeight="1" s="42">
       <c r="A501" s="11" t="n"/>
@@ -10721,6 +11256,7 @@
       <c r="H501" s="11" t="n"/>
       <c r="I501" s="34" t="n"/>
       <c r="J501" s="11" t="n"/>
+      <c r="K501" s="11" t="n"/>
     </row>
     <row r="502" ht="18" customHeight="1" s="42">
       <c r="A502" s="19" t="n"/>
@@ -10733,6 +11269,7 @@
       <c r="H502" s="19" t="n"/>
       <c r="I502" s="33" t="n"/>
       <c r="J502" s="19" t="n"/>
+      <c r="K502" s="19" t="n"/>
     </row>
     <row r="503" ht="18" customHeight="1" s="42">
       <c r="A503" s="11" t="n"/>
@@ -10745,6 +11282,7 @@
       <c r="H503" s="11" t="n"/>
       <c r="I503" s="34" t="n"/>
       <c r="J503" s="11" t="n"/>
+      <c r="K503" s="11" t="n"/>
     </row>
     <row r="504" ht="18" customHeight="1" s="42">
       <c r="A504" s="19" t="n"/>
@@ -10757,6 +11295,7 @@
       <c r="H504" s="19" t="n"/>
       <c r="I504" s="33" t="n"/>
       <c r="J504" s="19" t="n"/>
+      <c r="K504" s="19" t="n"/>
     </row>
     <row r="505" ht="18" customHeight="1" s="42">
       <c r="A505" s="11" t="n"/>
@@ -10769,6 +11308,7 @@
       <c r="H505" s="11" t="n"/>
       <c r="I505" s="34" t="n"/>
       <c r="J505" s="11" t="n"/>
+      <c r="K505" s="11" t="n"/>
     </row>
     <row r="506" ht="18" customHeight="1" s="42">
       <c r="A506" s="19" t="n"/>
@@ -10781,6 +11321,7 @@
       <c r="H506" s="19" t="n"/>
       <c r="I506" s="33" t="n"/>
       <c r="J506" s="19" t="n"/>
+      <c r="K506" s="19" t="n"/>
     </row>
     <row r="507" ht="18" customHeight="1" s="42">
       <c r="A507" s="11" t="n"/>
@@ -10793,6 +11334,7 @@
       <c r="H507" s="11" t="n"/>
       <c r="I507" s="34" t="n"/>
       <c r="J507" s="11" t="n"/>
+      <c r="K507" s="11" t="n"/>
     </row>
     <row r="508" ht="18" customHeight="1" s="42">
       <c r="A508" s="19" t="n"/>
@@ -10805,6 +11347,7 @@
       <c r="H508" s="19" t="n"/>
       <c r="I508" s="33" t="n"/>
       <c r="J508" s="19" t="n"/>
+      <c r="K508" s="19" t="n"/>
     </row>
     <row r="509" ht="18" customHeight="1" s="42">
       <c r="A509" s="11" t="n"/>
@@ -10817,6 +11360,7 @@
       <c r="H509" s="11" t="n"/>
       <c r="I509" s="34" t="n"/>
       <c r="J509" s="11" t="n"/>
+      <c r="K509" s="11" t="n"/>
     </row>
     <row r="510" ht="18" customHeight="1" s="42">
       <c r="A510" s="19" t="n"/>
@@ -10829,6 +11373,7 @@
       <c r="H510" s="19" t="n"/>
       <c r="I510" s="33" t="n"/>
       <c r="J510" s="19" t="n"/>
+      <c r="K510" s="19" t="n"/>
     </row>
     <row r="511" ht="18" customHeight="1" s="42">
       <c r="A511" s="11" t="n"/>
@@ -10841,6 +11386,7 @@
       <c r="H511" s="11" t="n"/>
       <c r="I511" s="34" t="n"/>
       <c r="J511" s="11" t="n"/>
+      <c r="K511" s="11" t="n"/>
     </row>
     <row r="512" ht="18" customHeight="1" s="42">
       <c r="A512" s="19" t="n"/>
@@ -10853,6 +11399,7 @@
       <c r="H512" s="19" t="n"/>
       <c r="I512" s="33" t="n"/>
       <c r="J512" s="19" t="n"/>
+      <c r="K512" s="19" t="n"/>
     </row>
     <row r="513" ht="18" customHeight="1" s="42">
       <c r="A513" s="11" t="n"/>
@@ -10865,6 +11412,7 @@
       <c r="H513" s="11" t="n"/>
       <c r="I513" s="34" t="n"/>
       <c r="J513" s="11" t="n"/>
+      <c r="K513" s="11" t="n"/>
     </row>
     <row r="514" ht="18" customHeight="1" s="42">
       <c r="A514" s="19" t="n"/>
@@ -10877,6 +11425,7 @@
       <c r="H514" s="19" t="n"/>
       <c r="I514" s="33" t="n"/>
       <c r="J514" s="19" t="n"/>
+      <c r="K514" s="19" t="n"/>
     </row>
     <row r="515" ht="18" customHeight="1" s="42">
       <c r="A515" s="11" t="n"/>
@@ -10889,6 +11438,7 @@
       <c r="H515" s="11" t="n"/>
       <c r="I515" s="34" t="n"/>
       <c r="J515" s="11" t="n"/>
+      <c r="K515" s="11" t="n"/>
     </row>
     <row r="516" ht="18" customHeight="1" s="42">
       <c r="A516" s="19" t="n"/>
@@ -10901,6 +11451,7 @@
       <c r="H516" s="19" t="n"/>
       <c r="I516" s="33" t="n"/>
       <c r="J516" s="19" t="n"/>
+      <c r="K516" s="19" t="n"/>
     </row>
     <row r="517" ht="18" customHeight="1" s="42">
       <c r="A517" s="11" t="n"/>
@@ -10913,6 +11464,7 @@
       <c r="H517" s="11" t="n"/>
       <c r="I517" s="34" t="n"/>
       <c r="J517" s="11" t="n"/>
+      <c r="K517" s="11" t="n"/>
     </row>
     <row r="518" ht="18" customHeight="1" s="42">
       <c r="A518" s="19" t="n"/>
@@ -10925,6 +11477,7 @@
       <c r="H518" s="19" t="n"/>
       <c r="I518" s="33" t="n"/>
       <c r="J518" s="19" t="n"/>
+      <c r="K518" s="19" t="n"/>
     </row>
     <row r="519" ht="18" customHeight="1" s="42">
       <c r="A519" s="11" t="n"/>
@@ -10937,6 +11490,7 @@
       <c r="H519" s="11" t="n"/>
       <c r="I519" s="34" t="n"/>
       <c r="J519" s="11" t="n"/>
+      <c r="K519" s="11" t="n"/>
     </row>
     <row r="520" ht="18" customHeight="1" s="42">
       <c r="A520" s="19" t="n"/>
@@ -10949,6 +11503,7 @@
       <c r="H520" s="19" t="n"/>
       <c r="I520" s="33" t="n"/>
       <c r="J520" s="19" t="n"/>
+      <c r="K520" s="19" t="n"/>
     </row>
     <row r="521" ht="18" customHeight="1" s="42">
       <c r="A521" s="11" t="n"/>
@@ -10961,6 +11516,7 @@
       <c r="H521" s="11" t="n"/>
       <c r="I521" s="34" t="n"/>
       <c r="J521" s="11" t="n"/>
+      <c r="K521" s="11" t="n"/>
     </row>
     <row r="522" ht="18" customHeight="1" s="42">
       <c r="A522" s="19" t="n"/>
@@ -10973,6 +11529,7 @@
       <c r="H522" s="19" t="n"/>
       <c r="I522" s="33" t="n"/>
       <c r="J522" s="19" t="n"/>
+      <c r="K522" s="19" t="n"/>
     </row>
     <row r="523" ht="18" customHeight="1" s="42">
       <c r="A523" s="11" t="n"/>
@@ -10985,6 +11542,7 @@
       <c r="H523" s="11" t="n"/>
       <c r="I523" s="34" t="n"/>
       <c r="J523" s="11" t="n"/>
+      <c r="K523" s="11" t="n"/>
     </row>
     <row r="524" ht="18" customHeight="1" s="42">
       <c r="A524" s="19" t="n"/>
@@ -10997,6 +11555,7 @@
       <c r="H524" s="19" t="n"/>
       <c r="I524" s="33" t="n"/>
       <c r="J524" s="19" t="n"/>
+      <c r="K524" s="19" t="n"/>
     </row>
     <row r="525" ht="18" customHeight="1" s="42">
       <c r="A525" s="11" t="n"/>
@@ -11009,6 +11568,7 @@
       <c r="H525" s="11" t="n"/>
       <c r="I525" s="34" t="n"/>
       <c r="J525" s="11" t="n"/>
+      <c r="K525" s="11" t="n"/>
     </row>
     <row r="526" ht="18" customHeight="1" s="42">
       <c r="A526" s="19" t="n"/>
@@ -11021,6 +11581,7 @@
       <c r="H526" s="19" t="n"/>
       <c r="I526" s="33" t="n"/>
       <c r="J526" s="19" t="n"/>
+      <c r="K526" s="19" t="n"/>
     </row>
     <row r="527" ht="18" customHeight="1" s="42">
       <c r="A527" s="11" t="n"/>
@@ -11033,6 +11594,7 @@
       <c r="H527" s="11" t="n"/>
       <c r="I527" s="34" t="n"/>
       <c r="J527" s="11" t="n"/>
+      <c r="K527" s="11" t="n"/>
     </row>
     <row r="528" ht="18" customHeight="1" s="42">
       <c r="A528" s="19" t="n"/>
@@ -11045,6 +11607,7 @@
       <c r="H528" s="19" t="n"/>
       <c r="I528" s="33" t="n"/>
       <c r="J528" s="19" t="n"/>
+      <c r="K528" s="19" t="n"/>
     </row>
     <row r="529" ht="18" customHeight="1" s="42">
       <c r="A529" s="11" t="n"/>
@@ -11057,6 +11620,7 @@
       <c r="H529" s="11" t="n"/>
       <c r="I529" s="34" t="n"/>
       <c r="J529" s="11" t="n"/>
+      <c r="K529" s="11" t="n"/>
     </row>
     <row r="530" ht="18" customHeight="1" s="42">
       <c r="A530" s="19" t="n"/>
@@ -11069,6 +11633,7 @@
       <c r="H530" s="19" t="n"/>
       <c r="I530" s="33" t="n"/>
       <c r="J530" s="19" t="n"/>
+      <c r="K530" s="19" t="n"/>
     </row>
     <row r="531" ht="18" customHeight="1" s="42">
       <c r="A531" s="11" t="n"/>
@@ -11081,6 +11646,7 @@
       <c r="H531" s="11" t="n"/>
       <c r="I531" s="34" t="n"/>
       <c r="J531" s="11" t="n"/>
+      <c r="K531" s="11" t="n"/>
     </row>
     <row r="532" ht="18" customHeight="1" s="42">
       <c r="A532" s="19" t="n"/>
@@ -11093,6 +11659,7 @@
       <c r="H532" s="19" t="n"/>
       <c r="I532" s="33" t="n"/>
       <c r="J532" s="19" t="n"/>
+      <c r="K532" s="19" t="n"/>
     </row>
     <row r="533" ht="18" customHeight="1" s="42">
       <c r="A533" s="11" t="n"/>
@@ -11105,6 +11672,7 @@
       <c r="H533" s="11" t="n"/>
       <c r="I533" s="34" t="n"/>
       <c r="J533" s="11" t="n"/>
+      <c r="K533" s="11" t="n"/>
     </row>
     <row r="534" ht="18" customHeight="1" s="42">
       <c r="A534" s="19" t="n"/>
@@ -11117,6 +11685,7 @@
       <c r="H534" s="19" t="n"/>
       <c r="I534" s="33" t="n"/>
       <c r="J534" s="19" t="n"/>
+      <c r="K534" s="19" t="n"/>
     </row>
     <row r="535" ht="18" customHeight="1" s="42">
       <c r="A535" s="11" t="n"/>
@@ -11129,6 +11698,7 @@
       <c r="H535" s="11" t="n"/>
       <c r="I535" s="34" t="n"/>
       <c r="J535" s="11" t="n"/>
+      <c r="K535" s="11" t="n"/>
     </row>
     <row r="536" ht="18" customHeight="1" s="42">
       <c r="A536" s="19" t="n"/>
@@ -11141,6 +11711,7 @@
       <c r="H536" s="19" t="n"/>
       <c r="I536" s="33" t="n"/>
       <c r="J536" s="19" t="n"/>
+      <c r="K536" s="19" t="n"/>
     </row>
     <row r="537" ht="18" customHeight="1" s="42">
       <c r="A537" s="11" t="n"/>
@@ -11153,6 +11724,7 @@
       <c r="H537" s="11" t="n"/>
       <c r="I537" s="34" t="n"/>
       <c r="J537" s="11" t="n"/>
+      <c r="K537" s="11" t="n"/>
     </row>
     <row r="538" ht="18" customHeight="1" s="42">
       <c r="A538" s="19" t="n"/>
@@ -11165,6 +11737,7 @@
       <c r="H538" s="19" t="n"/>
       <c r="I538" s="33" t="n"/>
       <c r="J538" s="19" t="n"/>
+      <c r="K538" s="19" t="n"/>
     </row>
     <row r="539" ht="18" customHeight="1" s="42">
       <c r="A539" s="11" t="n"/>
@@ -11177,6 +11750,7 @@
       <c r="H539" s="11" t="n"/>
       <c r="I539" s="34" t="n"/>
       <c r="J539" s="11" t="n"/>
+      <c r="K539" s="11" t="n"/>
     </row>
     <row r="540" ht="18" customHeight="1" s="42">
       <c r="A540" s="19" t="n"/>
@@ -11189,6 +11763,7 @@
       <c r="H540" s="19" t="n"/>
       <c r="I540" s="33" t="n"/>
       <c r="J540" s="19" t="n"/>
+      <c r="K540" s="19" t="n"/>
     </row>
     <row r="541" ht="18" customHeight="1" s="42">
       <c r="A541" s="11" t="n"/>
@@ -11201,6 +11776,7 @@
       <c r="H541" s="11" t="n"/>
       <c r="I541" s="34" t="n"/>
       <c r="J541" s="11" t="n"/>
+      <c r="K541" s="11" t="n"/>
     </row>
     <row r="542" ht="18" customHeight="1" s="42">
       <c r="A542" s="19" t="n"/>
@@ -11213,6 +11789,7 @@
       <c r="H542" s="19" t="n"/>
       <c r="I542" s="33" t="n"/>
       <c r="J542" s="19" t="n"/>
+      <c r="K542" s="19" t="n"/>
     </row>
     <row r="543" ht="18" customHeight="1" s="42">
       <c r="A543" s="11" t="n"/>
@@ -11225,6 +11802,7 @@
       <c r="H543" s="11" t="n"/>
       <c r="I543" s="34" t="n"/>
       <c r="J543" s="11" t="n"/>
+      <c r="K543" s="11" t="n"/>
     </row>
     <row r="544" ht="18" customHeight="1" s="42">
       <c r="A544" s="19" t="n"/>
@@ -11237,6 +11815,7 @@
       <c r="H544" s="19" t="n"/>
       <c r="I544" s="33" t="n"/>
       <c r="J544" s="19" t="n"/>
+      <c r="K544" s="19" t="n"/>
     </row>
     <row r="545" ht="18" customHeight="1" s="42">
       <c r="A545" s="11" t="n"/>
@@ -11249,6 +11828,7 @@
       <c r="H545" s="11" t="n"/>
       <c r="I545" s="34" t="n"/>
       <c r="J545" s="11" t="n"/>
+      <c r="K545" s="11" t="n"/>
     </row>
     <row r="546" ht="18" customHeight="1" s="42">
       <c r="A546" s="19" t="n"/>
@@ -11261,6 +11841,7 @@
       <c r="H546" s="19" t="n"/>
       <c r="I546" s="33" t="n"/>
       <c r="J546" s="19" t="n"/>
+      <c r="K546" s="19" t="n"/>
     </row>
     <row r="547" ht="18" customHeight="1" s="42">
       <c r="A547" s="11" t="n"/>
@@ -11273,6 +11854,7 @@
       <c r="H547" s="11" t="n"/>
       <c r="I547" s="34" t="n"/>
       <c r="J547" s="11" t="n"/>
+      <c r="K547" s="11" t="n"/>
     </row>
     <row r="548" ht="18" customHeight="1" s="42">
       <c r="A548" s="19" t="n"/>
@@ -11285,6 +11867,7 @@
       <c r="H548" s="19" t="n"/>
       <c r="I548" s="33" t="n"/>
       <c r="J548" s="19" t="n"/>
+      <c r="K548" s="19" t="n"/>
     </row>
     <row r="549" ht="18" customHeight="1" s="42">
       <c r="A549" s="11" t="n"/>
@@ -11297,6 +11880,7 @@
       <c r="H549" s="11" t="n"/>
       <c r="I549" s="34" t="n"/>
       <c r="J549" s="11" t="n"/>
+      <c r="K549" s="11" t="n"/>
     </row>
     <row r="550" ht="18" customHeight="1" s="42">
       <c r="A550" s="19" t="n"/>
@@ -11309,6 +11893,7 @@
       <c r="H550" s="19" t="n"/>
       <c r="I550" s="33" t="n"/>
       <c r="J550" s="19" t="n"/>
+      <c r="K550" s="19" t="n"/>
     </row>
     <row r="551" ht="18" customHeight="1" s="42">
       <c r="A551" s="11" t="n"/>
@@ -11321,6 +11906,7 @@
       <c r="H551" s="11" t="n"/>
       <c r="I551" s="34" t="n"/>
       <c r="J551" s="11" t="n"/>
+      <c r="K551" s="11" t="n"/>
     </row>
     <row r="552" ht="18" customHeight="1" s="42">
       <c r="A552" s="19" t="n"/>
@@ -11333,6 +11919,7 @@
       <c r="H552" s="19" t="n"/>
       <c r="I552" s="33" t="n"/>
       <c r="J552" s="19" t="n"/>
+      <c r="K552" s="19" t="n"/>
     </row>
     <row r="553" ht="18" customHeight="1" s="42">
       <c r="A553" s="11" t="n"/>
@@ -11345,6 +11932,7 @@
       <c r="H553" s="11" t="n"/>
       <c r="I553" s="34" t="n"/>
       <c r="J553" s="11" t="n"/>
+      <c r="K553" s="11" t="n"/>
     </row>
     <row r="554" ht="18" customHeight="1" s="42">
       <c r="A554" s="19" t="n"/>
@@ -11357,6 +11945,7 @@
       <c r="H554" s="19" t="n"/>
       <c r="I554" s="33" t="n"/>
       <c r="J554" s="19" t="n"/>
+      <c r="K554" s="19" t="n"/>
     </row>
     <row r="555" ht="18" customHeight="1" s="42">
       <c r="A555" s="11" t="n"/>
@@ -11369,6 +11958,7 @@
       <c r="H555" s="11" t="n"/>
       <c r="I555" s="34" t="n"/>
       <c r="J555" s="11" t="n"/>
+      <c r="K555" s="11" t="n"/>
     </row>
     <row r="556" ht="18" customHeight="1" s="42">
       <c r="A556" s="19" t="n"/>
@@ -11381,6 +11971,7 @@
       <c r="H556" s="19" t="n"/>
       <c r="I556" s="33" t="n"/>
       <c r="J556" s="19" t="n"/>
+      <c r="K556" s="19" t="n"/>
     </row>
     <row r="557" ht="18" customHeight="1" s="42">
       <c r="A557" s="11" t="n"/>
@@ -11393,6 +11984,7 @@
       <c r="H557" s="11" t="n"/>
       <c r="I557" s="34" t="n"/>
       <c r="J557" s="11" t="n"/>
+      <c r="K557" s="11" t="n"/>
     </row>
     <row r="558" ht="18" customHeight="1" s="42">
       <c r="A558" s="19" t="n"/>
@@ -11405,6 +11997,7 @@
       <c r="H558" s="19" t="n"/>
       <c r="I558" s="33" t="n"/>
       <c r="J558" s="19" t="n"/>
+      <c r="K558" s="19" t="n"/>
     </row>
     <row r="559" ht="18" customHeight="1" s="42">
       <c r="A559" s="11" t="n"/>
@@ -11417,6 +12010,7 @@
       <c r="H559" s="11" t="n"/>
       <c r="I559" s="34" t="n"/>
       <c r="J559" s="11" t="n"/>
+      <c r="K559" s="11" t="n"/>
     </row>
     <row r="560" ht="18" customHeight="1" s="42">
       <c r="A560" s="19" t="n"/>
@@ -11429,6 +12023,7 @@
       <c r="H560" s="19" t="n"/>
       <c r="I560" s="33" t="n"/>
       <c r="J560" s="19" t="n"/>
+      <c r="K560" s="19" t="n"/>
     </row>
     <row r="561" ht="18" customHeight="1" s="42">
       <c r="A561" s="11" t="n"/>
@@ -11441,6 +12036,7 @@
       <c r="H561" s="11" t="n"/>
       <c r="I561" s="34" t="n"/>
       <c r="J561" s="11" t="n"/>
+      <c r="K561" s="11" t="n"/>
     </row>
     <row r="562" ht="18" customHeight="1" s="42">
       <c r="A562" s="19" t="n"/>
@@ -11453,6 +12049,7 @@
       <c r="H562" s="19" t="n"/>
       <c r="I562" s="33" t="n"/>
       <c r="J562" s="19" t="n"/>
+      <c r="K562" s="19" t="n"/>
     </row>
     <row r="563" ht="18" customHeight="1" s="42">
       <c r="A563" s="11" t="n"/>
@@ -11465,6 +12062,7 @@
       <c r="H563" s="11" t="n"/>
       <c r="I563" s="34" t="n"/>
       <c r="J563" s="11" t="n"/>
+      <c r="K563" s="11" t="n"/>
     </row>
     <row r="564" ht="18" customHeight="1" s="42">
       <c r="A564" s="19" t="n"/>
@@ -11477,6 +12075,7 @@
       <c r="H564" s="19" t="n"/>
       <c r="I564" s="33" t="n"/>
       <c r="J564" s="19" t="n"/>
+      <c r="K564" s="19" t="n"/>
     </row>
     <row r="565" ht="18" customHeight="1" s="42">
       <c r="A565" s="11" t="n"/>
@@ -11489,6 +12088,7 @@
       <c r="H565" s="11" t="n"/>
       <c r="I565" s="34" t="n"/>
       <c r="J565" s="11" t="n"/>
+      <c r="K565" s="11" t="n"/>
     </row>
     <row r="566" ht="18" customHeight="1" s="42">
       <c r="A566" s="19" t="n"/>
@@ -11501,6 +12101,7 @@
       <c r="H566" s="19" t="n"/>
       <c r="I566" s="33" t="n"/>
       <c r="J566" s="19" t="n"/>
+      <c r="K566" s="19" t="n"/>
     </row>
     <row r="567" ht="18" customHeight="1" s="42">
       <c r="A567" s="11" t="n"/>
@@ -11513,6 +12114,7 @@
       <c r="H567" s="11" t="n"/>
       <c r="I567" s="34" t="n"/>
       <c r="J567" s="11" t="n"/>
+      <c r="K567" s="11" t="n"/>
     </row>
     <row r="568" ht="18" customHeight="1" s="42">
       <c r="A568" s="19" t="n"/>
@@ -11525,6 +12127,7 @@
       <c r="H568" s="19" t="n"/>
       <c r="I568" s="33" t="n"/>
       <c r="J568" s="19" t="n"/>
+      <c r="K568" s="19" t="n"/>
     </row>
     <row r="569" ht="18" customHeight="1" s="42">
       <c r="A569" s="11" t="n"/>
@@ -11537,6 +12140,7 @@
       <c r="H569" s="11" t="n"/>
       <c r="I569" s="34" t="n"/>
       <c r="J569" s="11" t="n"/>
+      <c r="K569" s="11" t="n"/>
     </row>
     <row r="570" ht="18" customHeight="1" s="42">
       <c r="A570" s="19" t="n"/>
@@ -11549,6 +12153,7 @@
       <c r="H570" s="19" t="n"/>
       <c r="I570" s="33" t="n"/>
       <c r="J570" s="19" t="n"/>
+      <c r="K570" s="19" t="n"/>
     </row>
     <row r="571" ht="18" customHeight="1" s="42">
       <c r="A571" s="11" t="n"/>
@@ -11561,6 +12166,7 @@
       <c r="H571" s="11" t="n"/>
       <c r="I571" s="34" t="n"/>
       <c r="J571" s="11" t="n"/>
+      <c r="K571" s="11" t="n"/>
     </row>
     <row r="572" ht="18" customHeight="1" s="42">
       <c r="A572" s="19" t="n"/>
@@ -11573,6 +12179,7 @@
       <c r="H572" s="19" t="n"/>
       <c r="I572" s="33" t="n"/>
       <c r="J572" s="19" t="n"/>
+      <c r="K572" s="19" t="n"/>
     </row>
     <row r="573" ht="18" customHeight="1" s="42">
       <c r="A573" s="11" t="n"/>
@@ -11585,6 +12192,7 @@
       <c r="H573" s="11" t="n"/>
       <c r="I573" s="34" t="n"/>
       <c r="J573" s="11" t="n"/>
+      <c r="K573" s="11" t="n"/>
     </row>
     <row r="574" ht="18" customHeight="1" s="42">
       <c r="A574" s="19" t="n"/>
@@ -11597,6 +12205,7 @@
       <c r="H574" s="19" t="n"/>
       <c r="I574" s="33" t="n"/>
       <c r="J574" s="19" t="n"/>
+      <c r="K574" s="19" t="n"/>
     </row>
     <row r="575" ht="18" customHeight="1" s="42">
       <c r="A575" s="11" t="n"/>
@@ -11609,6 +12218,7 @@
       <c r="H575" s="11" t="n"/>
       <c r="I575" s="34" t="n"/>
       <c r="J575" s="11" t="n"/>
+      <c r="K575" s="11" t="n"/>
     </row>
     <row r="576" ht="18" customHeight="1" s="42">
       <c r="A576" s="19" t="n"/>
@@ -11621,6 +12231,7 @@
       <c r="H576" s="19" t="n"/>
       <c r="I576" s="33" t="n"/>
       <c r="J576" s="19" t="n"/>
+      <c r="K576" s="19" t="n"/>
     </row>
     <row r="577" ht="18" customHeight="1" s="42">
       <c r="A577" s="11" t="n"/>
@@ -11633,6 +12244,7 @@
       <c r="H577" s="11" t="n"/>
       <c r="I577" s="34" t="n"/>
       <c r="J577" s="11" t="n"/>
+      <c r="K577" s="11" t="n"/>
     </row>
     <row r="578" ht="18" customHeight="1" s="42">
       <c r="A578" s="19" t="n"/>
@@ -11645,6 +12257,7 @@
       <c r="H578" s="19" t="n"/>
       <c r="I578" s="33" t="n"/>
       <c r="J578" s="19" t="n"/>
+      <c r="K578" s="19" t="n"/>
     </row>
     <row r="579" ht="18" customHeight="1" s="42">
       <c r="A579" s="11" t="n"/>
@@ -11657,6 +12270,7 @@
       <c r="H579" s="11" t="n"/>
       <c r="I579" s="34" t="n"/>
       <c r="J579" s="11" t="n"/>
+      <c r="K579" s="11" t="n"/>
     </row>
     <row r="580" ht="18" customHeight="1" s="42">
       <c r="A580" s="19" t="n"/>
@@ -11669,6 +12283,7 @@
       <c r="H580" s="19" t="n"/>
       <c r="I580" s="33" t="n"/>
       <c r="J580" s="19" t="n"/>
+      <c r="K580" s="19" t="n"/>
     </row>
     <row r="581" ht="18" customHeight="1" s="42">
       <c r="A581" s="11" t="n"/>
@@ -11681,6 +12296,7 @@
       <c r="H581" s="11" t="n"/>
       <c r="I581" s="34" t="n"/>
       <c r="J581" s="11" t="n"/>
+      <c r="K581" s="11" t="n"/>
     </row>
     <row r="582" ht="18" customHeight="1" s="42">
       <c r="A582" s="19" t="n"/>
@@ -11693,6 +12309,7 @@
       <c r="H582" s="19" t="n"/>
       <c r="I582" s="33" t="n"/>
       <c r="J582" s="19" t="n"/>
+      <c r="K582" s="19" t="n"/>
     </row>
     <row r="583" ht="18" customHeight="1" s="42">
       <c r="A583" s="11" t="n"/>
@@ -11705,6 +12322,7 @@
       <c r="H583" s="11" t="n"/>
       <c r="I583" s="34" t="n"/>
       <c r="J583" s="11" t="n"/>
+      <c r="K583" s="11" t="n"/>
     </row>
     <row r="584" ht="18" customHeight="1" s="42">
       <c r="A584" s="19" t="n"/>
@@ -11717,6 +12335,7 @@
       <c r="H584" s="19" t="n"/>
       <c r="I584" s="33" t="n"/>
       <c r="J584" s="19" t="n"/>
+      <c r="K584" s="19" t="n"/>
     </row>
     <row r="585" ht="18" customHeight="1" s="42">
       <c r="A585" s="11" t="n"/>
@@ -11729,6 +12348,7 @@
       <c r="H585" s="11" t="n"/>
       <c r="I585" s="34" t="n"/>
       <c r="J585" s="11" t="n"/>
+      <c r="K585" s="11" t="n"/>
     </row>
     <row r="586" ht="18" customHeight="1" s="42">
       <c r="A586" s="19" t="n"/>
@@ -11741,6 +12361,7 @@
       <c r="H586" s="19" t="n"/>
       <c r="I586" s="33" t="n"/>
       <c r="J586" s="19" t="n"/>
+      <c r="K586" s="19" t="n"/>
     </row>
     <row r="587" ht="18" customHeight="1" s="42">
       <c r="A587" s="11" t="n"/>
@@ -11753,6 +12374,7 @@
       <c r="H587" s="11" t="n"/>
       <c r="I587" s="34" t="n"/>
       <c r="J587" s="11" t="n"/>
+      <c r="K587" s="11" t="n"/>
     </row>
     <row r="588" ht="18" customHeight="1" s="42">
       <c r="A588" s="19" t="n"/>
@@ -11765,6 +12387,7 @@
       <c r="H588" s="19" t="n"/>
       <c r="I588" s="33" t="n"/>
       <c r="J588" s="19" t="n"/>
+      <c r="K588" s="19" t="n"/>
     </row>
     <row r="589" ht="18" customHeight="1" s="42">
       <c r="A589" s="11" t="n"/>
@@ -11777,6 +12400,7 @@
       <c r="H589" s="11" t="n"/>
       <c r="I589" s="34" t="n"/>
       <c r="J589" s="11" t="n"/>
+      <c r="K589" s="11" t="n"/>
     </row>
     <row r="590" ht="18" customHeight="1" s="42">
       <c r="A590" s="19" t="n"/>
@@ -11789,6 +12413,7 @@
       <c r="H590" s="19" t="n"/>
       <c r="I590" s="33" t="n"/>
       <c r="J590" s="19" t="n"/>
+      <c r="K590" s="19" t="n"/>
     </row>
     <row r="591" ht="18" customHeight="1" s="42">
       <c r="A591" s="11" t="n"/>
@@ -11801,6 +12426,7 @@
       <c r="H591" s="11" t="n"/>
       <c r="I591" s="34" t="n"/>
       <c r="J591" s="11" t="n"/>
+      <c r="K591" s="11" t="n"/>
     </row>
     <row r="592" ht="18" customHeight="1" s="42">
       <c r="A592" s="19" t="n"/>
@@ -11813,6 +12439,7 @@
       <c r="H592" s="19" t="n"/>
       <c r="I592" s="33" t="n"/>
       <c r="J592" s="19" t="n"/>
+      <c r="K592" s="19" t="n"/>
     </row>
     <row r="593" ht="18" customHeight="1" s="42">
       <c r="A593" s="11" t="n"/>
@@ -11825,6 +12452,7 @@
       <c r="H593" s="11" t="n"/>
       <c r="I593" s="34" t="n"/>
       <c r="J593" s="11" t="n"/>
+      <c r="K593" s="11" t="n"/>
     </row>
     <row r="594" ht="18" customHeight="1" s="42">
       <c r="A594" s="19" t="n"/>
@@ -11837,6 +12465,7 @@
       <c r="H594" s="19" t="n"/>
       <c r="I594" s="33" t="n"/>
       <c r="J594" s="19" t="n"/>
+      <c r="K594" s="19" t="n"/>
     </row>
     <row r="595" ht="18" customHeight="1" s="42">
       <c r="A595" s="11" t="n"/>
@@ -11849,6 +12478,7 @@
       <c r="H595" s="11" t="n"/>
       <c r="I595" s="34" t="n"/>
       <c r="J595" s="11" t="n"/>
+      <c r="K595" s="11" t="n"/>
     </row>
     <row r="596" ht="18" customHeight="1" s="42">
       <c r="A596" s="19" t="n"/>
@@ -11861,6 +12491,7 @@
       <c r="H596" s="19" t="n"/>
       <c r="I596" s="33" t="n"/>
       <c r="J596" s="19" t="n"/>
+      <c r="K596" s="19" t="n"/>
     </row>
     <row r="597" ht="18" customHeight="1" s="42">
       <c r="A597" s="11" t="n"/>
@@ -11873,6 +12504,7 @@
       <c r="H597" s="11" t="n"/>
       <c r="I597" s="34" t="n"/>
       <c r="J597" s="11" t="n"/>
+      <c r="K597" s="11" t="n"/>
     </row>
     <row r="598" ht="18" customHeight="1" s="42">
       <c r="A598" s="19" t="n"/>
@@ -11885,6 +12517,7 @@
       <c r="H598" s="19" t="n"/>
       <c r="I598" s="33" t="n"/>
       <c r="J598" s="19" t="n"/>
+      <c r="K598" s="19" t="n"/>
     </row>
     <row r="599" ht="18" customHeight="1" s="42">
       <c r="A599" s="11" t="n"/>
@@ -11897,6 +12530,7 @@
       <c r="H599" s="11" t="n"/>
       <c r="I599" s="34" t="n"/>
       <c r="J599" s="11" t="n"/>
+      <c r="K599" s="11" t="n"/>
     </row>
     <row r="600" ht="18" customHeight="1" s="42">
       <c r="A600" s="19" t="n"/>
@@ -11909,12 +12543,13 @@
       <c r="H600" s="19" t="n"/>
       <c r="I600" s="33" t="n"/>
       <c r="J600" s="19" t="n"/>
+      <c r="K600" s="19" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:J600"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F600">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
@@ -11943,7 +12578,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12204,7 +12839,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="58" customHeight="1" s="42">
+    <row r="9" ht="70" customHeight="1" s="42">
       <c r="A9" s="13" t="n">
         <v>5</v>
       </c>
@@ -12220,17 +12855,17 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>Unmapped category or item-type codes, which appear in the reports as a blank slicer entry.</t>
+          <t>Unmapped category codes, which appear in the reports as a blank slicer entry.</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>SSMS</t>
+          <t>Power BI — Power Query (doc 02 §6.5) or DAX query view (V05)</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>Run the coverage query in doc 02 §6.5. A non-zero result lists exactly which codes are missing from RefMappings.xlsx.</t>
+          <t>Run the coverage query in doc 02 §6.5, or the DAX EXCEPT query in V05. A non-zero result lists exactly which category codes are missing from RefMappings.xlsx. Item-type mapping is checked separately: no “Unmapped” entry in the ItemType slicer (doc 25 G2.05).</t>
         </is>
       </c>
       <c r="G9" s="26" t="inlineStr">
@@ -12339,7 +12974,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1" s="42">
+    <row r="12" ht="70" customHeight="1" s="42">
       <c r="A12" s="21" t="n">
         <v>8</v>
       </c>
@@ -12365,7 +13000,7 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Inspect every Tier 3 visual, every tooltip and every text box. This is the check to run last and to run slowly.</t>
+          <t>Inspect every visual on the V08 list — every visual carrying a case measure, the text on those pages, the drillthrough page and the tooltip page — including each tooltip. This is the check to run last and to run slowly.</t>
         </is>
       </c>
       <c r="G12" s="29" t="inlineStr">
@@ -12384,7 +13019,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1" s="42">
+    <row r="13" ht="83.5" customHeight="1" s="42">
       <c r="A13" s="13" t="n">
         <v>9</v>
       </c>
@@ -12410,7 +13045,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>On R1 Page 3, step through each slicer combination and confirm the baseline card holds a value. Note any combination that blanks it.</t>
+          <t>Run the V09 queries across BeverageClass × ItemType × Year for On-Premise Share 2019 Baseline and Item Type Share vs 2019 (pp); then on R1 Page 3 and R2 Page 2 step through the date slicer (including ranges without 2019) and every slicer value, and confirm no baseline visual blanks.</t>
         </is>
       </c>
       <c r="G13" s="26" t="inlineStr">
@@ -12474,7 +13109,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1" s="42">
+    <row r="15" ht="43" customHeight="1" s="42">
       <c r="A15" s="13" t="n">
         <v>11</v>
       </c>
@@ -12500,7 +13135,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>Read the Return Rows card unfiltered and confirm the caveat text box is present on the page that uses it.</t>
+          <t>Read the Return Rows card unfiltered, confirm the tooltip on card 3.8 explains returns (doc 15 spec 3.8), and that no filter removes negative values.</t>
         </is>
       </c>
       <c r="G15" s="31" t="inlineStr">
@@ -12564,7 +13199,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1" s="42">
+    <row r="17" ht="43" customHeight="1" s="42">
       <c r="A17" s="13" t="n">
         <v>13</v>
       </c>
@@ -12590,7 +13225,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>Place Cohort Size on a table by CohortYear with a total, and compare the total against COUNTROWS(DimItem).</t>
+          <t>Place Cohort Size on a table by CohortYear with a total, and compare the total against COUNTROWS(DimItem). V13 Part 2 does this in DAX query view.</t>
         </is>
       </c>
       <c r="G17" s="26" t="inlineStr">
@@ -12609,7 +13244,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="58" customHeight="1" s="42">
+    <row r="18" ht="56.5" customHeight="1" s="42">
       <c r="A18" s="21" t="n">
         <v>14</v>
       </c>
@@ -12635,7 +13270,7 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>On the R3 Pareto visual, read the right-hand edge under each slicer combination in the doc 15 spec. Record the combinations tested.</t>
+          <t>Run the V14 query with no filter and again under each year and item type (Part 1b) — Cumulative must be exactly 1 each time. The R3 Pareto shows the top 100 items only, so the chart confirms behaviour, not the criterion.</t>
         </is>
       </c>
       <c r="G18" s="29" t="inlineStr">
@@ -12819,7 +13454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/22_Validation_Results.xlsx
+++ b/docs/22_Validation_Results.xlsx
@@ -1424,7 +1424,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="42" customHeight="1" s="42">
+    <row r="55" ht="56.5" customHeight="1" s="42">
       <c r="B55" s="1" t="inlineStr">
         <is>
           <t>docs/validation/</t>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>One step-by-step procedure per check, V01 to V17, written for someone who has never run it. Each exists as a .docx to read and an .xlsx with a Pass/Fail drop-down on every step. The results still belong here, on Check Results — the V files are the instructions, not the record.</t>
+          <t>One step-by-step procedure per check, V01 to V17, written for someone who has never run it. Each exists as a .docx to read and an .xlsx with a Pass/Fail drop-down on every tick table (V07, V08, V15, V16 and V17). The results still belong here, on Check Results — the V files are the instructions, not the record.</t>
         </is>
       </c>
     </row>
@@ -2184,6 +2184,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1" s="42">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -4346,6 +4347,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1" s="42">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -12612,6 +12614,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1" s="42">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -13487,6 +13490,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1" s="42">
       <c r="A4" s="8" t="inlineStr">
         <is>
